--- a/docs/src/reference/data-dictionaries/S_Dict.xlsx
+++ b/docs/src/reference/data-dictionaries/S_Dict.xlsx
@@ -7445,12 +7445,12 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>SAMSHA 2019, 2021; Vivitrol 2020; OSRM 2020;</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019; Vivitrol, 2020; Open Source Routing Machine, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB88" t="inlineStr"/>
@@ -7509,12 +7509,12 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>SAMSHA 2019, 2021; Vivitrol 2020; OSRM 2020;</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019; Vivitrol, 2020; Open Source Routing Machine, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB89" t="inlineStr"/>
@@ -7573,12 +7573,12 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>SAMSHA 2019, 2021; Vivitrol 2020; OSRM 2020;</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019; Vivitrol, 2020; Open Source Routing Machine, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB90" t="inlineStr"/>
@@ -7637,12 +7637,12 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>SAMSHA 2019, 2021; Vivitrol 2020; OSRM 2020;</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019; Vivitrol, 2020; Open Source Routing Machine, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB91" t="inlineStr"/>
@@ -7701,12 +7701,12 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>SAMSHA 2019, 2021; Vivitrol 2020; OSRM 2020;</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019; Vivitrol, 2020; Open Source Routing Machine, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB92" t="inlineStr"/>
@@ -7765,12 +7765,12 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>SAMSHA 2019, 2021; Vivitrol 2020; OSRM 2020;</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019; Vivitrol, 2020; Open Source Routing Machine, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB93" t="inlineStr"/>
@@ -7829,12 +7829,12 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>SAMSHA 2019, 2021; Vivitrol 2020; OSRM 2020;</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019; Vivitrol, 2020; Open Source Routing Machine, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB94" t="inlineStr"/>
@@ -7893,12 +7893,12 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>SAMSHA 2019, 2021; Vivitrol 2020; OSRM 2020;</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019; Vivitrol, 2020; Open Source Routing Machine, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB95" t="inlineStr"/>
@@ -7957,12 +7957,12 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>SAMSHA 2019, 2021; Vivitrol 2020; OSRM 2020;</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019; Vivitrol, 2020; Open Source Routing Machine, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB96" t="inlineStr"/>
@@ -8021,12 +8021,12 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>SAMSHA 2019, 2021; Vivitrol 2020; OSRM 2020;</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019; Vivitrol, 2020; Open Source Routing Machine, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB97" t="inlineStr"/>
@@ -8085,12 +8085,12 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>SAMSHA 2019, 2021; Vivitrol 2020; OSRM 2020;</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019; Vivitrol, 2020; Open Source Routing Machine, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB98" t="inlineStr"/>
@@ -8149,12 +8149,12 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>SAMSHA 2019, 2021; Vivitrol 2020; OSRM 2020;</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019; Vivitrol, 2020; Open Source Routing Machine, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB99" t="inlineStr"/>
@@ -8213,12 +8213,12 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>SAMSHA 2019, 2021; Vivitrol 2020; OSRM 2020;</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019; Vivitrol, 2020; Open Source Routing Machine, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB100" t="inlineStr"/>
@@ -8277,12 +8277,12 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>SAMSHA 2019, 2021; Vivitrol 2020; OSRM 2020;</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019; Vivitrol, 2020; Open Source Routing Machine, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB101" t="inlineStr"/>

--- a/docs/src/reference/data-dictionaries/S_Dict.xlsx
+++ b/docs/src/reference/data-dictionaries/S_Dict.xlsx
@@ -7253,12 +7253,12 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>CovidCareMap 2020</t>
+          <t>CovidCareMap 2020; CMS 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>CovidCareMap, 2020</t>
+          <t xml:space="preserve"> CovidCareMap Healthcare System Capacity data, 2020; Centers for Medicare &amp; Medicaid Services, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB85" t="inlineStr"/>
@@ -7317,12 +7317,12 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>CovidCareMap 2020</t>
+          <t>CovidCareMap 2020; CMS 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>CovidCareMap, 2020</t>
+          <t xml:space="preserve"> CovidCareMap Healthcare System Capacity data, 2020; Centers for Medicare &amp; Medicaid Services, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB86" t="inlineStr"/>
@@ -7381,12 +7381,12 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>CovidCareMap 2020</t>
+          <t>CovidCareMap 2020; CMS 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>CovidCareMap, 2020</t>
+          <t xml:space="preserve"> CovidCareMap Healthcare System Capacity data, 2020; Centers for Medicare &amp; Medicaid Services, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB87" t="inlineStr"/>
@@ -8512,7 +8512,11 @@
       <c r="P105" t="inlineStr"/>
       <c r="Q105" t="inlineStr"/>
       <c r="R105" t="inlineStr"/>
-      <c r="S105" t="inlineStr"/>
+      <c r="S105" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T105" t="inlineStr"/>
       <c r="U105" t="inlineStr"/>
       <c r="V105" t="inlineStr">
@@ -8533,12 +8537,12 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>InfoGroup 2019</t>
+          <t>InfoGroup 2019; Amazon S3 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>InfoGroup, 2019</t>
+          <t>InfoGroup, 2019; Amazon S3, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB105" t="inlineStr"/>
@@ -8576,7 +8580,11 @@
       <c r="P106" t="inlineStr"/>
       <c r="Q106" t="inlineStr"/>
       <c r="R106" t="inlineStr"/>
-      <c r="S106" t="inlineStr"/>
+      <c r="S106" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T106" t="inlineStr"/>
       <c r="U106" t="inlineStr"/>
       <c r="V106" t="inlineStr">
@@ -8597,12 +8605,12 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>InfoGroup 2019</t>
+          <t>InfoGroup 2019; Amazon S3 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>InfoGroup, 2019</t>
+          <t>InfoGroup, 2019; Amazon S3, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB106" t="inlineStr"/>
@@ -8640,7 +8648,11 @@
       <c r="P107" t="inlineStr"/>
       <c r="Q107" t="inlineStr"/>
       <c r="R107" t="inlineStr"/>
-      <c r="S107" t="inlineStr"/>
+      <c r="S107" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T107" t="inlineStr"/>
       <c r="U107" t="inlineStr"/>
       <c r="V107" t="inlineStr">
@@ -8661,12 +8673,12 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>InfoGroup 2019</t>
+          <t>InfoGroup 2019; Amazon S3 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>InfoGroup, 2019</t>
+          <t>InfoGroup, 2019; Amazon S3, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB107" t="inlineStr"/>

--- a/docs/src/reference/data-dictionaries/S_Dict.xlsx
+++ b/docs/src/reference/data-dictionaries/S_Dict.xlsx
@@ -7232,7 +7232,11 @@
       <c r="P85" t="inlineStr"/>
       <c r="Q85" t="inlineStr"/>
       <c r="R85" t="inlineStr"/>
-      <c r="S85" t="inlineStr"/>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T85" t="inlineStr"/>
       <c r="U85" t="inlineStr"/>
       <c r="V85" t="inlineStr">
@@ -7296,7 +7300,11 @@
       <c r="P86" t="inlineStr"/>
       <c r="Q86" t="inlineStr"/>
       <c r="R86" t="inlineStr"/>
-      <c r="S86" t="inlineStr"/>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T86" t="inlineStr"/>
       <c r="U86" t="inlineStr"/>
       <c r="V86" t="inlineStr">
@@ -7360,7 +7368,11 @@
       <c r="P87" t="inlineStr"/>
       <c r="Q87" t="inlineStr"/>
       <c r="R87" t="inlineStr"/>
-      <c r="S87" t="inlineStr"/>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T87" t="inlineStr"/>
       <c r="U87" t="inlineStr"/>
       <c r="V87" t="inlineStr">
@@ -7808,7 +7820,11 @@
       <c r="P94" t="inlineStr"/>
       <c r="Q94" t="inlineStr"/>
       <c r="R94" t="inlineStr"/>
-      <c r="S94" t="inlineStr"/>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T94" t="inlineStr"/>
       <c r="U94" t="inlineStr"/>
       <c r="V94" t="inlineStr">
@@ -7872,7 +7888,11 @@
       <c r="P95" t="inlineStr"/>
       <c r="Q95" t="inlineStr"/>
       <c r="R95" t="inlineStr"/>
-      <c r="S95" t="inlineStr"/>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T95" t="inlineStr"/>
       <c r="U95" t="inlineStr"/>
       <c r="V95" t="inlineStr">
@@ -7936,7 +7956,11 @@
       <c r="P96" t="inlineStr"/>
       <c r="Q96" t="inlineStr"/>
       <c r="R96" t="inlineStr"/>
-      <c r="S96" t="inlineStr"/>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T96" t="inlineStr"/>
       <c r="U96" t="inlineStr"/>
       <c r="V96" t="inlineStr">
@@ -8320,7 +8344,11 @@
       <c r="P102" t="inlineStr"/>
       <c r="Q102" t="inlineStr"/>
       <c r="R102" t="inlineStr"/>
-      <c r="S102" t="inlineStr"/>
+      <c r="S102" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T102" t="inlineStr"/>
       <c r="U102" t="inlineStr"/>
       <c r="V102" t="inlineStr">
@@ -8384,7 +8412,11 @@
       <c r="P103" t="inlineStr"/>
       <c r="Q103" t="inlineStr"/>
       <c r="R103" t="inlineStr"/>
-      <c r="S103" t="inlineStr"/>
+      <c r="S103" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T103" t="inlineStr"/>
       <c r="U103" t="inlineStr"/>
       <c r="V103" t="inlineStr">
@@ -8448,7 +8480,11 @@
       <c r="P104" t="inlineStr"/>
       <c r="Q104" t="inlineStr"/>
       <c r="R104" t="inlineStr"/>
-      <c r="S104" t="inlineStr"/>
+      <c r="S104" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T104" t="inlineStr"/>
       <c r="U104" t="inlineStr"/>
       <c r="V104" t="inlineStr">

--- a/docs/src/reference/data-dictionaries/S_Dict.xlsx
+++ b/docs/src/reference/data-dictionaries/S_Dict.xlsx
@@ -8369,12 +8369,12 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>SAMHSA 2020</t>
+          <t>SAMHSA 2020, 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB102" t="inlineStr"/>
@@ -8437,12 +8437,12 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>SAMHSA 2020</t>
+          <t>SAMHSA 2020, 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB103" t="inlineStr"/>
@@ -8505,12 +8505,12 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>SAMHSA 2020</t>
+          <t>SAMHSA 2020, 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB104" t="inlineStr"/>

--- a/docs/src/reference/data-dictionaries/S_Dict.xlsx
+++ b/docs/src/reference/data-dictionaries/S_Dict.xlsx
@@ -1649,12 +1649,12 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>Vera Institute of Justice 2025</t>
+          <t>Vera 2017, 2022, 2023, 2024</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>Vera Institute of Justice, 2025</t>
+          <t>Vera Institute of Justice 2017, 2022, 2023, 2024</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr"/>
@@ -1721,12 +1721,12 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>Vera Institute of Justice 2025</t>
+          <t>Vera 2017, 2022, 2023, 2024</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>Vera Institute of Justice, 2025</t>
+          <t>Vera Institute of Justice 2017, 2022, 2023, 2024</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr"/>
@@ -1797,12 +1797,12 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>Vera Institute of Justice 2025</t>
+          <t>Vera 2017, 2022, 2023, 2024</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>Vera Institute of Justice, 2025</t>
+          <t>Vera Institute of Justice 2017, 2022, 2023, 2024</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr"/>
@@ -1873,12 +1873,12 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>Vera Institute of Justice 2025</t>
+          <t>Vera 2017, 2022, 2023, 2024</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>Vera Institute of Justice, 2025</t>
+          <t>Vera Institute of Justice 2017, 2022, 2023, 2024</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr"/>
@@ -1949,12 +1949,12 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>Vera Institute of Justice 2025</t>
+          <t>Vera 2017, 2022, 2023, 2024</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>Vera Institute of Justice, 2025</t>
+          <t>Vera Institute of Justice 2017, 2022, 2023, 2024</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr"/>
@@ -2025,12 +2025,12 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>Vera Institute of Justice 2025</t>
+          <t>Vera 2017, 2022, 2023, 2024</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>Vera Institute of Justice, 2025</t>
+          <t>Vera Institute of Justice 2017, 2022, 2023, 2024</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr"/>
@@ -2062,7 +2062,11 @@
       </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
@@ -2093,12 +2097,12 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>Vera Institute of Justice 2025</t>
+          <t>Vera 2016, 2019, 2022, 2024</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>Vera Institute of Justice, 2025</t>
+          <t>Vera Institute of Justice 2016, 2019, 2022, 2024</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr"/>
@@ -2130,7 +2134,11 @@
       </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
@@ -2161,12 +2169,12 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>Vera Institute of Justice 2025</t>
+          <t>Vera 2016, 2019, 2022, 2024</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>Vera Institute of Justice, 2025</t>
+          <t>Vera Institute of Justice 2016, 2019, 2022, 2024</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr"/>
@@ -2198,7 +2206,11 @@
       </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
@@ -2233,12 +2245,12 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>Vera Institute of Justice 2025</t>
+          <t>Vera 2016, 2019, 2022, 2024</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>Vera Institute of Justice, 2025</t>
+          <t>Vera Institute of Justice 2016, 2019, 2022, 2024</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr"/>
@@ -2270,7 +2282,11 @@
       </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
@@ -2305,12 +2321,12 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>Vera Institute of Justice 2025</t>
+          <t>Vera 2016, 2019, 2022, 2024</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>Vera Institute of Justice, 2025</t>
+          <t>Vera Institute of Justice 2016, 2019, 2022, 2024</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr"/>
@@ -5989,12 +6005,12 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>County Health Rankings &amp; Roadmaps (CHR&amp;R), 2025</t>
+          <t>CHR&amp;R 2025</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>County Health Rankings &amp; Roadmaps (CHR&amp;R), 2025</t>
+          <t>County Health Rankings &amp; Roadmaps (CHR&amp;R) 2025</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr"/>

--- a/docs/src/reference/data-dictionaries/S_Dict.xlsx
+++ b/docs/src/reference/data-dictionaries/S_Dict.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD236"/>
+  <dimension ref="A1:AD230"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -7767,11 +7767,7 @@
       <c r="K93" t="inlineStr"/>
       <c r="L93" t="inlineStr"/>
       <c r="M93" t="inlineStr"/>
-      <c r="N93" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N93" t="inlineStr"/>
       <c r="O93" t="inlineStr"/>
       <c r="P93" t="inlineStr"/>
       <c r="Q93" t="inlineStr"/>
@@ -7785,12 +7781,12 @@
       <c r="U93" t="inlineStr"/>
       <c r="V93" t="inlineStr">
         <is>
-          <t>BupCtTmDr</t>
+          <t>BupCtTmDr2</t>
         </is>
       </c>
       <c r="W93" t="inlineStr">
         <is>
-          <t>Tracts with Buprenorphine Provider within 30-min (driving)</t>
+          <t>Count of Tracts within 30-min drive of Buprenorphine Provider, with Impedance factor</t>
         </is>
       </c>
       <c r="X93" t="inlineStr"/>
@@ -7849,12 +7845,12 @@
       <c r="U94" t="inlineStr"/>
       <c r="V94" t="inlineStr">
         <is>
-          <t>BupCtTmDr2</t>
+          <t>BupTmDrP2</t>
         </is>
       </c>
       <c r="W94" t="inlineStr">
         <is>
-          <t>Count of Tracts within 30-min drive of Buprenorphine Provider, with Impedance factor</t>
+          <t>% Tracts within 30-min drive of Buprenorphine Provider(BUP), with Impedance factor</t>
         </is>
       </c>
       <c r="X94" t="inlineStr"/>
@@ -7908,21 +7904,17 @@
       <c r="P95" t="inlineStr"/>
       <c r="Q95" t="inlineStr"/>
       <c r="R95" t="inlineStr"/>
-      <c r="S95" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="S95" t="inlineStr"/>
       <c r="T95" t="inlineStr"/>
       <c r="U95" t="inlineStr"/>
       <c r="V95" t="inlineStr">
         <is>
-          <t>BupTmDrP</t>
+          <t>CntBupT</t>
         </is>
       </c>
       <c r="W95" t="inlineStr">
         <is>
-          <t>% Tracts With Buprenorphine Provider (30-min drive)</t>
+          <t>Tracts with Buprenorphine Provider (30-min driving)</t>
         </is>
       </c>
       <c r="X95" t="inlineStr"/>
@@ -7967,26 +7959,26 @@
       <c r="K96" t="inlineStr"/>
       <c r="L96" t="inlineStr"/>
       <c r="M96" t="inlineStr"/>
-      <c r="N96" t="inlineStr"/>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O96" t="inlineStr"/>
       <c r="P96" t="inlineStr"/>
       <c r="Q96" t="inlineStr"/>
       <c r="R96" t="inlineStr"/>
-      <c r="S96" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="S96" t="inlineStr"/>
       <c r="T96" t="inlineStr"/>
       <c r="U96" t="inlineStr"/>
       <c r="V96" t="inlineStr">
         <is>
-          <t>BupTmDrP2</t>
+          <t>CntMetT</t>
         </is>
       </c>
       <c r="W96" t="inlineStr">
         <is>
-          <t>% Tracts within 30-min drive of Buprenorphine Provider(BUP), with Impedance factor</t>
+          <t>Tracts with Methadone Provider (30-min driving)</t>
         </is>
       </c>
       <c r="X96" t="inlineStr"/>
@@ -8045,12 +8037,12 @@
       <c r="U97" t="inlineStr"/>
       <c r="V97" t="inlineStr">
         <is>
-          <t>CntBupT</t>
+          <t>CntNaltT</t>
         </is>
       </c>
       <c r="W97" t="inlineStr">
         <is>
-          <t>Tracts with Buprenorphine Provider (30-min driving)</t>
+          <t>Tracts with Naltrexone Provider (30-min driving)</t>
         </is>
       </c>
       <c r="X97" t="inlineStr"/>
@@ -8104,17 +8096,21 @@
       <c r="P98" t="inlineStr"/>
       <c r="Q98" t="inlineStr"/>
       <c r="R98" t="inlineStr"/>
-      <c r="S98" t="inlineStr"/>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T98" t="inlineStr"/>
       <c r="U98" t="inlineStr"/>
       <c r="V98" t="inlineStr">
         <is>
-          <t>CntMetT</t>
+          <t>MetAvTmDr</t>
         </is>
       </c>
       <c r="W98" t="inlineStr">
         <is>
-          <t>Tracts with Methadone Provider (30-min driving)</t>
+          <t>Driving Time (min) to Nearest Methadone Provider</t>
         </is>
       </c>
       <c r="X98" t="inlineStr"/>
@@ -8159,26 +8155,26 @@
       <c r="K99" t="inlineStr"/>
       <c r="L99" t="inlineStr"/>
       <c r="M99" t="inlineStr"/>
-      <c r="N99" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N99" t="inlineStr"/>
       <c r="O99" t="inlineStr"/>
       <c r="P99" t="inlineStr"/>
       <c r="Q99" t="inlineStr"/>
       <c r="R99" t="inlineStr"/>
-      <c r="S99" t="inlineStr"/>
+      <c r="S99" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T99" t="inlineStr"/>
       <c r="U99" t="inlineStr"/>
       <c r="V99" t="inlineStr">
         <is>
-          <t>CntNaltT</t>
+          <t>MetAvTmDr2</t>
         </is>
       </c>
       <c r="W99" t="inlineStr">
         <is>
-          <t>Tracts with Naltrexone Provider (30-min driving)</t>
+          <t>Average driving time to nearest Methadone Provider(MET), with Impedance factor</t>
         </is>
       </c>
       <c r="X99" t="inlineStr"/>
@@ -8223,11 +8219,7 @@
       <c r="K100" t="inlineStr"/>
       <c r="L100" t="inlineStr"/>
       <c r="M100" t="inlineStr"/>
-      <c r="N100" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N100" t="inlineStr"/>
       <c r="O100" t="inlineStr"/>
       <c r="P100" t="inlineStr"/>
       <c r="Q100" t="inlineStr"/>
@@ -8241,12 +8233,12 @@
       <c r="U100" t="inlineStr"/>
       <c r="V100" t="inlineStr">
         <is>
-          <t>MetAvTmDr</t>
+          <t>MetCtTmDr2</t>
         </is>
       </c>
       <c r="W100" t="inlineStr">
         <is>
-          <t>Driving Time (min) to Nearest Methadone Provider</t>
+          <t>Count of Tracts within 30-min drive of Methadone Provider, with Impedance factor</t>
         </is>
       </c>
       <c r="X100" t="inlineStr"/>
@@ -8305,12 +8297,12 @@
       <c r="U101" t="inlineStr"/>
       <c r="V101" t="inlineStr">
         <is>
-          <t>MetAvTmDr2</t>
+          <t>MetTmDrP2</t>
         </is>
       </c>
       <c r="W101" t="inlineStr">
         <is>
-          <t>Average driving time to nearest Methadone Provider(MET), with Impedance factor</t>
+          <t>% Tracts within 30-min drive of Methadone Provider(MET), with Impedance factor</t>
         </is>
       </c>
       <c r="X101" t="inlineStr"/>
@@ -8373,12 +8365,12 @@
       <c r="U102" t="inlineStr"/>
       <c r="V102" t="inlineStr">
         <is>
-          <t>MetCtTmDr</t>
+          <t>NaltAvTmDr</t>
         </is>
       </c>
       <c r="W102" t="inlineStr">
         <is>
-          <t>Tracts with Methadone Provider within 30-min (driving)</t>
+          <t>Driving Time (min) to Nearest Naltrexone Provider</t>
         </is>
       </c>
       <c r="X102" t="inlineStr"/>
@@ -8437,12 +8429,12 @@
       <c r="U103" t="inlineStr"/>
       <c r="V103" t="inlineStr">
         <is>
-          <t>MetCtTmDr2</t>
+          <t>NaltAvTmDr2</t>
         </is>
       </c>
       <c r="W103" t="inlineStr">
         <is>
-          <t>Count of Tracts within 30-min drive of Methadone Provider, with Impedance factor</t>
+          <t>Average driving time to nearest Naltrexone Provider (NALT), with Impedance factor</t>
         </is>
       </c>
       <c r="X103" t="inlineStr"/>
@@ -8487,11 +8479,7 @@
       <c r="K104" t="inlineStr"/>
       <c r="L104" t="inlineStr"/>
       <c r="M104" t="inlineStr"/>
-      <c r="N104" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N104" t="inlineStr"/>
       <c r="O104" t="inlineStr"/>
       <c r="P104" t="inlineStr"/>
       <c r="Q104" t="inlineStr"/>
@@ -8505,12 +8493,12 @@
       <c r="U104" t="inlineStr"/>
       <c r="V104" t="inlineStr">
         <is>
-          <t>MetTmDrP</t>
+          <t>NaltCtTmDr2</t>
         </is>
       </c>
       <c r="W104" t="inlineStr">
         <is>
-          <t>% Tracts With Methadone Provider (30-min drive)</t>
+          <t>Count of Tracts within 30-min drive of Naltrexone Provider, with Impedance factor</t>
         </is>
       </c>
       <c r="X104" t="inlineStr"/>
@@ -8569,12 +8557,12 @@
       <c r="U105" t="inlineStr"/>
       <c r="V105" t="inlineStr">
         <is>
-          <t>MetTmDrP2</t>
+          <t>NaltTmDrP2</t>
         </is>
       </c>
       <c r="W105" t="inlineStr">
         <is>
-          <t>% Tracts within 30-min drive of Methadone Provider(MET), with Impedance factor</t>
+          <t>% Tracts within 30-min drive of Naltrexone Provider (NALT), with Impedance factor</t>
         </is>
       </c>
       <c r="X105" t="inlineStr"/>
@@ -8619,12 +8607,12 @@
       <c r="K106" t="inlineStr"/>
       <c r="L106" t="inlineStr"/>
       <c r="M106" t="inlineStr"/>
-      <c r="N106" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="O106" t="inlineStr"/>
+      <c r="N106" t="inlineStr"/>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="P106" t="inlineStr"/>
       <c r="Q106" t="inlineStr"/>
       <c r="R106" t="inlineStr"/>
@@ -8637,12 +8625,12 @@
       <c r="U106" t="inlineStr"/>
       <c r="V106" t="inlineStr">
         <is>
-          <t>NaltAvTmDr</t>
+          <t>OtpAvTmDr</t>
         </is>
       </c>
       <c r="W106" t="inlineStr">
         <is>
-          <t>Driving Time (min) to Nearest Naltrexone Provider</t>
+          <t>Driving Time (min) to nearest Opioid Treatment Program (OTP)</t>
         </is>
       </c>
       <c r="X106" t="inlineStr"/>
@@ -8701,12 +8689,12 @@
       <c r="U107" t="inlineStr"/>
       <c r="V107" t="inlineStr">
         <is>
-          <t>NaltAvTmDr2</t>
+          <t>OtpAvTmDr2</t>
         </is>
       </c>
       <c r="W107" t="inlineStr">
         <is>
-          <t>Average driving time to nearest Naltrexone Provider (NALT), with Impedance factor</t>
+          <t>Average driving time to nearest Opioid Treatment Provider (Otp), with Impedance factor</t>
         </is>
       </c>
       <c r="X107" t="inlineStr"/>
@@ -8751,12 +8739,12 @@
       <c r="K108" t="inlineStr"/>
       <c r="L108" t="inlineStr"/>
       <c r="M108" t="inlineStr"/>
-      <c r="N108" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="O108" t="inlineStr"/>
+      <c r="N108" t="inlineStr"/>
+      <c r="O108" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="P108" t="inlineStr"/>
       <c r="Q108" t="inlineStr"/>
       <c r="R108" t="inlineStr"/>
@@ -8769,12 +8757,12 @@
       <c r="U108" t="inlineStr"/>
       <c r="V108" t="inlineStr">
         <is>
-          <t>NaltCtTmDr</t>
+          <t>OtpCtTmDr</t>
         </is>
       </c>
       <c r="W108" t="inlineStr">
         <is>
-          <t>Tracts with Naltrexone Provider within 30-min (driving)</t>
+          <t>Tracts with Opioid Treatment Program (OTP) (30-min drive)</t>
         </is>
       </c>
       <c r="X108" t="inlineStr"/>
@@ -8833,12 +8821,12 @@
       <c r="U109" t="inlineStr"/>
       <c r="V109" t="inlineStr">
         <is>
-          <t>NaltCtTmDr2</t>
+          <t>OtpCtTmDr2</t>
         </is>
       </c>
       <c r="W109" t="inlineStr">
         <is>
-          <t>Count of Tracts within 30-min drive of Naltrexone Provider, with Impedance factor</t>
+          <t>Count of Tracts within 30-min drive of Opioid Treatment Provider, with Impedance factor</t>
         </is>
       </c>
       <c r="X109" t="inlineStr"/>
@@ -8883,30 +8871,26 @@
       <c r="K110" t="inlineStr"/>
       <c r="L110" t="inlineStr"/>
       <c r="M110" t="inlineStr"/>
-      <c r="N110" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="O110" t="inlineStr"/>
+      <c r="N110" t="inlineStr"/>
+      <c r="O110" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="P110" t="inlineStr"/>
       <c r="Q110" t="inlineStr"/>
       <c r="R110" t="inlineStr"/>
-      <c r="S110" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="S110" t="inlineStr"/>
       <c r="T110" t="inlineStr"/>
       <c r="U110" t="inlineStr"/>
       <c r="V110" t="inlineStr">
         <is>
-          <t>NaltTmDrP</t>
+          <t>OtpTmDrP</t>
         </is>
       </c>
       <c r="W110" t="inlineStr">
         <is>
-          <t>% Tracts With Naltrexone Provider (30-min drive)</t>
+          <t>% Tracts with Opioid Treatment Program (OTP) (30-min drive)</t>
         </is>
       </c>
       <c r="X110" t="inlineStr"/>
@@ -8965,12 +8949,12 @@
       <c r="U111" t="inlineStr"/>
       <c r="V111" t="inlineStr">
         <is>
-          <t>NaltTmDrP2</t>
+          <t>OtpTmDrP2</t>
         </is>
       </c>
       <c r="W111" t="inlineStr">
         <is>
-          <t>% Tracts within 30-min drive of Naltrexone Provider (NALT), with Impedance factor</t>
+          <t>% Tracts within 30-min drive of Opioid Treatment Provider (Otp), with Impedance factor</t>
         </is>
       </c>
       <c r="X111" t="inlineStr"/>
@@ -9015,30 +8999,26 @@
       <c r="K112" t="inlineStr"/>
       <c r="L112" t="inlineStr"/>
       <c r="M112" t="inlineStr"/>
-      <c r="N112" t="inlineStr"/>
-      <c r="O112" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O112" t="inlineStr"/>
       <c r="P112" t="inlineStr"/>
       <c r="Q112" t="inlineStr"/>
       <c r="R112" t="inlineStr"/>
-      <c r="S112" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="S112" t="inlineStr"/>
       <c r="T112" t="inlineStr"/>
       <c r="U112" t="inlineStr"/>
       <c r="V112" t="inlineStr">
         <is>
-          <t>OtpAvTmDr</t>
+          <t>PctBupT</t>
         </is>
       </c>
       <c r="W112" t="inlineStr">
         <is>
-          <t>Driving Time (min) to nearest Opioid Treatment Program (OTP)</t>
+          <t>% Tracts within 30-min Drive of Buprenorphine Provider</t>
         </is>
       </c>
       <c r="X112" t="inlineStr"/>
@@ -9083,26 +9063,26 @@
       <c r="K113" t="inlineStr"/>
       <c r="L113" t="inlineStr"/>
       <c r="M113" t="inlineStr"/>
-      <c r="N113" t="inlineStr"/>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O113" t="inlineStr"/>
       <c r="P113" t="inlineStr"/>
       <c r="Q113" t="inlineStr"/>
       <c r="R113" t="inlineStr"/>
-      <c r="S113" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="S113" t="inlineStr"/>
       <c r="T113" t="inlineStr"/>
       <c r="U113" t="inlineStr"/>
       <c r="V113" t="inlineStr">
         <is>
-          <t>OtpAvTmDr2</t>
+          <t>PctMetT</t>
         </is>
       </c>
       <c r="W113" t="inlineStr">
         <is>
-          <t>Average driving time to nearest Opioid Treatment Provider (Otp), with Impedance factor</t>
+          <t>% Tracts within 30-min Drive of Methadone Provider</t>
         </is>
       </c>
       <c r="X113" t="inlineStr"/>
@@ -9147,30 +9127,26 @@
       <c r="K114" t="inlineStr"/>
       <c r="L114" t="inlineStr"/>
       <c r="M114" t="inlineStr"/>
-      <c r="N114" t="inlineStr"/>
-      <c r="O114" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O114" t="inlineStr"/>
       <c r="P114" t="inlineStr"/>
       <c r="Q114" t="inlineStr"/>
       <c r="R114" t="inlineStr"/>
-      <c r="S114" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="S114" t="inlineStr"/>
       <c r="T114" t="inlineStr"/>
       <c r="U114" t="inlineStr"/>
       <c r="V114" t="inlineStr">
         <is>
-          <t>OtpCtTmDr</t>
+          <t>PctNaltT</t>
         </is>
       </c>
       <c r="W114" t="inlineStr">
         <is>
-          <t>Tracts with Opioid Treatment Program (OTP) (30-min drive)</t>
+          <t>% Tracts within 30-min Drive of Naltrexone Provider</t>
         </is>
       </c>
       <c r="X114" t="inlineStr"/>
@@ -9229,12 +9205,12 @@
       <c r="U115" t="inlineStr"/>
       <c r="V115" t="inlineStr">
         <is>
-          <t>OtpCtTmDr2</t>
+          <t>TlBupTmBk</t>
         </is>
       </c>
       <c r="W115" t="inlineStr">
         <is>
-          <t>Count of Tracts within 30-min drive of Opioid Treatment Provider, with Impedance factor</t>
+          <t>Biking time to nearest telehealth buprenorphine provider</t>
         </is>
       </c>
       <c r="X115" t="inlineStr"/>
@@ -9280,11 +9256,7 @@
       <c r="L116" t="inlineStr"/>
       <c r="M116" t="inlineStr"/>
       <c r="N116" t="inlineStr"/>
-      <c r="O116" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="O116" t="inlineStr"/>
       <c r="P116" t="inlineStr"/>
       <c r="Q116" t="inlineStr"/>
       <c r="R116" t="inlineStr"/>
@@ -9297,12 +9269,12 @@
       <c r="U116" t="inlineStr"/>
       <c r="V116" t="inlineStr">
         <is>
-          <t>OtpTmDrP</t>
+          <t>TlBupTmWk</t>
         </is>
       </c>
       <c r="W116" t="inlineStr">
         <is>
-          <t>% Tracts with Opioid Treatment Program (OTP) (30-min drive)</t>
+          <t>Walking time to nearest telehealth buprenorphine provider</t>
         </is>
       </c>
       <c r="X116" t="inlineStr"/>
@@ -9333,7 +9305,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Spatial Access to MOUDs</t>
+          <t>Spatial Access to Mental Health Providers</t>
         </is>
       </c>
       <c r="C117" t="inlineStr"/>
@@ -9347,7 +9319,11 @@
       <c r="K117" t="inlineStr"/>
       <c r="L117" t="inlineStr"/>
       <c r="M117" t="inlineStr"/>
-      <c r="N117" t="inlineStr"/>
+      <c r="N117" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O117" t="inlineStr"/>
       <c r="P117" t="inlineStr"/>
       <c r="Q117" t="inlineStr"/>
@@ -9361,28 +9337,28 @@
       <c r="U117" t="inlineStr"/>
       <c r="V117" t="inlineStr">
         <is>
-          <t>OtpTmDrP2</t>
+          <t>MhAvTmDr</t>
         </is>
       </c>
       <c r="W117" t="inlineStr">
         <is>
-          <t>% Tracts within 30-min drive of Opioid Treatment Provider (Otp), with Impedance factor</t>
+          <t>Driving Time (min) to nearest Mental Health Provider</t>
         </is>
       </c>
       <c r="X117" t="inlineStr"/>
       <c r="Y117" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_MOUDs.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Mental_Health.md</t>
         </is>
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
+          <t>SAMHSA 2020, 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB117" t="inlineStr"/>
@@ -9397,7 +9373,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Spatial Access to MOUDs</t>
+          <t>Spatial Access to Mental Health Providers</t>
         </is>
       </c>
       <c r="C118" t="inlineStr"/>
@@ -9420,33 +9396,37 @@
       <c r="P118" t="inlineStr"/>
       <c r="Q118" t="inlineStr"/>
       <c r="R118" t="inlineStr"/>
-      <c r="S118" t="inlineStr"/>
+      <c r="S118" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T118" t="inlineStr"/>
       <c r="U118" t="inlineStr"/>
       <c r="V118" t="inlineStr">
         <is>
-          <t>PctBupT</t>
+          <t>MhCtTmDr</t>
         </is>
       </c>
       <c r="W118" t="inlineStr">
         <is>
-          <t>% Tracts within 30-min Drive of Buprenorphine Provider</t>
+          <t>Tracts with Mental Health Provider (30-min drive)</t>
         </is>
       </c>
       <c r="X118" t="inlineStr"/>
       <c r="Y118" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_MOUDs.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Mental_Health.md</t>
         </is>
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
+          <t>SAMHSA 2020, 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB118" t="inlineStr"/>
@@ -9461,7 +9441,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Spatial Access to MOUDs</t>
+          <t>Spatial Access to Mental Health Providers</t>
         </is>
       </c>
       <c r="C119" t="inlineStr"/>
@@ -9484,33 +9464,37 @@
       <c r="P119" t="inlineStr"/>
       <c r="Q119" t="inlineStr"/>
       <c r="R119" t="inlineStr"/>
-      <c r="S119" t="inlineStr"/>
+      <c r="S119" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T119" t="inlineStr"/>
       <c r="U119" t="inlineStr"/>
       <c r="V119" t="inlineStr">
         <is>
-          <t>PctMetT</t>
+          <t>MhTmDrP</t>
         </is>
       </c>
       <c r="W119" t="inlineStr">
         <is>
-          <t>% Tracts within 30-min Drive of Methadone Provider</t>
+          <t>% Tracts with Mental Health Provider (30-min drive)</t>
         </is>
       </c>
       <c r="X119" t="inlineStr"/>
       <c r="Y119" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_MOUDs.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Mental_Health.md</t>
         </is>
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
+          <t>SAMHSA 2020, 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB119" t="inlineStr"/>
@@ -9525,7 +9509,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Spatial Access to MOUDs</t>
+          <t>Spatial Access to Pharmacies</t>
         </is>
       </c>
       <c r="C120" t="inlineStr"/>
@@ -9538,43 +9522,47 @@
       <c r="J120" t="inlineStr"/>
       <c r="K120" t="inlineStr"/>
       <c r="L120" t="inlineStr"/>
-      <c r="M120" t="inlineStr"/>
-      <c r="N120" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N120" t="inlineStr"/>
       <c r="O120" t="inlineStr"/>
       <c r="P120" t="inlineStr"/>
       <c r="Q120" t="inlineStr"/>
       <c r="R120" t="inlineStr"/>
-      <c r="S120" t="inlineStr"/>
+      <c r="S120" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T120" t="inlineStr"/>
       <c r="U120" t="inlineStr"/>
       <c r="V120" t="inlineStr">
         <is>
-          <t>PctNaltT</t>
+          <t>RxAvTmDr</t>
         </is>
       </c>
       <c r="W120" t="inlineStr">
         <is>
-          <t>% Tracts within 30-min Drive of Naltrexone Provider</t>
+          <t xml:space="preserve">Avg. Driving Time (min) to nearest Pharmacy </t>
         </is>
       </c>
       <c r="X120" t="inlineStr"/>
       <c r="Y120" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_MOUDs.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Pharmacies.md</t>
         </is>
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
+          <t>InfoGroup 2019; Amazon S3 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
+          <t>InfoGroup, 2019; Amazon S3, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB120" t="inlineStr"/>
@@ -9589,7 +9577,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Spatial Access to MOUDs</t>
+          <t>Spatial Access to Pharmacies</t>
         </is>
       </c>
       <c r="C121" t="inlineStr"/>
@@ -9602,7 +9590,11 @@
       <c r="J121" t="inlineStr"/>
       <c r="K121" t="inlineStr"/>
       <c r="L121" t="inlineStr"/>
-      <c r="M121" t="inlineStr"/>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="N121" t="inlineStr"/>
       <c r="O121" t="inlineStr"/>
       <c r="P121" t="inlineStr"/>
@@ -9617,28 +9609,28 @@
       <c r="U121" t="inlineStr"/>
       <c r="V121" t="inlineStr">
         <is>
-          <t>TlBupTmBk</t>
+          <t>RxCtTmDr</t>
         </is>
       </c>
       <c r="W121" t="inlineStr">
         <is>
-          <t>Biking time to nearest telehealth buprenorphine provider</t>
+          <t>Tracts with Pharmacy (30-min drive)</t>
         </is>
       </c>
       <c r="X121" t="inlineStr"/>
       <c r="Y121" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_MOUDs.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Pharmacies.md</t>
         </is>
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
+          <t>InfoGroup 2019; Amazon S3 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
+          <t>InfoGroup, 2019; Amazon S3, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB121" t="inlineStr"/>
@@ -9653,7 +9645,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Spatial Access to MOUDs</t>
+          <t>Spatial Access to Pharmacies</t>
         </is>
       </c>
       <c r="C122" t="inlineStr"/>
@@ -9666,7 +9658,11 @@
       <c r="J122" t="inlineStr"/>
       <c r="K122" t="inlineStr"/>
       <c r="L122" t="inlineStr"/>
-      <c r="M122" t="inlineStr"/>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="N122" t="inlineStr"/>
       <c r="O122" t="inlineStr"/>
       <c r="P122" t="inlineStr"/>
@@ -9681,28 +9677,28 @@
       <c r="U122" t="inlineStr"/>
       <c r="V122" t="inlineStr">
         <is>
-          <t>TlBupTmWk</t>
+          <t>RxTmDrP</t>
         </is>
       </c>
       <c r="W122" t="inlineStr">
         <is>
-          <t>Walking time to nearest telehealth buprenorphine provider</t>
+          <t>% tracts with Pharmacy (30-min drive)</t>
         </is>
       </c>
       <c r="X122" t="inlineStr"/>
       <c r="Y122" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_MOUDs.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Pharmacies.md</t>
         </is>
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
+          <t>InfoGroup 2019; Amazon S3 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
+          <t>InfoGroup, 2019; Amazon S3, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB122" t="inlineStr"/>
@@ -9717,7 +9713,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Spatial Access to Mental Health Providers</t>
+          <t>Spatial Access to Substance Use Treatment Providers</t>
         </is>
       </c>
       <c r="C123" t="inlineStr"/>
@@ -9731,11 +9727,7 @@
       <c r="K123" t="inlineStr"/>
       <c r="L123" t="inlineStr"/>
       <c r="M123" t="inlineStr"/>
-      <c r="N123" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N123" t="inlineStr"/>
       <c r="O123" t="inlineStr"/>
       <c r="P123" t="inlineStr"/>
       <c r="Q123" t="inlineStr"/>
@@ -9749,28 +9741,28 @@
       <c r="U123" t="inlineStr"/>
       <c r="V123" t="inlineStr">
         <is>
-          <t>MhAvTmDr</t>
+          <t>SutAvTmDr</t>
         </is>
       </c>
       <c r="W123" t="inlineStr">
         <is>
-          <t>Driving Time (min) to nearest Mental Health Provider</t>
+          <t>Driving Time (min) to nearest Substance Use Treatment program</t>
         </is>
       </c>
       <c r="X123" t="inlineStr"/>
       <c r="Y123" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Mental_Health.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_SubstanceUseTreatment.md</t>
         </is>
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>SAMHSA 2020, 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>SAMHSA 2020</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020</t>
         </is>
       </c>
       <c r="AB123" t="inlineStr"/>
@@ -9785,7 +9777,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Spatial Access to Mental Health Providers</t>
+          <t>Spatial Access to Substance Use Treatment Providers</t>
         </is>
       </c>
       <c r="C124" t="inlineStr"/>
@@ -9799,11 +9791,7 @@
       <c r="K124" t="inlineStr"/>
       <c r="L124" t="inlineStr"/>
       <c r="M124" t="inlineStr"/>
-      <c r="N124" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N124" t="inlineStr"/>
       <c r="O124" t="inlineStr"/>
       <c r="P124" t="inlineStr"/>
       <c r="Q124" t="inlineStr"/>
@@ -9817,28 +9805,28 @@
       <c r="U124" t="inlineStr"/>
       <c r="V124" t="inlineStr">
         <is>
-          <t>MhCtTmDr</t>
+          <t>SutAvTmDr2</t>
         </is>
       </c>
       <c r="W124" t="inlineStr">
         <is>
-          <t>Tracts with Mental Health Provider (30-min drive)</t>
+          <t>Average driving time to nearest Substance Use Treatment Provider (Sut), with Impedance factor</t>
         </is>
       </c>
       <c r="X124" t="inlineStr"/>
       <c r="Y124" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Mental_Health.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_SubstanceUseTreatment.md</t>
         </is>
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>SAMHSA 2020, 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>SAMHSA 2020</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020</t>
         </is>
       </c>
       <c r="AB124" t="inlineStr"/>
@@ -9853,7 +9841,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Spatial Access to Mental Health Providers</t>
+          <t>Spatial Access to Substance Use Treatment Providers</t>
         </is>
       </c>
       <c r="C125" t="inlineStr"/>
@@ -9867,11 +9855,7 @@
       <c r="K125" t="inlineStr"/>
       <c r="L125" t="inlineStr"/>
       <c r="M125" t="inlineStr"/>
-      <c r="N125" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N125" t="inlineStr"/>
       <c r="O125" t="inlineStr"/>
       <c r="P125" t="inlineStr"/>
       <c r="Q125" t="inlineStr"/>
@@ -9885,28 +9869,28 @@
       <c r="U125" t="inlineStr"/>
       <c r="V125" t="inlineStr">
         <is>
-          <t>MhTmDrP</t>
+          <t>SutCtTmDr</t>
         </is>
       </c>
       <c r="W125" t="inlineStr">
         <is>
-          <t>% Tracts with Mental Health Provider (30-min drive)</t>
+          <t>Tracts with Substance Use Treatment (SUT) program (30-min drive)</t>
         </is>
       </c>
       <c r="X125" t="inlineStr"/>
       <c r="Y125" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Mental_Health.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_SubstanceUseTreatment.md</t>
         </is>
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>SAMHSA 2020, 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>SAMHSA 2020</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020</t>
         </is>
       </c>
       <c r="AB125" t="inlineStr"/>
@@ -9921,7 +9905,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Spatial Access to Pharmacies</t>
+          <t>Spatial Access to Substance Use Treatment Providers</t>
         </is>
       </c>
       <c r="C126" t="inlineStr"/>
@@ -9934,11 +9918,7 @@
       <c r="J126" t="inlineStr"/>
       <c r="K126" t="inlineStr"/>
       <c r="L126" t="inlineStr"/>
-      <c r="M126" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="M126" t="inlineStr"/>
       <c r="N126" t="inlineStr"/>
       <c r="O126" t="inlineStr"/>
       <c r="P126" t="inlineStr"/>
@@ -9953,28 +9933,28 @@
       <c r="U126" t="inlineStr"/>
       <c r="V126" t="inlineStr">
         <is>
-          <t>RxAvTmDr</t>
+          <t>SutCtTmDr2</t>
         </is>
       </c>
       <c r="W126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Avg. Driving Time (min) to nearest Pharmacy </t>
+          <t>Count of Tracts within 30-min drive of Substance Use Treatment Provider, with Impedance factor</t>
         </is>
       </c>
       <c r="X126" t="inlineStr"/>
       <c r="Y126" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Pharmacies.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_SubstanceUseTreatment.md</t>
         </is>
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>InfoGroup 2019; Amazon S3 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>SAMHSA 2020</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
         <is>
-          <t>InfoGroup, 2019; Amazon S3, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020</t>
         </is>
       </c>
       <c r="AB126" t="inlineStr"/>
@@ -9989,7 +9969,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Spatial Access to Pharmacies</t>
+          <t>Spatial Access to Substance Use Treatment Providers</t>
         </is>
       </c>
       <c r="C127" t="inlineStr"/>
@@ -10002,11 +9982,7 @@
       <c r="J127" t="inlineStr"/>
       <c r="K127" t="inlineStr"/>
       <c r="L127" t="inlineStr"/>
-      <c r="M127" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="M127" t="inlineStr"/>
       <c r="N127" t="inlineStr"/>
       <c r="O127" t="inlineStr"/>
       <c r="P127" t="inlineStr"/>
@@ -10021,28 +9997,28 @@
       <c r="U127" t="inlineStr"/>
       <c r="V127" t="inlineStr">
         <is>
-          <t>RxCtTmDr</t>
+          <t>SutTmDrP</t>
         </is>
       </c>
       <c r="W127" t="inlineStr">
         <is>
-          <t>Tracts with Pharmacy (30-min drive)</t>
+          <t>% tracts with Substance Use Treatment program (30-min drive)</t>
         </is>
       </c>
       <c r="X127" t="inlineStr"/>
       <c r="Y127" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Pharmacies.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_SubstanceUseTreatment.md</t>
         </is>
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>InfoGroup 2019; Amazon S3 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>SAMHSA 2020</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
         <is>
-          <t>InfoGroup, 2019; Amazon S3, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020</t>
         </is>
       </c>
       <c r="AB127" t="inlineStr"/>
@@ -10057,7 +10033,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Spatial Access to Pharmacies</t>
+          <t>Spatial Access to Substance Use Treatment Providers</t>
         </is>
       </c>
       <c r="C128" t="inlineStr"/>
@@ -10070,11 +10046,7 @@
       <c r="J128" t="inlineStr"/>
       <c r="K128" t="inlineStr"/>
       <c r="L128" t="inlineStr"/>
-      <c r="M128" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="M128" t="inlineStr"/>
       <c r="N128" t="inlineStr"/>
       <c r="O128" t="inlineStr"/>
       <c r="P128" t="inlineStr"/>
@@ -10089,28 +10061,28 @@
       <c r="U128" t="inlineStr"/>
       <c r="V128" t="inlineStr">
         <is>
-          <t>RxTmDrP</t>
+          <t>SutTmDrP2</t>
         </is>
       </c>
       <c r="W128" t="inlineStr">
         <is>
-          <t>% tracts with Pharmacy (30-min drive)</t>
+          <t>% Tracts within 30-min drive of Substance Use Treatment Provider (Sut), with Impedance factor</t>
         </is>
       </c>
       <c r="X128" t="inlineStr"/>
       <c r="Y128" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Pharmacies.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_SubstanceUseTreatment.md</t>
         </is>
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>InfoGroup 2019; Amazon S3 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>SAMHSA 2020</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>InfoGroup, 2019; Amazon S3, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020</t>
         </is>
       </c>
       <c r="AB128" t="inlineStr"/>
@@ -10139,21 +10111,21 @@
       <c r="K129" t="inlineStr"/>
       <c r="L129" t="inlineStr"/>
       <c r="M129" t="inlineStr"/>
-      <c r="N129" t="inlineStr"/>
+      <c r="N129" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O129" t="inlineStr"/>
       <c r="P129" t="inlineStr"/>
       <c r="Q129" t="inlineStr"/>
       <c r="R129" t="inlineStr"/>
-      <c r="S129" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="S129" t="inlineStr"/>
       <c r="T129" t="inlineStr"/>
       <c r="U129" t="inlineStr"/>
       <c r="V129" t="inlineStr">
         <is>
-          <t>SutAvTmDr</t>
+          <t>SutpAvTmDr</t>
         </is>
       </c>
       <c r="W129" t="inlineStr">
@@ -10203,26 +10175,26 @@
       <c r="K130" t="inlineStr"/>
       <c r="L130" t="inlineStr"/>
       <c r="M130" t="inlineStr"/>
-      <c r="N130" t="inlineStr"/>
+      <c r="N130" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O130" t="inlineStr"/>
       <c r="P130" t="inlineStr"/>
       <c r="Q130" t="inlineStr"/>
       <c r="R130" t="inlineStr"/>
-      <c r="S130" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="S130" t="inlineStr"/>
       <c r="T130" t="inlineStr"/>
       <c r="U130" t="inlineStr"/>
       <c r="V130" t="inlineStr">
         <is>
-          <t>SutAvTmDr2</t>
+          <t>SutpCtTmDr</t>
         </is>
       </c>
       <c r="W130" t="inlineStr">
         <is>
-          <t>Average driving time to nearest Substance Use Treatment Provider (Sut), with Impedance factor</t>
+          <t>Tracts with Substance Use Treatment (SUT) program (30-min drive)</t>
         </is>
       </c>
       <c r="X130" t="inlineStr"/>
@@ -10267,26 +10239,26 @@
       <c r="K131" t="inlineStr"/>
       <c r="L131" t="inlineStr"/>
       <c r="M131" t="inlineStr"/>
-      <c r="N131" t="inlineStr"/>
+      <c r="N131" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O131" t="inlineStr"/>
       <c r="P131" t="inlineStr"/>
       <c r="Q131" t="inlineStr"/>
       <c r="R131" t="inlineStr"/>
-      <c r="S131" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="S131" t="inlineStr"/>
       <c r="T131" t="inlineStr"/>
       <c r="U131" t="inlineStr"/>
       <c r="V131" t="inlineStr">
         <is>
-          <t>SutCtTmDr</t>
+          <t>SutpTmDrP</t>
         </is>
       </c>
       <c r="W131" t="inlineStr">
         <is>
-          <t>Tracts with Substance Use Treatment (SUT) program (30-min drive)</t>
+          <t>% tracts with Substance Use Treatment program (30-min drive)</t>
         </is>
       </c>
       <c r="X131" t="inlineStr"/>
@@ -10317,7 +10289,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Spatial Access to Substance Use Treatment Providers</t>
+          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
         </is>
       </c>
       <c r="C132" t="inlineStr"/>
@@ -10331,7 +10303,11 @@
       <c r="K132" t="inlineStr"/>
       <c r="L132" t="inlineStr"/>
       <c r="M132" t="inlineStr"/>
-      <c r="N132" t="inlineStr"/>
+      <c r="N132" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O132" t="inlineStr"/>
       <c r="P132" t="inlineStr"/>
       <c r="Q132" t="inlineStr"/>
@@ -10345,28 +10321,28 @@
       <c r="U132" t="inlineStr"/>
       <c r="V132" t="inlineStr">
         <is>
-          <t>SutCtTmDr2</t>
+          <t>FqhcAvTmDr</t>
         </is>
       </c>
       <c r="W132" t="inlineStr">
         <is>
-          <t>Count of Tracts within 30-min drive of Substance Use Treatment Provider, with Impedance factor</t>
+          <t>Average driving time to nearest Federally Qualified Health Center (FQHC)</t>
         </is>
       </c>
       <c r="X132" t="inlineStr"/>
       <c r="Y132" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_SubstanceUseTreatment.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
         </is>
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>SAMHSA 2020</t>
+          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020</t>
+          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB132" t="inlineStr"/>
@@ -10381,7 +10357,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Spatial Access to Substance Use Treatment Providers</t>
+          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
         </is>
       </c>
       <c r="C133" t="inlineStr"/>
@@ -10395,7 +10371,11 @@
       <c r="K133" t="inlineStr"/>
       <c r="L133" t="inlineStr"/>
       <c r="M133" t="inlineStr"/>
-      <c r="N133" t="inlineStr"/>
+      <c r="N133" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O133" t="inlineStr"/>
       <c r="P133" t="inlineStr"/>
       <c r="Q133" t="inlineStr"/>
@@ -10409,28 +10389,28 @@
       <c r="U133" t="inlineStr"/>
       <c r="V133" t="inlineStr">
         <is>
-          <t>SutTmDrP</t>
+          <t>FqhcCtTmDr</t>
         </is>
       </c>
       <c r="W133" t="inlineStr">
         <is>
-          <t>% tracts with Substance Use Treatment program (30-min drive)</t>
+          <t>Count of Tracts within 30-min drive of Federally Qualified Health Center (FQHC)</t>
         </is>
       </c>
       <c r="X133" t="inlineStr"/>
       <c r="Y133" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_SubstanceUseTreatment.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
         </is>
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>SAMHSA 2020</t>
+          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020</t>
+          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB133" t="inlineStr"/>
@@ -10445,7 +10425,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Spatial Access to Substance Use Treatment Providers</t>
+          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
         </is>
       </c>
       <c r="C134" t="inlineStr"/>
@@ -10459,7 +10439,11 @@
       <c r="K134" t="inlineStr"/>
       <c r="L134" t="inlineStr"/>
       <c r="M134" t="inlineStr"/>
-      <c r="N134" t="inlineStr"/>
+      <c r="N134" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O134" t="inlineStr"/>
       <c r="P134" t="inlineStr"/>
       <c r="Q134" t="inlineStr"/>
@@ -10473,28 +10457,28 @@
       <c r="U134" t="inlineStr"/>
       <c r="V134" t="inlineStr">
         <is>
-          <t>SutTmDrP2</t>
+          <t>FqhcTmDrP</t>
         </is>
       </c>
       <c r="W134" t="inlineStr">
         <is>
-          <t>% Tracts within 30-min drive of Substance Use Treatment Provider (Sut), with Impedance factor</t>
+          <t>% Tracts within 30-min drive of Federally Qualified Health Center (FQHC)</t>
         </is>
       </c>
       <c r="X134" t="inlineStr"/>
       <c r="Y134" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_SubstanceUseTreatment.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
         </is>
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>SAMHSA 2020</t>
+          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020</t>
+          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB134" t="inlineStr"/>
@@ -10509,7 +10493,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Spatial Access to Substance Use Treatment Providers</t>
+          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
         </is>
       </c>
       <c r="C135" t="inlineStr"/>
@@ -10521,44 +10505,48 @@
       <c r="I135" t="inlineStr"/>
       <c r="J135" t="inlineStr"/>
       <c r="K135" t="inlineStr"/>
-      <c r="L135" t="inlineStr"/>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="M135" t="inlineStr"/>
-      <c r="N135" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N135" t="inlineStr"/>
       <c r="O135" t="inlineStr"/>
       <c r="P135" t="inlineStr"/>
       <c r="Q135" t="inlineStr"/>
       <c r="R135" t="inlineStr"/>
-      <c r="S135" t="inlineStr"/>
+      <c r="S135" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T135" t="inlineStr"/>
       <c r="U135" t="inlineStr"/>
       <c r="V135" t="inlineStr">
         <is>
-          <t>SutpAvTmDr</t>
+          <t>TotTracts</t>
         </is>
       </c>
       <c r="W135" t="inlineStr">
         <is>
-          <t>Driving Time (min) to nearest Substance Use Treatment program</t>
+          <t>Total Census Tract Count</t>
         </is>
       </c>
       <c r="X135" t="inlineStr"/>
       <c r="Y135" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_SubstanceUseTreatment.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
         </is>
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>SAMHSA 2020</t>
+          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020</t>
+          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB135" t="inlineStr"/>
@@ -10568,12 +10556,12 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Environment</t>
+          <t>Economic</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Spatial Access to Substance Use Treatment Providers</t>
+          <t>Employment Trends</t>
         </is>
       </c>
       <c r="C136" t="inlineStr"/>
@@ -10585,13 +10573,13 @@
       <c r="I136" t="inlineStr"/>
       <c r="J136" t="inlineStr"/>
       <c r="K136" t="inlineStr"/>
-      <c r="L136" t="inlineStr"/>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="M136" t="inlineStr"/>
-      <c r="N136" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N136" t="inlineStr"/>
       <c r="O136" t="inlineStr"/>
       <c r="P136" t="inlineStr"/>
       <c r="Q136" t="inlineStr"/>
@@ -10601,28 +10589,28 @@
       <c r="U136" t="inlineStr"/>
       <c r="V136" t="inlineStr">
         <is>
-          <t>SutpCtTmDr</t>
+          <t>EssnWrkE</t>
         </is>
       </c>
       <c r="W136" t="inlineStr">
         <is>
-          <t>Tracts with Substance Use Treatment (SUT) program (30-min drive)</t>
+          <t>Count of Essential Workers</t>
         </is>
       </c>
       <c r="X136" t="inlineStr"/>
       <c r="Y136" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_SubstanceUseTreatment.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
         </is>
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>SAMHSA 2020</t>
+          <t>ACS 2018, 2023</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020</t>
+          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
         </is>
       </c>
       <c r="AB136" t="inlineStr"/>
@@ -10632,12 +10620,12 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Environment</t>
+          <t>Economic</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Spatial Access to Substance Use Treatment Providers</t>
+          <t>Employment Trends</t>
         </is>
       </c>
       <c r="C137" t="inlineStr"/>
@@ -10649,7 +10637,11 @@
       <c r="I137" t="inlineStr"/>
       <c r="J137" t="inlineStr"/>
       <c r="K137" t="inlineStr"/>
-      <c r="L137" t="inlineStr"/>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="M137" t="inlineStr"/>
       <c r="N137" t="inlineStr">
         <is>
@@ -10658,35 +10650,39 @@
       </c>
       <c r="O137" t="inlineStr"/>
       <c r="P137" t="inlineStr"/>
-      <c r="Q137" t="inlineStr"/>
+      <c r="Q137" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="R137" t="inlineStr"/>
       <c r="S137" t="inlineStr"/>
       <c r="T137" t="inlineStr"/>
       <c r="U137" t="inlineStr"/>
       <c r="V137" t="inlineStr">
         <is>
-          <t>SutpTmDrP</t>
+          <t>EssnWrkP</t>
         </is>
       </c>
       <c r="W137" t="inlineStr">
         <is>
-          <t>% tracts with Substance Use Treatment program (30-min drive)</t>
+          <t>Essential Workers %</t>
         </is>
       </c>
       <c r="X137" t="inlineStr"/>
       <c r="Y137" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_SubstanceUseTreatment.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
         </is>
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>SAMHSA 2020</t>
+          <t>ACS 2018, 2023</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020</t>
+          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
         </is>
       </c>
       <c r="AB137" t="inlineStr"/>
@@ -10696,12 +10692,12 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Environment</t>
+          <t>Economic</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
+          <t>Employment Trends</t>
         </is>
       </c>
       <c r="C138" t="inlineStr"/>
@@ -10713,7 +10709,11 @@
       <c r="I138" t="inlineStr"/>
       <c r="J138" t="inlineStr"/>
       <c r="K138" t="inlineStr"/>
-      <c r="L138" t="inlineStr"/>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="M138" t="inlineStr"/>
       <c r="N138" t="inlineStr">
         <is>
@@ -10722,39 +10722,39 @@
       </c>
       <c r="O138" t="inlineStr"/>
       <c r="P138" t="inlineStr"/>
-      <c r="Q138" t="inlineStr"/>
+      <c r="Q138" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="R138" t="inlineStr"/>
-      <c r="S138" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="S138" t="inlineStr"/>
       <c r="T138" t="inlineStr"/>
       <c r="U138" t="inlineStr"/>
       <c r="V138" t="inlineStr">
         <is>
-          <t>FqhcAvTmDr</t>
+          <t>HghRskP</t>
         </is>
       </c>
       <c r="W138" t="inlineStr">
         <is>
-          <t>Average driving time to nearest Federally Qualified Health Center (FQHC)</t>
+          <t>Employed % - High Risk of Injury</t>
         </is>
       </c>
       <c r="X138" t="inlineStr"/>
       <c r="Y138" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
         </is>
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>ACS 2018, 2023</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
         <is>
-          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
         </is>
       </c>
       <c r="AB138" t="inlineStr"/>
@@ -10764,12 +10764,12 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Environment</t>
+          <t>Economic</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
+          <t>Employment Trends</t>
         </is>
       </c>
       <c r="C139" t="inlineStr"/>
@@ -10781,7 +10781,11 @@
       <c r="I139" t="inlineStr"/>
       <c r="J139" t="inlineStr"/>
       <c r="K139" t="inlineStr"/>
-      <c r="L139" t="inlineStr"/>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="M139" t="inlineStr"/>
       <c r="N139" t="inlineStr">
         <is>
@@ -10790,39 +10794,39 @@
       </c>
       <c r="O139" t="inlineStr"/>
       <c r="P139" t="inlineStr"/>
-      <c r="Q139" t="inlineStr"/>
+      <c r="Q139" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="R139" t="inlineStr"/>
-      <c r="S139" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="S139" t="inlineStr"/>
       <c r="T139" t="inlineStr"/>
       <c r="U139" t="inlineStr"/>
       <c r="V139" t="inlineStr">
         <is>
-          <t>FqhcCtTmDr</t>
+          <t>HltCrP</t>
         </is>
       </c>
       <c r="W139" t="inlineStr">
         <is>
-          <t>Count of Tracts within 30-min drive of Federally Qualified Health Center (FQHC)</t>
+          <t>Employed % - Health Care</t>
         </is>
       </c>
       <c r="X139" t="inlineStr"/>
       <c r="Y139" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
         </is>
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>ACS 2018, 2023</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
         </is>
       </c>
       <c r="AB139" t="inlineStr"/>
@@ -10832,12 +10836,12 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Environment</t>
+          <t>Economic</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
+          <t>Employment Trends</t>
         </is>
       </c>
       <c r="C140" t="inlineStr"/>
@@ -10849,7 +10853,11 @@
       <c r="I140" t="inlineStr"/>
       <c r="J140" t="inlineStr"/>
       <c r="K140" t="inlineStr"/>
-      <c r="L140" t="inlineStr"/>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="M140" t="inlineStr"/>
       <c r="N140" t="inlineStr">
         <is>
@@ -10858,39 +10866,39 @@
       </c>
       <c r="O140" t="inlineStr"/>
       <c r="P140" t="inlineStr"/>
-      <c r="Q140" t="inlineStr"/>
+      <c r="Q140" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="R140" t="inlineStr"/>
-      <c r="S140" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="S140" t="inlineStr"/>
       <c r="T140" t="inlineStr"/>
       <c r="U140" t="inlineStr"/>
       <c r="V140" t="inlineStr">
         <is>
-          <t>FqhcTmDrP</t>
+          <t>RetailP</t>
         </is>
       </c>
       <c r="W140" t="inlineStr">
         <is>
-          <t>% Tracts within 30-min drive of Federally Qualified Health Center (FQHC)</t>
+          <t>Employed % - Retail</t>
         </is>
       </c>
       <c r="X140" t="inlineStr"/>
       <c r="Y140" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
         </is>
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>ACS 2018, 2023</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
         </is>
       </c>
       <c r="AB140" t="inlineStr"/>
@@ -10900,12 +10908,12 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Environment</t>
+          <t>Economic</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
+          <t>Employment Trends</t>
         </is>
       </c>
       <c r="C141" t="inlineStr"/>
@@ -10923,42 +10931,46 @@
         </is>
       </c>
       <c r="M141" t="inlineStr"/>
-      <c r="N141" t="inlineStr"/>
+      <c r="N141" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O141" t="inlineStr"/>
       <c r="P141" t="inlineStr"/>
-      <c r="Q141" t="inlineStr"/>
+      <c r="Q141" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="R141" t="inlineStr"/>
-      <c r="S141" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="S141" t="inlineStr"/>
       <c r="T141" t="inlineStr"/>
       <c r="U141" t="inlineStr"/>
       <c r="V141" t="inlineStr">
         <is>
-          <t>TotTracts</t>
+          <t>TotWrkE</t>
         </is>
       </c>
       <c r="W141" t="inlineStr">
         <is>
-          <t>Total Census Tract Count</t>
+          <t>Count of Working Population</t>
         </is>
       </c>
       <c r="X141" t="inlineStr"/>
       <c r="Y141" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
         </is>
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>ACS 2018, 2023</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
         <is>
-          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
         </is>
       </c>
       <c r="AB141" t="inlineStr"/>
@@ -10973,7 +10985,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Employment Trends</t>
+          <t>Great Recession Foreclosure Rate</t>
         </is>
       </c>
       <c r="C142" t="inlineStr"/>
@@ -11001,28 +11013,28 @@
       <c r="U142" t="inlineStr"/>
       <c r="V142" t="inlineStr">
         <is>
-          <t>EssnWrkE</t>
+          <t>ForDqP</t>
         </is>
       </c>
       <c r="W142" t="inlineStr">
         <is>
-          <t>Count of Essential Workers</t>
+          <t>Foreclosure &amp; Delinquency %</t>
         </is>
       </c>
       <c r="X142" t="inlineStr"/>
       <c r="Y142" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Foreclosure_Rate.md</t>
         </is>
       </c>
       <c r="Z142" t="inlineStr">
         <is>
-          <t>ACS 2018, 2023</t>
+          <t>HUD 2018; ACS 2012, 2018</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
         <is>
-          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
+          <t>U.S. Department of Housing and Urban Development Neighborhood Stabilization Program; American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates</t>
         </is>
       </c>
       <c r="AB142" t="inlineStr"/>
@@ -11037,7 +11049,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Employment Trends</t>
+          <t>Great Recession Foreclosure Rate</t>
         </is>
       </c>
       <c r="C143" t="inlineStr"/>
@@ -11055,46 +11067,38 @@
         </is>
       </c>
       <c r="M143" t="inlineStr"/>
-      <c r="N143" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N143" t="inlineStr"/>
       <c r="O143" t="inlineStr"/>
       <c r="P143" t="inlineStr"/>
-      <c r="Q143" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="Q143" t="inlineStr"/>
       <c r="R143" t="inlineStr"/>
       <c r="S143" t="inlineStr"/>
       <c r="T143" t="inlineStr"/>
       <c r="U143" t="inlineStr"/>
       <c r="V143" t="inlineStr">
         <is>
-          <t>EssnWrkP</t>
+          <t>ForDqTot</t>
         </is>
       </c>
       <c r="W143" t="inlineStr">
         <is>
-          <t>Essential Workers %</t>
+          <t>Foreclosure &amp; Delinquency Count</t>
         </is>
       </c>
       <c r="X143" t="inlineStr"/>
       <c r="Y143" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Foreclosure_Rate.md</t>
         </is>
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>ACS 2018, 2023</t>
+          <t>HUD 2018; ACS 2012, 2018</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
         <is>
-          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
+          <t>U.S. Department of Housing and Urban Development Neighborhood Stabilization Program; American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates</t>
         </is>
       </c>
       <c r="AB143" t="inlineStr"/>
@@ -11109,13 +11113,17 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Employment Trends</t>
+          <t>Great Recession Foreclosure Rate</t>
         </is>
       </c>
       <c r="C144" t="inlineStr"/>
       <c r="D144" t="inlineStr"/>
       <c r="E144" t="inlineStr"/>
-      <c r="F144" t="inlineStr"/>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="G144" t="inlineStr"/>
       <c r="H144" t="inlineStr"/>
       <c r="I144" t="inlineStr"/>
@@ -11145,28 +11153,28 @@
       <c r="U144" t="inlineStr"/>
       <c r="V144" t="inlineStr">
         <is>
-          <t>HghRskP</t>
+          <t>GiniCoeff</t>
         </is>
       </c>
       <c r="W144" t="inlineStr">
         <is>
-          <t>Employed % - High Risk of Injury</t>
+          <t>Income Inequality (Gini Coefficient)</t>
         </is>
       </c>
       <c r="X144" t="inlineStr"/>
       <c r="Y144" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Foreclosure_Rate.md</t>
         </is>
       </c>
       <c r="Z144" t="inlineStr">
         <is>
-          <t>ACS 2018, 2023</t>
+          <t>HUD 2018; ACS 2012, 2018</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
         <is>
-          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
+          <t>U.S. Department of Housing and Urban Development Neighborhood Stabilization Program; American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates</t>
         </is>
       </c>
       <c r="AB144" t="inlineStr"/>
@@ -11181,7 +11189,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Employment Trends</t>
+          <t>Internet Access</t>
         </is>
       </c>
       <c r="C145" t="inlineStr"/>
@@ -11193,52 +11201,44 @@
       <c r="I145" t="inlineStr"/>
       <c r="J145" t="inlineStr"/>
       <c r="K145" t="inlineStr"/>
-      <c r="L145" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="M145" t="inlineStr"/>
-      <c r="N145" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L145" t="inlineStr"/>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N145" t="inlineStr"/>
       <c r="O145" t="inlineStr"/>
       <c r="P145" t="inlineStr"/>
-      <c r="Q145" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="Q145" t="inlineStr"/>
       <c r="R145" t="inlineStr"/>
       <c r="S145" t="inlineStr"/>
       <c r="T145" t="inlineStr"/>
       <c r="U145" t="inlineStr"/>
       <c r="V145" t="inlineStr">
         <is>
-          <t>HltCrP</t>
+          <t>NoIntP</t>
         </is>
       </c>
       <c r="W145" t="inlineStr">
         <is>
-          <t>Employed % - Health Care</t>
+          <t>Households without Internet Access %</t>
         </is>
       </c>
       <c r="X145" t="inlineStr"/>
       <c r="Y145" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Internet_Access.md</t>
         </is>
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>ACS 2018, 2023</t>
+          <t>ACS 2019</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
         <is>
-          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
+          <t>American Community Survey 2015-2019 5-Year Estimate</t>
         </is>
       </c>
       <c r="AB145" t="inlineStr"/>
@@ -11253,13 +11253,17 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Employment Trends</t>
+          <t>Poverty, Income, Gini Coefficient</t>
         </is>
       </c>
       <c r="C146" t="inlineStr"/>
       <c r="D146" t="inlineStr"/>
       <c r="E146" t="inlineStr"/>
-      <c r="F146" t="inlineStr"/>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="G146" t="inlineStr"/>
       <c r="H146" t="inlineStr"/>
       <c r="I146" t="inlineStr"/>
@@ -11289,28 +11293,28 @@
       <c r="U146" t="inlineStr"/>
       <c r="V146" t="inlineStr">
         <is>
-          <t>RetailP</t>
+          <t>MedInc</t>
         </is>
       </c>
       <c r="W146" t="inlineStr">
         <is>
-          <t>Employed % - Retail</t>
+          <t>Median Income</t>
         </is>
       </c>
       <c r="X146" t="inlineStr"/>
       <c r="Y146" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Economic_Characteristics.md</t>
         </is>
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>ACS 2018, 2023</t>
+          <t>ACS 2012, 2018; Social Explorer 2010</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
         <is>
-          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
+          <t>American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates; Social Explorer Historic Census Data on 2010 Geographies</t>
         </is>
       </c>
       <c r="AB146" t="inlineStr"/>
@@ -11325,13 +11329,17 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Employment Trends</t>
+          <t>Poverty, Income, Gini Coefficient</t>
         </is>
       </c>
       <c r="C147" t="inlineStr"/>
       <c r="D147" t="inlineStr"/>
       <c r="E147" t="inlineStr"/>
-      <c r="F147" t="inlineStr"/>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="G147" t="inlineStr"/>
       <c r="H147" t="inlineStr"/>
       <c r="I147" t="inlineStr"/>
@@ -11361,28 +11369,28 @@
       <c r="U147" t="inlineStr"/>
       <c r="V147" t="inlineStr">
         <is>
-          <t>TotWrkE</t>
+          <t>PciE</t>
         </is>
       </c>
       <c r="W147" t="inlineStr">
         <is>
-          <t>Count of Working Population</t>
+          <t>Per Capita Income</t>
         </is>
       </c>
       <c r="X147" t="inlineStr"/>
       <c r="Y147" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Economic_Characteristics.md</t>
         </is>
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>ACS 2018, 2023</t>
+          <t>ACS 2012, 2018; Social Explorer 2010</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
         <is>
-          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
+          <t>American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates; Social Explorer Historic Census Data on 2010 Geographies</t>
         </is>
       </c>
       <c r="AB147" t="inlineStr"/>
@@ -11397,13 +11405,29 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Great Recession Foreclosure Rate</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr"/>
-      <c r="D148" t="inlineStr"/>
-      <c r="E148" t="inlineStr"/>
-      <c r="F148" t="inlineStr"/>
+          <t>Poverty, Income, Gini Coefficient</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="G148" t="inlineStr"/>
       <c r="H148" t="inlineStr"/>
       <c r="I148" t="inlineStr"/>
@@ -11415,38 +11439,50 @@
         </is>
       </c>
       <c r="M148" t="inlineStr"/>
-      <c r="N148" t="inlineStr"/>
+      <c r="N148" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O148" t="inlineStr"/>
       <c r="P148" t="inlineStr"/>
-      <c r="Q148" t="inlineStr"/>
+      <c r="Q148" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="R148" t="inlineStr"/>
       <c r="S148" t="inlineStr"/>
       <c r="T148" t="inlineStr"/>
-      <c r="U148" t="inlineStr"/>
+      <c r="U148" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="V148" t="inlineStr">
         <is>
-          <t>ForDqP</t>
+          <t>PovP</t>
         </is>
       </c>
       <c r="W148" t="inlineStr">
         <is>
-          <t>Foreclosure &amp; Delinquency %</t>
+          <t>Poverty %</t>
         </is>
       </c>
       <c r="X148" t="inlineStr"/>
       <c r="Y148" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Foreclosure_Rate.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Economic_Characteristics.md</t>
         </is>
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>HUD 2018; ACS 2012, 2018</t>
+          <t>ACS 2012, 2018; Social Explorer 2010</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
         <is>
-          <t>U.S. Department of Housing and Urban Development Neighborhood Stabilization Program; American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates</t>
+          <t>American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates; Social Explorer Historic Census Data on 2010 Geographies</t>
         </is>
       </c>
       <c r="AB148" t="inlineStr"/>
@@ -11461,13 +11497,29 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Great Recession Foreclosure Rate</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr"/>
-      <c r="D149" t="inlineStr"/>
-      <c r="E149" t="inlineStr"/>
-      <c r="F149" t="inlineStr"/>
+          <t>Poverty, Income, Gini Coefficient</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="G149" t="inlineStr"/>
       <c r="H149" t="inlineStr"/>
       <c r="I149" t="inlineStr"/>
@@ -11479,38 +11531,50 @@
         </is>
       </c>
       <c r="M149" t="inlineStr"/>
-      <c r="N149" t="inlineStr"/>
+      <c r="N149" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O149" t="inlineStr"/>
       <c r="P149" t="inlineStr"/>
-      <c r="Q149" t="inlineStr"/>
+      <c r="Q149" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="R149" t="inlineStr"/>
       <c r="S149" t="inlineStr"/>
       <c r="T149" t="inlineStr"/>
-      <c r="U149" t="inlineStr"/>
+      <c r="U149" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="V149" t="inlineStr">
         <is>
-          <t>ForDqTot</t>
+          <t>UnempP</t>
         </is>
       </c>
       <c r="W149" t="inlineStr">
         <is>
-          <t>Foreclosure &amp; Delinquency Count</t>
+          <t>Unemployment %</t>
         </is>
       </c>
       <c r="X149" t="inlineStr"/>
       <c r="Y149" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Foreclosure_Rate.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Economic_Characteristics.md</t>
         </is>
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>HUD 2018; ACS 2012, 2018</t>
+          <t>ACS 2012, 2018; Social Explorer 2010</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
         <is>
-          <t>U.S. Department of Housing and Urban Development Neighborhood Stabilization Program; American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates</t>
+          <t>American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates; Social Explorer Historic Census Data on 2010 Geographies</t>
         </is>
       </c>
       <c r="AB149" t="inlineStr"/>
@@ -11520,38 +11584,26 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Great Recession Foreclosure Rate</t>
+          <t>Buprenorphine Policy Proportion</t>
         </is>
       </c>
       <c r="C150" t="inlineStr"/>
       <c r="D150" t="inlineStr"/>
       <c r="E150" t="inlineStr"/>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="F150" t="inlineStr"/>
       <c r="G150" t="inlineStr"/>
       <c r="H150" t="inlineStr"/>
       <c r="I150" t="inlineStr"/>
       <c r="J150" t="inlineStr"/>
       <c r="K150" t="inlineStr"/>
-      <c r="L150" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L150" t="inlineStr"/>
       <c r="M150" t="inlineStr"/>
-      <c r="N150" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N150" t="inlineStr"/>
       <c r="O150" t="inlineStr"/>
       <c r="P150" t="inlineStr"/>
       <c r="Q150" t="inlineStr">
@@ -11559,34 +11611,38 @@
           <t>x</t>
         </is>
       </c>
-      <c r="R150" t="inlineStr"/>
+      <c r="R150" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="S150" t="inlineStr"/>
       <c r="T150" t="inlineStr"/>
       <c r="U150" t="inlineStr"/>
       <c r="V150" t="inlineStr">
         <is>
-          <t>GiniCoeff</t>
+          <t>BupPolP</t>
         </is>
       </c>
       <c r="W150" t="inlineStr">
         <is>
-          <t>Income Inequality (Gini Coefficient)</t>
+          <t>Buprenorphine Policy Proportion</t>
         </is>
       </c>
       <c r="X150" t="inlineStr"/>
       <c r="Y150" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Foreclosure_Rate.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/medicaid_variables_saket/metadata/Bup_Policy_Proportion.md</t>
         </is>
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>HUD 2018; ACS 2012, 2018</t>
+          <t>CPHLR 2025</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
         <is>
-          <t>U.S. Department of Housing and Urban Development Neighborhood Stabilization Program; American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates</t>
+          <t>Center for Public Health Law Research &amp; Vital Strategies</t>
         </is>
       </c>
       <c r="AB150" t="inlineStr"/>
@@ -11596,12 +11652,12 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Internet Access</t>
+          <t>Buprenorphine Policy Proportion</t>
         </is>
       </c>
       <c r="C151" t="inlineStr"/>
@@ -11614,43 +11670,47 @@
       <c r="J151" t="inlineStr"/>
       <c r="K151" t="inlineStr"/>
       <c r="L151" t="inlineStr"/>
-      <c r="M151" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="M151" t="inlineStr"/>
       <c r="N151" t="inlineStr"/>
       <c r="O151" t="inlineStr"/>
       <c r="P151" t="inlineStr"/>
-      <c r="Q151" t="inlineStr"/>
-      <c r="R151" t="inlineStr"/>
+      <c r="Q151" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="R151" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="S151" t="inlineStr"/>
       <c r="T151" t="inlineStr"/>
       <c r="U151" t="inlineStr"/>
       <c r="V151" t="inlineStr">
         <is>
-          <t>NoIntP</t>
+          <t>EdBupPolP</t>
         </is>
       </c>
       <c r="W151" t="inlineStr">
         <is>
-          <t>Households without Internet Access %</t>
+          <t>Entire Data Period Buprenorphine Policy Proportion</t>
         </is>
       </c>
       <c r="X151" t="inlineStr"/>
       <c r="Y151" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Internet_Access.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/medicaid_variables_saket/metadata/Bup_Policy_Proportion.md</t>
         </is>
       </c>
       <c r="Z151" t="inlineStr">
         <is>
-          <t>ACS 2019</t>
+          <t>CPHLR 2025</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
         <is>
-          <t>American Community Survey 2015-2019 5-Year Estimate</t>
+          <t>Center for Public Health Law Research &amp; Vital Strategies</t>
         </is>
       </c>
       <c r="AB151" t="inlineStr"/>
@@ -11660,38 +11720,26 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Poverty, Income, Gini Coefficient</t>
+          <t>Buprenorphine Policy Proportion</t>
         </is>
       </c>
       <c r="C152" t="inlineStr"/>
       <c r="D152" t="inlineStr"/>
       <c r="E152" t="inlineStr"/>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="F152" t="inlineStr"/>
       <c r="G152" t="inlineStr"/>
       <c r="H152" t="inlineStr"/>
       <c r="I152" t="inlineStr"/>
       <c r="J152" t="inlineStr"/>
       <c r="K152" t="inlineStr"/>
-      <c r="L152" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L152" t="inlineStr"/>
       <c r="M152" t="inlineStr"/>
-      <c r="N152" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N152" t="inlineStr"/>
       <c r="O152" t="inlineStr"/>
       <c r="P152" t="inlineStr"/>
       <c r="Q152" t="inlineStr">
@@ -11699,34 +11747,38 @@
           <t>x</t>
         </is>
       </c>
-      <c r="R152" t="inlineStr"/>
+      <c r="R152" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="S152" t="inlineStr"/>
       <c r="T152" t="inlineStr"/>
       <c r="U152" t="inlineStr"/>
       <c r="V152" t="inlineStr">
         <is>
-          <t>MedInc</t>
+          <t>PerImpBupP</t>
         </is>
       </c>
       <c r="W152" t="inlineStr">
         <is>
-          <t>Median Income</t>
+          <t>Periods of Buprenorphine Policy Implementation</t>
         </is>
       </c>
       <c r="X152" t="inlineStr"/>
       <c r="Y152" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Economic_Characteristics.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/medicaid_variables_saket/metadata/Bup_Policy_Proportion.md</t>
         </is>
       </c>
       <c r="Z152" t="inlineStr">
         <is>
-          <t>ACS 2012, 2018; Social Explorer 2010</t>
+          <t>CPHLR 2025</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
         <is>
-          <t>American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates; Social Explorer Historic Census Data on 2010 Geographies</t>
+          <t>Center for Public Health Law Research &amp; Vital Strategies</t>
         </is>
       </c>
       <c r="AB152" t="inlineStr"/>
@@ -11736,73 +11788,73 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Poverty, Income, Gini Coefficient</t>
+          <t>Harm Reduction Policies</t>
         </is>
       </c>
       <c r="C153" t="inlineStr"/>
       <c r="D153" t="inlineStr"/>
       <c r="E153" t="inlineStr"/>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="F153" t="inlineStr"/>
       <c r="G153" t="inlineStr"/>
       <c r="H153" t="inlineStr"/>
       <c r="I153" t="inlineStr"/>
       <c r="J153" t="inlineStr"/>
-      <c r="K153" t="inlineStr"/>
-      <c r="L153" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="M153" t="inlineStr"/>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="L153" t="inlineStr"/>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="N153" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="O153" t="inlineStr"/>
+      <c r="O153" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="P153" t="inlineStr"/>
-      <c r="Q153" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="Q153" t="inlineStr"/>
       <c r="R153" t="inlineStr"/>
       <c r="S153" t="inlineStr"/>
       <c r="T153" t="inlineStr"/>
       <c r="U153" t="inlineStr"/>
       <c r="V153" t="inlineStr">
         <is>
-          <t>PciE</t>
+          <t>AnyGslDt</t>
         </is>
       </c>
       <c r="W153" t="inlineStr">
         <is>
-          <t>Per Capita Income</t>
+          <t>Any Good Samaritan Law (date)</t>
         </is>
       </c>
       <c r="X153" t="inlineStr"/>
       <c r="Y153" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Economic_Characteristics.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Good_Samaritan_Laws.md</t>
         </is>
       </c>
       <c r="Z153" t="inlineStr">
         <is>
-          <t>ACS 2012, 2018; Social Explorer 2010</t>
+          <t>OPTIC 2017, 2019, 2020, 2021</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
         <is>
-          <t>American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates; Social Explorer Historic Census Data on 2010 Geographies</t>
+          <t>RAND-USC Schaeffer Opioid Policy Tools and Information Center, 2017, 2019, 2020, 2021</t>
         </is>
       </c>
       <c r="AB153" t="inlineStr"/>
@@ -11812,89 +11864,73 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Poverty, Income, Gini Coefficient</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="D154" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+          <t>Harm Reduction Policies</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr"/>
+      <c r="D154" t="inlineStr"/>
+      <c r="E154" t="inlineStr"/>
+      <c r="F154" t="inlineStr"/>
       <c r="G154" t="inlineStr"/>
       <c r="H154" t="inlineStr"/>
       <c r="I154" t="inlineStr"/>
       <c r="J154" t="inlineStr"/>
-      <c r="K154" t="inlineStr"/>
-      <c r="L154" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="M154" t="inlineStr"/>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="L154" t="inlineStr"/>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="N154" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="O154" t="inlineStr"/>
+      <c r="O154" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="P154" t="inlineStr"/>
-      <c r="Q154" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="Q154" t="inlineStr"/>
       <c r="R154" t="inlineStr"/>
       <c r="S154" t="inlineStr"/>
       <c r="T154" t="inlineStr"/>
-      <c r="U154" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="U154" t="inlineStr"/>
       <c r="V154" t="inlineStr">
         <is>
-          <t>PovP</t>
+          <t>AnyGslFr</t>
         </is>
       </c>
       <c r="W154" t="inlineStr">
         <is>
-          <t>Poverty %</t>
+          <t>Any Good Samaritan Law (fraction of year in 2018)</t>
         </is>
       </c>
       <c r="X154" t="inlineStr"/>
       <c r="Y154" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Economic_Characteristics.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Good_Samaritan_Laws.md</t>
         </is>
       </c>
       <c r="Z154" t="inlineStr">
         <is>
-          <t>ACS 2012, 2018; Social Explorer 2010</t>
+          <t>OPTIC 2017, 2019, 2020, 2021</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
         <is>
-          <t>American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates; Social Explorer Historic Census Data on 2010 Geographies</t>
+          <t>RAND-USC Schaeffer Opioid Policy Tools and Information Center, 2017, 2019, 2020, 2021</t>
         </is>
       </c>
       <c r="AB154" t="inlineStr"/>
@@ -11904,89 +11940,81 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Poverty, Income, Gini Coefficient</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="D155" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="E155" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="F155" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+          <t>Harm Reduction Policies</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr"/>
+      <c r="D155" t="inlineStr"/>
+      <c r="E155" t="inlineStr"/>
+      <c r="F155" t="inlineStr"/>
       <c r="G155" t="inlineStr"/>
       <c r="H155" t="inlineStr"/>
       <c r="I155" t="inlineStr"/>
       <c r="J155" t="inlineStr"/>
-      <c r="K155" t="inlineStr"/>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="L155" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="M155" t="inlineStr"/>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="N155" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="O155" t="inlineStr"/>
-      <c r="P155" t="inlineStr"/>
-      <c r="Q155" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="O155" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="P155" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Q155" t="inlineStr"/>
       <c r="R155" t="inlineStr"/>
       <c r="S155" t="inlineStr"/>
       <c r="T155" t="inlineStr"/>
-      <c r="U155" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="U155" t="inlineStr"/>
       <c r="V155" t="inlineStr">
         <is>
-          <t>UnempP</t>
+          <t>AnyNalxDt</t>
         </is>
       </c>
       <c r="W155" t="inlineStr">
         <is>
-          <t>Unemployment %</t>
+          <t>Any Naloxone Law (date)</t>
         </is>
       </c>
       <c r="X155" t="inlineStr"/>
       <c r="Y155" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Economic_Characteristics.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Naloxone_Policy.md</t>
         </is>
       </c>
       <c r="Z155" t="inlineStr">
         <is>
-          <t>ACS 2012, 2018; Social Explorer 2010</t>
+          <t>OPTIC 2017-2022</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
         <is>
-          <t>American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates; Social Explorer Historic Census Data on 2010 Geographies</t>
+          <t>RAND-USC Schaeffer Opioid Policy Tools and Information Center, 2017-2022</t>
         </is>
       </c>
       <c r="AB155" t="inlineStr"/>
@@ -12001,7 +12029,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Buprenorphine Policy Proportion</t>
+          <t>Harm Reduction Policies</t>
         </is>
       </c>
       <c r="C156" t="inlineStr"/>
@@ -12012,49 +12040,65 @@
       <c r="H156" t="inlineStr"/>
       <c r="I156" t="inlineStr"/>
       <c r="J156" t="inlineStr"/>
-      <c r="K156" t="inlineStr"/>
-      <c r="L156" t="inlineStr"/>
-      <c r="M156" t="inlineStr"/>
-      <c r="N156" t="inlineStr"/>
-      <c r="O156" t="inlineStr"/>
-      <c r="P156" t="inlineStr"/>
-      <c r="Q156" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="R156" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N156" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O156" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="P156" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Q156" t="inlineStr"/>
+      <c r="R156" t="inlineStr"/>
       <c r="S156" t="inlineStr"/>
       <c r="T156" t="inlineStr"/>
       <c r="U156" t="inlineStr"/>
       <c r="V156" t="inlineStr">
         <is>
-          <t>BupPolP</t>
+          <t>AnyNalxFr</t>
         </is>
       </c>
       <c r="W156" t="inlineStr">
         <is>
-          <t>Buprenorphine Policy Proportion</t>
+          <t>Naloxone Law allowing distribution through a standing or order (fraction of year in 2017)</t>
         </is>
       </c>
       <c r="X156" t="inlineStr"/>
       <c r="Y156" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/medicaid_variables_saket/metadata/Bup_Policy_Proportion.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Naloxone_Policy.md</t>
         </is>
       </c>
       <c r="Z156" t="inlineStr">
         <is>
-          <t>CPHLR 2025</t>
+          <t>OPTIC 2017-2022</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
         <is>
-          <t>Center for Public Health Law Research &amp; Vital Strategies</t>
+          <t>RAND-USC Schaeffer Opioid Policy Tools and Information Center, 2017-2022</t>
         </is>
       </c>
       <c r="AB156" t="inlineStr"/>
@@ -12069,7 +12113,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Buprenorphine Policy Proportion</t>
+          <t>Harm Reduction Policies</t>
         </is>
       </c>
       <c r="C157" t="inlineStr"/>
@@ -12082,47 +12126,43 @@
       <c r="J157" t="inlineStr"/>
       <c r="K157" t="inlineStr"/>
       <c r="L157" t="inlineStr"/>
-      <c r="M157" t="inlineStr"/>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="N157" t="inlineStr"/>
       <c r="O157" t="inlineStr"/>
       <c r="P157" t="inlineStr"/>
-      <c r="Q157" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="R157" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="Q157" t="inlineStr"/>
+      <c r="R157" t="inlineStr"/>
       <c r="S157" t="inlineStr"/>
       <c r="T157" t="inlineStr"/>
       <c r="U157" t="inlineStr"/>
       <c r="V157" t="inlineStr">
         <is>
-          <t>EdBupPolP</t>
+          <t>ExpSsp</t>
         </is>
       </c>
       <c r="W157" t="inlineStr">
         <is>
-          <t>Entire Data Period Buprenorphine Policy Proportion</t>
+          <t>Syringe Service Program (SSP) Authorization Laws</t>
         </is>
       </c>
       <c r="X157" t="inlineStr"/>
       <c r="Y157" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/medicaid_variables_saket/metadata/Bup_Policy_Proportion.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Syringe_Policy.md</t>
         </is>
       </c>
       <c r="Z157" t="inlineStr">
         <is>
-          <t>CPHLR 2025</t>
+          <t>LawAtlas 2019</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
         <is>
-          <t>Center for Public Health Law Research &amp; Vital Strategies</t>
+          <t>Fernández-Viña MH, Prood NE, Herpolsheimer A, Waimberg J, Burris S. State Laws Governing Syringe Services Programs and Participant Syringe Possession, 2014-2019. Public Health Reports. 2020;135:128S-137S. doi:10.1177/0033354920921817</t>
         </is>
       </c>
       <c r="AB157" t="inlineStr"/>
@@ -12137,7 +12177,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Buprenorphine Policy Proportion</t>
+          <t>Harm Reduction Policies</t>
         </is>
       </c>
       <c r="C158" t="inlineStr"/>
@@ -12148,49 +12188,57 @@
       <c r="H158" t="inlineStr"/>
       <c r="I158" t="inlineStr"/>
       <c r="J158" t="inlineStr"/>
-      <c r="K158" t="inlineStr"/>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="L158" t="inlineStr"/>
-      <c r="M158" t="inlineStr"/>
-      <c r="N158" t="inlineStr"/>
-      <c r="O158" t="inlineStr"/>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N158" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O158" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="P158" t="inlineStr"/>
-      <c r="Q158" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="R158" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="Q158" t="inlineStr"/>
+      <c r="R158" t="inlineStr"/>
       <c r="S158" t="inlineStr"/>
       <c r="T158" t="inlineStr"/>
       <c r="U158" t="inlineStr"/>
       <c r="V158" t="inlineStr">
         <is>
-          <t>PerImpBupP</t>
+          <t>GslArrDt</t>
         </is>
       </c>
       <c r="W158" t="inlineStr">
         <is>
-          <t>Periods of Buprenorphine Policy Implementation</t>
+          <t>Good Samaritan Law Protecting Arrest (date)</t>
         </is>
       </c>
       <c r="X158" t="inlineStr"/>
       <c r="Y158" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/medicaid_variables_saket/metadata/Bup_Policy_Proportion.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Good_Samaritan_Laws.md</t>
         </is>
       </c>
       <c r="Z158" t="inlineStr">
         <is>
-          <t>CPHLR 2025</t>
+          <t>OPTIC 2017, 2019, 2020, 2021</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
         <is>
-          <t>Center for Public Health Law Research &amp; Vital Strategies</t>
+          <t>RAND-USC Schaeffer Opioid Policy Tools and Information Center, 2017, 2019, 2020, 2021</t>
         </is>
       </c>
       <c r="AB158" t="inlineStr"/>
@@ -12245,12 +12293,12 @@
       <c r="U159" t="inlineStr"/>
       <c r="V159" t="inlineStr">
         <is>
-          <t>AnyGslDt</t>
+          <t>GslArrFr</t>
         </is>
       </c>
       <c r="W159" t="inlineStr">
         <is>
-          <t>Any Good Samaritan Law (date)</t>
+          <t>Good Samaritan Law Protecting Arrest (fraction of year in 2018)</t>
         </is>
       </c>
       <c r="X159" t="inlineStr"/>
@@ -12297,7 +12345,11 @@
           <t>x</t>
         </is>
       </c>
-      <c r="L160" t="inlineStr"/>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="M160" t="inlineStr">
         <is>
           <t>x</t>
@@ -12313,7 +12365,11 @@
           <t>x</t>
         </is>
       </c>
-      <c r="P160" t="inlineStr"/>
+      <c r="P160" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="Q160" t="inlineStr"/>
       <c r="R160" t="inlineStr"/>
       <c r="S160" t="inlineStr"/>
@@ -12321,28 +12377,28 @@
       <c r="U160" t="inlineStr"/>
       <c r="V160" t="inlineStr">
         <is>
-          <t>AnyGslFr</t>
+          <t>NalxPrStDt</t>
         </is>
       </c>
       <c r="W160" t="inlineStr">
         <is>
-          <t>Any Good Samaritan Law (fraction of year in 2018)</t>
+          <t>Naloxone Law allowing distribution through a standing or order (date)</t>
         </is>
       </c>
       <c r="X160" t="inlineStr"/>
       <c r="Y160" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Good_Samaritan_Laws.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Naloxone_Policy.md</t>
         </is>
       </c>
       <c r="Z160" t="inlineStr">
         <is>
-          <t>OPTIC 2017, 2019, 2020, 2021</t>
+          <t>OPTIC 2017-2022</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
         <is>
-          <t>RAND-USC Schaeffer Opioid Policy Tools and Information Center, 2017, 2019, 2020, 2021</t>
+          <t>RAND-USC Schaeffer Opioid Policy Tools and Information Center, 2017-2022</t>
         </is>
       </c>
       <c r="AB160" t="inlineStr"/>
@@ -12405,12 +12461,12 @@
       <c r="U161" t="inlineStr"/>
       <c r="V161" t="inlineStr">
         <is>
-          <t>AnyNalxDt</t>
+          <t>NalxPrStFr</t>
         </is>
       </c>
       <c r="W161" t="inlineStr">
         <is>
-          <t>Any Naloxone Law (date)</t>
+          <t>Naloxone Law in Effect (fraction of year in 2017)</t>
         </is>
       </c>
       <c r="X161" t="inlineStr"/>
@@ -12489,12 +12545,12 @@
       <c r="U162" t="inlineStr"/>
       <c r="V162" t="inlineStr">
         <is>
-          <t>AnyNalxFr</t>
+          <t>NalxPresDt</t>
         </is>
       </c>
       <c r="W162" t="inlineStr">
         <is>
-          <t>Naloxone Law allowing distribution through a standing or order (fraction of year in 2017)</t>
+          <t>Naloxone Law allowing pharmacists prescriptive authority (date)</t>
         </is>
       </c>
       <c r="X162" t="inlineStr"/>
@@ -12536,16 +12592,36 @@
       <c r="H163" t="inlineStr"/>
       <c r="I163" t="inlineStr"/>
       <c r="J163" t="inlineStr"/>
-      <c r="K163" t="inlineStr"/>
-      <c r="L163" t="inlineStr"/>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="M163" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="N163" t="inlineStr"/>
-      <c r="O163" t="inlineStr"/>
-      <c r="P163" t="inlineStr"/>
+      <c r="N163" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O163" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="P163" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="Q163" t="inlineStr"/>
       <c r="R163" t="inlineStr"/>
       <c r="S163" t="inlineStr"/>
@@ -12553,28 +12629,28 @@
       <c r="U163" t="inlineStr"/>
       <c r="V163" t="inlineStr">
         <is>
-          <t>ExpSsp</t>
+          <t>NalxPresFr</t>
         </is>
       </c>
       <c r="W163" t="inlineStr">
         <is>
-          <t>Syringe Service Program (SSP) Authorization Laws</t>
+          <t>Naloxone Law allowing pharmacists prescriptive authority (fraction of year in 2017)</t>
         </is>
       </c>
       <c r="X163" t="inlineStr"/>
       <c r="Y163" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Syringe_Policy.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Naloxone_Policy.md</t>
         </is>
       </c>
       <c r="Z163" t="inlineStr">
         <is>
-          <t>LawAtlas 2019</t>
+          <t>OPTIC 2017-2022</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
         <is>
-          <t>Fernández-Viña MH, Prood NE, Herpolsheimer A, Waimberg J, Burris S. State Laws Governing Syringe Services Programs and Participant Syringe Possession, 2014-2019. Public Health Reports. 2020;135:128S-137S. doi:10.1177/0033354920921817</t>
+          <t>RAND-USC Schaeffer Opioid Policy Tools and Information Center, 2017-2022</t>
         </is>
       </c>
       <c r="AB163" t="inlineStr"/>
@@ -12600,27 +12676,15 @@
       <c r="H164" t="inlineStr"/>
       <c r="I164" t="inlineStr"/>
       <c r="J164" t="inlineStr"/>
-      <c r="K164" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="K164" t="inlineStr"/>
       <c r="L164" t="inlineStr"/>
       <c r="M164" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="N164" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="O164" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N164" t="inlineStr"/>
+      <c r="O164" t="inlineStr"/>
       <c r="P164" t="inlineStr"/>
       <c r="Q164" t="inlineStr"/>
       <c r="R164" t="inlineStr"/>
@@ -12629,28 +12693,28 @@
       <c r="U164" t="inlineStr"/>
       <c r="V164" t="inlineStr">
         <is>
-          <t>GslArrDt</t>
+          <t>NoLwRmUnc</t>
         </is>
       </c>
       <c r="W164" t="inlineStr">
         <is>
-          <t>Good Samaritan Law Protecting Arrest (date)</t>
+          <t>Laws removing barriers to SSPs</t>
         </is>
       </c>
       <c r="X164" t="inlineStr"/>
       <c r="Y164" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Good_Samaritan_Laws.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Syringe_Policy.md</t>
         </is>
       </c>
       <c r="Z164" t="inlineStr">
         <is>
-          <t>OPTIC 2017, 2019, 2020, 2021</t>
+          <t>LawAtlas 2019</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
         <is>
-          <t>RAND-USC Schaeffer Opioid Policy Tools and Information Center, 2017, 2019, 2020, 2021</t>
+          <t>Fernández-Viña MH, Prood NE, Herpolsheimer A, Waimberg J, Burris S. State Laws Governing Syringe Services Programs and Participant Syringe Possession, 2014-2019. Public Health Reports. 2020;135:128S-137S. doi:10.1177/0033354920921817</t>
         </is>
       </c>
       <c r="AB164" t="inlineStr"/>
@@ -12676,27 +12740,15 @@
       <c r="H165" t="inlineStr"/>
       <c r="I165" t="inlineStr"/>
       <c r="J165" t="inlineStr"/>
-      <c r="K165" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="K165" t="inlineStr"/>
       <c r="L165" t="inlineStr"/>
       <c r="M165" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="N165" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="O165" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N165" t="inlineStr"/>
+      <c r="O165" t="inlineStr"/>
       <c r="P165" t="inlineStr"/>
       <c r="Q165" t="inlineStr"/>
       <c r="R165" t="inlineStr"/>
@@ -12705,28 +12757,28 @@
       <c r="U165" t="inlineStr"/>
       <c r="V165" t="inlineStr">
         <is>
-          <t>GslArrFr</t>
+          <t>NoPrphLw</t>
         </is>
       </c>
       <c r="W165" t="inlineStr">
         <is>
-          <t>Good Samaritan Law Protecting Arrest (fraction of year in 2018)</t>
+          <t>Drug Paraphernalia Laws</t>
         </is>
       </c>
       <c r="X165" t="inlineStr"/>
       <c r="Y165" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Good_Samaritan_Laws.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Syringe_Policy.md</t>
         </is>
       </c>
       <c r="Z165" t="inlineStr">
         <is>
-          <t>OPTIC 2017, 2019, 2020, 2021</t>
+          <t>LawAtlas 2019</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
         <is>
-          <t>RAND-USC Schaeffer Opioid Policy Tools and Information Center, 2017, 2019, 2020, 2021</t>
+          <t>Fernández-Viña MH, Prood NE, Herpolsheimer A, Waimberg J, Burris S. State Laws Governing Syringe Services Programs and Participant Syringe Possession, 2014-2019. Public Health Reports. 2020;135:128S-137S. doi:10.1177/0033354920921817</t>
         </is>
       </c>
       <c r="AB165" t="inlineStr"/>
@@ -12752,36 +12804,16 @@
       <c r="H166" t="inlineStr"/>
       <c r="I166" t="inlineStr"/>
       <c r="J166" t="inlineStr"/>
-      <c r="K166" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="L166" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="K166" t="inlineStr"/>
+      <c r="L166" t="inlineStr"/>
       <c r="M166" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="N166" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="O166" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="P166" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N166" t="inlineStr"/>
+      <c r="O166" t="inlineStr"/>
+      <c r="P166" t="inlineStr"/>
       <c r="Q166" t="inlineStr"/>
       <c r="R166" t="inlineStr"/>
       <c r="S166" t="inlineStr"/>
@@ -12789,28 +12821,28 @@
       <c r="U166" t="inlineStr"/>
       <c r="V166" t="inlineStr">
         <is>
-          <t>NalxPrStDt</t>
+          <t>NtPrFrDsSy</t>
         </is>
       </c>
       <c r="W166" t="inlineStr">
         <is>
-          <t>Naloxone Law allowing distribution through a standing or order (date)</t>
+          <t>Distribution of Syringes Laws</t>
         </is>
       </c>
       <c r="X166" t="inlineStr"/>
       <c r="Y166" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Naloxone_Policy.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Syringe_Policy.md</t>
         </is>
       </c>
       <c r="Z166" t="inlineStr">
         <is>
-          <t>OPTIC 2017-2022</t>
+          <t>LawAtlas 2019</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
         <is>
-          <t>RAND-USC Schaeffer Opioid Policy Tools and Information Center, 2017-2022</t>
+          <t>Fernández-Viña MH, Prood NE, Herpolsheimer A, Waimberg J, Burris S. State Laws Governing Syringe Services Programs and Participant Syringe Possession, 2014-2019. Public Health Reports. 2020;135:128S-137S. doi:10.1177/0033354920921817</t>
         </is>
       </c>
       <c r="AB166" t="inlineStr"/>
@@ -12836,36 +12868,16 @@
       <c r="H167" t="inlineStr"/>
       <c r="I167" t="inlineStr"/>
       <c r="J167" t="inlineStr"/>
-      <c r="K167" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="L167" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="K167" t="inlineStr"/>
+      <c r="L167" t="inlineStr"/>
       <c r="M167" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="N167" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="O167" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="P167" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N167" t="inlineStr"/>
+      <c r="O167" t="inlineStr"/>
+      <c r="P167" t="inlineStr"/>
       <c r="Q167" t="inlineStr"/>
       <c r="R167" t="inlineStr"/>
       <c r="S167" t="inlineStr"/>
@@ -12873,28 +12885,28 @@
       <c r="U167" t="inlineStr"/>
       <c r="V167" t="inlineStr">
         <is>
-          <t>NalxPrStFr</t>
+          <t>PrExcInj</t>
         </is>
       </c>
       <c r="W167" t="inlineStr">
         <is>
-          <t>Naloxone Law in Effect (fraction of year in 2017)</t>
+          <t>Paraphernalia exludes objects used for injecting drugs</t>
         </is>
       </c>
       <c r="X167" t="inlineStr"/>
       <c r="Y167" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Naloxone_Policy.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Syringe_Policy.md</t>
         </is>
       </c>
       <c r="Z167" t="inlineStr">
         <is>
-          <t>OPTIC 2017-2022</t>
+          <t>LawAtlas 2019</t>
         </is>
       </c>
       <c r="AA167" t="inlineStr">
         <is>
-          <t>RAND-USC Schaeffer Opioid Policy Tools and Information Center, 2017-2022</t>
+          <t>Fernández-Viña MH, Prood NE, Herpolsheimer A, Waimberg J, Burris S. State Laws Governing Syringe Services Programs and Participant Syringe Possession, 2014-2019. Public Health Reports. 2020;135:128S-137S. doi:10.1177/0033354920921817</t>
         </is>
       </c>
       <c r="AB167" t="inlineStr"/>
@@ -12920,36 +12932,16 @@
       <c r="H168" t="inlineStr"/>
       <c r="I168" t="inlineStr"/>
       <c r="J168" t="inlineStr"/>
-      <c r="K168" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="L168" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="K168" t="inlineStr"/>
+      <c r="L168" t="inlineStr"/>
       <c r="M168" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="N168" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="O168" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="P168" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N168" t="inlineStr"/>
+      <c r="O168" t="inlineStr"/>
+      <c r="P168" t="inlineStr"/>
       <c r="Q168" t="inlineStr"/>
       <c r="R168" t="inlineStr"/>
       <c r="S168" t="inlineStr"/>
@@ -12957,28 +12949,28 @@
       <c r="U168" t="inlineStr"/>
       <c r="V168" t="inlineStr">
         <is>
-          <t>NalxPresDt</t>
+          <t>PrNtRefInj</t>
         </is>
       </c>
       <c r="W168" t="inlineStr">
         <is>
-          <t>Naloxone Law allowing pharmacists prescriptive authority (date)</t>
+          <t>Paraphernalia does not refer to objects used for injecting drugs</t>
         </is>
       </c>
       <c r="X168" t="inlineStr"/>
       <c r="Y168" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Naloxone_Policy.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Syringe_Policy.md</t>
         </is>
       </c>
       <c r="Z168" t="inlineStr">
         <is>
-          <t>OPTIC 2017-2022</t>
+          <t>LawAtlas 2019</t>
         </is>
       </c>
       <c r="AA168" t="inlineStr">
         <is>
-          <t>RAND-USC Schaeffer Opioid Policy Tools and Information Center, 2017-2022</t>
+          <t>Fernández-Viña MH, Prood NE, Herpolsheimer A, Waimberg J, Burris S. State Laws Governing Syringe Services Programs and Participant Syringe Possession, 2014-2019. Public Health Reports. 2020;135:128S-137S. doi:10.1177/0033354920921817</t>
         </is>
       </c>
       <c r="AB168" t="inlineStr"/>
@@ -12993,7 +12985,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Harm Reduction Policies</t>
+          <t>Marijuana Policies</t>
         </is>
       </c>
       <c r="C169" t="inlineStr"/>
@@ -13034,35 +13026,39 @@
           <t>x</t>
         </is>
       </c>
-      <c r="Q169" t="inlineStr"/>
+      <c r="Q169" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="R169" t="inlineStr"/>
       <c r="S169" t="inlineStr"/>
       <c r="T169" t="inlineStr"/>
       <c r="U169" t="inlineStr"/>
       <c r="V169" t="inlineStr">
         <is>
-          <t>NalxPresFr</t>
+          <t>MdMarijLaw</t>
         </is>
       </c>
       <c r="W169" t="inlineStr">
         <is>
-          <t>Naloxone Law allowing pharmacists prescriptive authority (fraction of year in 2017)</t>
+          <t xml:space="preserve">Laws authorizing medical marijuana use </t>
         </is>
       </c>
       <c r="X169" t="inlineStr"/>
       <c r="Y169" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Naloxone_Policy.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Medical_Marijuana_Laws.md</t>
         </is>
       </c>
       <c r="Z169" t="inlineStr">
         <is>
-          <t>OPTIC 2017-2022</t>
+          <t>PDAPS 2017</t>
         </is>
       </c>
       <c r="AA169" t="inlineStr">
         <is>
-          <t>RAND-USC Schaeffer Opioid Policy Tools and Information Center, 2017-2022</t>
+          <t>Prescription Drug Abuse Policy System, Medical Marijuana Caregiver Rules, 2017</t>
         </is>
       </c>
       <c r="AB169" t="inlineStr"/>
@@ -13077,7 +13073,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Harm Reduction Policies</t>
+          <t>Medicaid Policy Proportion</t>
         </is>
       </c>
       <c r="C170" t="inlineStr"/>
@@ -13099,34 +13095,38 @@
       <c r="O170" t="inlineStr"/>
       <c r="P170" t="inlineStr"/>
       <c r="Q170" t="inlineStr"/>
-      <c r="R170" t="inlineStr"/>
+      <c r="R170" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="S170" t="inlineStr"/>
       <c r="T170" t="inlineStr"/>
       <c r="U170" t="inlineStr"/>
       <c r="V170" t="inlineStr">
         <is>
-          <t>NoLwRmUnc</t>
+          <t>MedPolP5Yr</t>
         </is>
       </c>
       <c r="W170" t="inlineStr">
         <is>
-          <t>Laws removing barriers to SSPs</t>
+          <t>Five-Year Medicaid Expansion Proportion</t>
         </is>
       </c>
       <c r="X170" t="inlineStr"/>
       <c r="Y170" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Syringe_Policy.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/medicaid_variables_saket/metadata/Medicaid_Policy_Proportion.md</t>
         </is>
       </c>
       <c r="Z170" t="inlineStr">
         <is>
-          <t>LawAtlas 2019</t>
+          <t>KFF 2025</t>
         </is>
       </c>
       <c r="AA170" t="inlineStr">
         <is>
-          <t>Fernández-Viña MH, Prood NE, Herpolsheimer A, Waimberg J, Burris S. State Laws Governing Syringe Services Programs and Participant Syringe Possession, 2014-2019. Public Health Reports. 2020;135:128S-137S. doi:10.1177/0033354920921817</t>
+          <t>KFF (Status of State Action on Medicaid Expansion Decision) 2025</t>
         </is>
       </c>
       <c r="AB170" t="inlineStr"/>
@@ -13141,7 +13141,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Harm Reduction Policies</t>
+          <t>Medicaid Policy Proportion</t>
         </is>
       </c>
       <c r="C171" t="inlineStr"/>
@@ -13149,48 +13149,88 @@
       <c r="E171" t="inlineStr"/>
       <c r="F171" t="inlineStr"/>
       <c r="G171" t="inlineStr"/>
-      <c r="H171" t="inlineStr"/>
-      <c r="I171" t="inlineStr"/>
-      <c r="J171" t="inlineStr"/>
-      <c r="K171" t="inlineStr"/>
-      <c r="L171" t="inlineStr"/>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="L171" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="M171" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="N171" t="inlineStr"/>
-      <c r="O171" t="inlineStr"/>
-      <c r="P171" t="inlineStr"/>
-      <c r="Q171" t="inlineStr"/>
-      <c r="R171" t="inlineStr"/>
+      <c r="N171" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O171" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="P171" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Q171" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="R171" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="S171" t="inlineStr"/>
       <c r="T171" t="inlineStr"/>
       <c r="U171" t="inlineStr"/>
       <c r="V171" t="inlineStr">
         <is>
-          <t>NoPrphLw</t>
+          <t>MedPolProp</t>
         </is>
       </c>
       <c r="W171" t="inlineStr">
         <is>
-          <t>Drug Paraphernalia Laws</t>
+          <t>Medicaid Expansion Proportion</t>
         </is>
       </c>
       <c r="X171" t="inlineStr"/>
       <c r="Y171" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Syringe_Policy.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/medicaid_variables_saket/metadata/Medicaid_Policy_Proportion.md</t>
         </is>
       </c>
       <c r="Z171" t="inlineStr">
         <is>
-          <t>LawAtlas 2019</t>
+          <t>KFF 2025</t>
         </is>
       </c>
       <c r="AA171" t="inlineStr">
         <is>
-          <t>Fernández-Viña MH, Prood NE, Herpolsheimer A, Waimberg J, Burris S. State Laws Governing Syringe Services Programs and Participant Syringe Possession, 2014-2019. Public Health Reports. 2020;135:128S-137S. doi:10.1177/0033354920921817</t>
+          <t>KFF (Status of State Action on Medicaid Expansion Decision) 2025</t>
         </is>
       </c>
       <c r="AB171" t="inlineStr"/>
@@ -13205,7 +13245,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Harm Reduction Policies</t>
+          <t>Prescription Drug Monitoring Programs (PDMP)</t>
         </is>
       </c>
       <c r="C172" t="inlineStr"/>
@@ -13216,45 +13256,69 @@
       <c r="H172" t="inlineStr"/>
       <c r="I172" t="inlineStr"/>
       <c r="J172" t="inlineStr"/>
-      <c r="K172" t="inlineStr"/>
-      <c r="L172" t="inlineStr"/>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="L172" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="M172" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="N172" t="inlineStr"/>
-      <c r="O172" t="inlineStr"/>
-      <c r="P172" t="inlineStr"/>
-      <c r="Q172" t="inlineStr"/>
+      <c r="N172" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O172" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="P172" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Q172" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="R172" t="inlineStr"/>
       <c r="S172" t="inlineStr"/>
       <c r="T172" t="inlineStr"/>
       <c r="U172" t="inlineStr"/>
       <c r="V172" t="inlineStr">
         <is>
-          <t>NtPrFrDsSy</t>
+          <t>AnyPdmpDt</t>
         </is>
       </c>
       <c r="W172" t="inlineStr">
         <is>
-          <t>Distribution of Syringes Laws</t>
+          <t>Any PDMP start date</t>
         </is>
       </c>
       <c r="X172" t="inlineStr"/>
       <c r="Y172" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Syringe_Policy.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/PDMP_Presence.md</t>
         </is>
       </c>
       <c r="Z172" t="inlineStr">
         <is>
-          <t>LawAtlas 2019</t>
+          <t>OPTIC 2017-2022</t>
         </is>
       </c>
       <c r="AA172" t="inlineStr">
         <is>
-          <t>Fernández-Viña MH, Prood NE, Herpolsheimer A, Waimberg J, Burris S. State Laws Governing Syringe Services Programs and Participant Syringe Possession, 2014-2019. Public Health Reports. 2020;135:128S-137S. doi:10.1177/0033354920921817</t>
+          <t>RAND-USC Schaeffer Opioid Policy Tools and Information Center, 2017-2022</t>
         </is>
       </c>
       <c r="AB172" t="inlineStr"/>
@@ -13269,7 +13333,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Harm Reduction Policies</t>
+          <t>Prescription Drug Monitoring Programs (PDMP)</t>
         </is>
       </c>
       <c r="C173" t="inlineStr"/>
@@ -13280,45 +13344,69 @@
       <c r="H173" t="inlineStr"/>
       <c r="I173" t="inlineStr"/>
       <c r="J173" t="inlineStr"/>
-      <c r="K173" t="inlineStr"/>
-      <c r="L173" t="inlineStr"/>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="L173" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="M173" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="N173" t="inlineStr"/>
-      <c r="O173" t="inlineStr"/>
-      <c r="P173" t="inlineStr"/>
-      <c r="Q173" t="inlineStr"/>
+      <c r="N173" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O173" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="P173" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Q173" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="R173" t="inlineStr"/>
       <c r="S173" t="inlineStr"/>
       <c r="T173" t="inlineStr"/>
       <c r="U173" t="inlineStr"/>
       <c r="V173" t="inlineStr">
         <is>
-          <t>PrExcInj</t>
+          <t>AnyPdmpFr</t>
         </is>
       </c>
       <c r="W173" t="inlineStr">
         <is>
-          <t>Paraphernalia exludes objects used for injecting drugs</t>
+          <t>Any PDMP (fraction of year in 2017)</t>
         </is>
       </c>
       <c r="X173" t="inlineStr"/>
       <c r="Y173" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Syringe_Policy.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/PDMP_Presence.md</t>
         </is>
       </c>
       <c r="Z173" t="inlineStr">
         <is>
-          <t>LawAtlas 2019</t>
+          <t>OPTIC 2017-2022</t>
         </is>
       </c>
       <c r="AA173" t="inlineStr">
         <is>
-          <t>Fernández-Viña MH, Prood NE, Herpolsheimer A, Waimberg J, Burris S. State Laws Governing Syringe Services Programs and Participant Syringe Possession, 2014-2019. Public Health Reports. 2020;135:128S-137S. doi:10.1177/0033354920921817</t>
+          <t>RAND-USC Schaeffer Opioid Policy Tools and Information Center, 2017-2022</t>
         </is>
       </c>
       <c r="AB173" t="inlineStr"/>
@@ -13333,7 +13421,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Harm Reduction Policies</t>
+          <t>Prescription Drug Monitoring Programs (PDMP)</t>
         </is>
       </c>
       <c r="C174" t="inlineStr"/>
@@ -13344,45 +13432,69 @@
       <c r="H174" t="inlineStr"/>
       <c r="I174" t="inlineStr"/>
       <c r="J174" t="inlineStr"/>
-      <c r="K174" t="inlineStr"/>
-      <c r="L174" t="inlineStr"/>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="L174" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="M174" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="N174" t="inlineStr"/>
-      <c r="O174" t="inlineStr"/>
-      <c r="P174" t="inlineStr"/>
-      <c r="Q174" t="inlineStr"/>
+      <c r="N174" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O174" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="P174" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Q174" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="R174" t="inlineStr"/>
       <c r="S174" t="inlineStr"/>
       <c r="T174" t="inlineStr"/>
       <c r="U174" t="inlineStr"/>
       <c r="V174" t="inlineStr">
         <is>
-          <t>PrNtRefInj</t>
+          <t>AnyPdmphDt</t>
         </is>
       </c>
       <c r="W174" t="inlineStr">
         <is>
-          <t>Paraphernalia does not refer to objects used for injecting drugs</t>
+          <t>Any Horowitz PDMP start date</t>
         </is>
       </c>
       <c r="X174" t="inlineStr"/>
       <c r="Y174" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Syringe_Policy.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/PDMP_Presence.md</t>
         </is>
       </c>
       <c r="Z174" t="inlineStr">
         <is>
-          <t>LawAtlas 2019</t>
+          <t>OPTIC 2017-2022</t>
         </is>
       </c>
       <c r="AA174" t="inlineStr">
         <is>
-          <t>Fernández-Viña MH, Prood NE, Herpolsheimer A, Waimberg J, Burris S. State Laws Governing Syringe Services Programs and Participant Syringe Possession, 2014-2019. Public Health Reports. 2020;135:128S-137S. doi:10.1177/0033354920921817</t>
+          <t>RAND-USC Schaeffer Opioid Policy Tools and Information Center, 2017-2022</t>
         </is>
       </c>
       <c r="AB174" t="inlineStr"/>
@@ -13397,7 +13509,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Marijuana Policies</t>
+          <t>Prescription Drug Monitoring Programs (PDMP)</t>
         </is>
       </c>
       <c r="C175" t="inlineStr"/>
@@ -13449,28 +13561,28 @@
       <c r="U175" t="inlineStr"/>
       <c r="V175" t="inlineStr">
         <is>
-          <t>MdMarijLaw</t>
+          <t>AnyPdmphFr</t>
         </is>
       </c>
       <c r="W175" t="inlineStr">
         <is>
-          <t xml:space="preserve">Laws authorizing medical marijuana use </t>
+          <t>Any Horowitz PDMP (fraction of year in 2017)</t>
         </is>
       </c>
       <c r="X175" t="inlineStr"/>
       <c r="Y175" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Medical_Marijuana_Laws.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/PDMP_Presence.md</t>
         </is>
       </c>
       <c r="Z175" t="inlineStr">
         <is>
-          <t>PDAPS 2017</t>
+          <t>OPTIC 2017-2022</t>
         </is>
       </c>
       <c r="AA175" t="inlineStr">
         <is>
-          <t>Prescription Drug Abuse Policy System, Medical Marijuana Caregiver Rules, 2017</t>
+          <t>RAND-USC Schaeffer Opioid Policy Tools and Information Center, 2017-2022</t>
         </is>
       </c>
       <c r="AB175" t="inlineStr"/>
@@ -13485,7 +13597,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Medicaid Policy Proportion</t>
+          <t>Prescription Drug Monitoring Programs (PDMP)</t>
         </is>
       </c>
       <c r="C176" t="inlineStr"/>
@@ -13496,49 +13608,69 @@
       <c r="H176" t="inlineStr"/>
       <c r="I176" t="inlineStr"/>
       <c r="J176" t="inlineStr"/>
-      <c r="K176" t="inlineStr"/>
-      <c r="L176" t="inlineStr"/>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="L176" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="M176" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="N176" t="inlineStr"/>
-      <c r="O176" t="inlineStr"/>
-      <c r="P176" t="inlineStr"/>
-      <c r="Q176" t="inlineStr"/>
-      <c r="R176" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N176" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O176" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="P176" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Q176" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="R176" t="inlineStr"/>
       <c r="S176" t="inlineStr"/>
       <c r="T176" t="inlineStr"/>
       <c r="U176" t="inlineStr"/>
       <c r="V176" t="inlineStr">
         <is>
-          <t>MedPolP5Yr</t>
+          <t>ElcPdmpDt</t>
         </is>
       </c>
       <c r="W176" t="inlineStr">
         <is>
-          <t>Five-Year Medicaid Expansion Proportion</t>
+          <t>Electronic PDMP start date</t>
         </is>
       </c>
       <c r="X176" t="inlineStr"/>
       <c r="Y176" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/medicaid_variables_saket/metadata/Medicaid_Policy_Proportion.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/PDMP_Presence.md</t>
         </is>
       </c>
       <c r="Z176" t="inlineStr">
         <is>
-          <t>KFF 2025</t>
+          <t>OPTIC 2017-2022</t>
         </is>
       </c>
       <c r="AA176" t="inlineStr">
         <is>
-          <t>KFF (Status of State Action on Medicaid Expansion Decision) 2025</t>
+          <t>RAND-USC Schaeffer Opioid Policy Tools and Information Center, 2017-2022</t>
         </is>
       </c>
       <c r="AB176" t="inlineStr"/>
@@ -13553,7 +13685,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Medicaid Policy Proportion</t>
+          <t>Prescription Drug Monitoring Programs (PDMP)</t>
         </is>
       </c>
       <c r="C177" t="inlineStr"/>
@@ -13561,21 +13693,9 @@
       <c r="E177" t="inlineStr"/>
       <c r="F177" t="inlineStr"/>
       <c r="G177" t="inlineStr"/>
-      <c r="H177" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="I177" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="J177" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="H177" t="inlineStr"/>
+      <c r="I177" t="inlineStr"/>
+      <c r="J177" t="inlineStr"/>
       <c r="K177" t="inlineStr">
         <is>
           <t>x</t>
@@ -13611,38 +13731,34 @@
           <t>x</t>
         </is>
       </c>
-      <c r="R177" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="R177" t="inlineStr"/>
       <c r="S177" t="inlineStr"/>
       <c r="T177" t="inlineStr"/>
       <c r="U177" t="inlineStr"/>
       <c r="V177" t="inlineStr">
         <is>
-          <t>MedPolProp</t>
+          <t>ElcPdmpFr</t>
         </is>
       </c>
       <c r="W177" t="inlineStr">
         <is>
-          <t>Medicaid Expansion Proportion</t>
+          <t>Electronic PDMP (fraction of year in 2017)</t>
         </is>
       </c>
       <c r="X177" t="inlineStr"/>
       <c r="Y177" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/medicaid_variables_saket/metadata/Medicaid_Policy_Proportion.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/PDMP_Presence.md</t>
         </is>
       </c>
       <c r="Z177" t="inlineStr">
         <is>
-          <t>KFF 2025</t>
+          <t>OPTIC 2017-2022</t>
         </is>
       </c>
       <c r="AA177" t="inlineStr">
         <is>
-          <t>KFF (Status of State Action on Medicaid Expansion Decision) 2025</t>
+          <t>RAND-USC Schaeffer Opioid Policy Tools and Information Center, 2017-2022</t>
         </is>
       </c>
       <c r="AB177" t="inlineStr"/>
@@ -13709,12 +13825,12 @@
       <c r="U178" t="inlineStr"/>
       <c r="V178" t="inlineStr">
         <is>
-          <t>AnyPdmpDt</t>
+          <t>MsAcPdmpDt</t>
         </is>
       </c>
       <c r="W178" t="inlineStr">
         <is>
-          <t>Any PDMP start date</t>
+          <t>Must-Access PDMP start date</t>
         </is>
       </c>
       <c r="X178" t="inlineStr"/>
@@ -13797,12 +13913,12 @@
       <c r="U179" t="inlineStr"/>
       <c r="V179" t="inlineStr">
         <is>
-          <t>AnyPdmpFr</t>
+          <t>MsAcPdmpFr</t>
         </is>
       </c>
       <c r="W179" t="inlineStr">
         <is>
-          <t>Any PDMP (fraction of year in 2017)</t>
+          <t>Must-Access PDMP (fraction of year in 2017)</t>
         </is>
       </c>
       <c r="X179" t="inlineStr"/>
@@ -13885,12 +14001,12 @@
       <c r="U180" t="inlineStr"/>
       <c r="V180" t="inlineStr">
         <is>
-          <t>AnyPdmphDt</t>
+          <t>OpPdmpDt</t>
         </is>
       </c>
       <c r="W180" t="inlineStr">
         <is>
-          <t>Any Horowitz PDMP start date</t>
+          <t>Operational PDMP start date</t>
         </is>
       </c>
       <c r="X180" t="inlineStr"/>
@@ -13973,12 +14089,12 @@
       <c r="U181" t="inlineStr"/>
       <c r="V181" t="inlineStr">
         <is>
-          <t>AnyPdmphFr</t>
+          <t>OpPdmpFr</t>
         </is>
       </c>
       <c r="W181" t="inlineStr">
         <is>
-          <t>Any Horowitz PDMP (fraction of year in 2017)</t>
+          <t>Operational PDMP (fraction of year in 2017)</t>
         </is>
       </c>
       <c r="X181" t="inlineStr"/>
@@ -14009,7 +14125,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Prescription Drug Monitoring Programs (PDMP)</t>
+          <t>State &amp; Local Government Expenditures</t>
         </is>
       </c>
       <c r="C182" t="inlineStr"/>
@@ -14020,16 +14136,8 @@
       <c r="H182" t="inlineStr"/>
       <c r="I182" t="inlineStr"/>
       <c r="J182" t="inlineStr"/>
-      <c r="K182" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="L182" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="K182" t="inlineStr"/>
+      <c r="L182" t="inlineStr"/>
       <c r="M182" t="inlineStr">
         <is>
           <t>x</t>
@@ -14050,39 +14158,35 @@
           <t>x</t>
         </is>
       </c>
-      <c r="Q182" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="Q182" t="inlineStr"/>
       <c r="R182" t="inlineStr"/>
       <c r="S182" t="inlineStr"/>
       <c r="T182" t="inlineStr"/>
       <c r="U182" t="inlineStr"/>
       <c r="V182" t="inlineStr">
         <is>
-          <t>ElcPdmpDt</t>
+          <t>CrrctExp</t>
         </is>
       </c>
       <c r="W182" t="inlineStr">
         <is>
-          <t>Electronic PDMP start date</t>
+          <t>Corrections expenditures</t>
         </is>
       </c>
       <c r="X182" t="inlineStr"/>
       <c r="Y182" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/PDMP_Presence.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Public_Expenditures.md</t>
         </is>
       </c>
       <c r="Z182" t="inlineStr">
         <is>
-          <t>OPTIC 2017-2022</t>
+          <t>Survey of State and Local Government Finances 2018-2022</t>
         </is>
       </c>
       <c r="AA182" t="inlineStr">
         <is>
-          <t>RAND-USC Schaeffer Opioid Policy Tools and Information Center, 2017-2022</t>
+          <t>U.S. Census Bureau Annual Survey of State and Local Government Finances via Urban Institute &amp; Tax Policy Center's State and Local Finance Data Finder</t>
         </is>
       </c>
       <c r="AB182" t="inlineStr"/>
@@ -14097,7 +14201,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Prescription Drug Monitoring Programs (PDMP)</t>
+          <t>State &amp; Local Government Expenditures</t>
         </is>
       </c>
       <c r="C183" t="inlineStr"/>
@@ -14108,36 +14212,16 @@
       <c r="H183" t="inlineStr"/>
       <c r="I183" t="inlineStr"/>
       <c r="J183" t="inlineStr"/>
-      <c r="K183" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="K183" t="inlineStr"/>
       <c r="L183" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="M183" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="N183" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="O183" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="P183" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="M183" t="inlineStr"/>
+      <c r="N183" t="inlineStr"/>
+      <c r="O183" t="inlineStr"/>
+      <c r="P183" t="inlineStr"/>
       <c r="Q183" t="inlineStr">
         <is>
           <t>x</t>
@@ -14149,28 +14233,28 @@
       <c r="U183" t="inlineStr"/>
       <c r="V183" t="inlineStr">
         <is>
-          <t>ElcPdmpFr</t>
+          <t>ExpnFedExp</t>
         </is>
       </c>
       <c r="W183" t="inlineStr">
         <is>
-          <t>Electronic PDMP (fraction of year in 2017)</t>
+          <t>Expansion Medicaid Federal Spending</t>
         </is>
       </c>
       <c r="X183" t="inlineStr"/>
       <c r="Y183" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/PDMP_Presence.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Medical_Expenditures.md</t>
         </is>
       </c>
       <c r="Z183" t="inlineStr">
         <is>
-          <t>OPTIC 2017-2022</t>
+          <t>KFF 2018, 2019</t>
         </is>
       </c>
       <c r="AA183" t="inlineStr">
         <is>
-          <t>RAND-USC Schaeffer Opioid Policy Tools and Information Center, 2017-2022</t>
+          <t>Kaiser Family Foundation,  2018, 2019</t>
         </is>
       </c>
       <c r="AB183" t="inlineStr"/>
@@ -14185,7 +14269,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Prescription Drug Monitoring Programs (PDMP)</t>
+          <t>State &amp; Local Government Expenditures</t>
         </is>
       </c>
       <c r="C184" t="inlineStr"/>
@@ -14196,36 +14280,16 @@
       <c r="H184" t="inlineStr"/>
       <c r="I184" t="inlineStr"/>
       <c r="J184" t="inlineStr"/>
-      <c r="K184" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="K184" t="inlineStr"/>
       <c r="L184" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="M184" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="N184" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="O184" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="P184" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="M184" t="inlineStr"/>
+      <c r="N184" t="inlineStr"/>
+      <c r="O184" t="inlineStr"/>
+      <c r="P184" t="inlineStr"/>
       <c r="Q184" t="inlineStr">
         <is>
           <t>x</t>
@@ -14237,28 +14301,28 @@
       <c r="U184" t="inlineStr"/>
       <c r="V184" t="inlineStr">
         <is>
-          <t>MsAcPdmpDt</t>
+          <t>ExpnSttExp</t>
         </is>
       </c>
       <c r="W184" t="inlineStr">
         <is>
-          <t>Must-Access PDMP start date</t>
+          <t>Expansion Medicaid State Spending</t>
         </is>
       </c>
       <c r="X184" t="inlineStr"/>
       <c r="Y184" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/PDMP_Presence.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Medical_Expenditures.md</t>
         </is>
       </c>
       <c r="Z184" t="inlineStr">
         <is>
-          <t>OPTIC 2017-2022</t>
+          <t>KFF 2018, 2019</t>
         </is>
       </c>
       <c r="AA184" t="inlineStr">
         <is>
-          <t>RAND-USC Schaeffer Opioid Policy Tools and Information Center, 2017-2022</t>
+          <t>Kaiser Family Foundation,  2018, 2019</t>
         </is>
       </c>
       <c r="AB184" t="inlineStr"/>
@@ -14273,7 +14337,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Prescription Drug Monitoring Programs (PDMP)</t>
+          <t>State &amp; Local Government Expenditures</t>
         </is>
       </c>
       <c r="C185" t="inlineStr"/>
@@ -14284,16 +14348,8 @@
       <c r="H185" t="inlineStr"/>
       <c r="I185" t="inlineStr"/>
       <c r="J185" t="inlineStr"/>
-      <c r="K185" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="L185" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="K185" t="inlineStr"/>
+      <c r="L185" t="inlineStr"/>
       <c r="M185" t="inlineStr">
         <is>
           <t>x</t>
@@ -14314,39 +14370,35 @@
           <t>x</t>
         </is>
       </c>
-      <c r="Q185" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="Q185" t="inlineStr"/>
       <c r="R185" t="inlineStr"/>
       <c r="S185" t="inlineStr"/>
       <c r="T185" t="inlineStr"/>
       <c r="U185" t="inlineStr"/>
       <c r="V185" t="inlineStr">
         <is>
-          <t>MsAcPdmpFr</t>
+          <t>HlthExp</t>
         </is>
       </c>
       <c r="W185" t="inlineStr">
         <is>
-          <t>Must-Access PDMP (fraction of year in 2017)</t>
+          <t>Public health expenditures</t>
         </is>
       </c>
       <c r="X185" t="inlineStr"/>
       <c r="Y185" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/PDMP_Presence.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Public_Expenditures.md</t>
         </is>
       </c>
       <c r="Z185" t="inlineStr">
         <is>
-          <t>OPTIC 2017-2022</t>
+          <t>Survey of State and Local Government Finances 2018-2022</t>
         </is>
       </c>
       <c r="AA185" t="inlineStr">
         <is>
-          <t>RAND-USC Schaeffer Opioid Policy Tools and Information Center, 2017-2022</t>
+          <t>U.S. Census Bureau Annual Survey of State and Local Government Finances via Urban Institute &amp; Tax Policy Center's State and Local Finance Data Finder</t>
         </is>
       </c>
       <c r="AB185" t="inlineStr"/>
@@ -14361,7 +14413,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Prescription Drug Monitoring Programs (PDMP)</t>
+          <t>State &amp; Local Government Expenditures</t>
         </is>
       </c>
       <c r="C186" t="inlineStr"/>
@@ -14372,11 +14424,7 @@
       <c r="H186" t="inlineStr"/>
       <c r="I186" t="inlineStr"/>
       <c r="J186" t="inlineStr"/>
-      <c r="K186" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="K186" t="inlineStr"/>
       <c r="L186" t="inlineStr">
         <is>
           <t>x</t>
@@ -14387,21 +14435,9 @@
           <t>x</t>
         </is>
       </c>
-      <c r="N186" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="O186" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="P186" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N186" t="inlineStr"/>
+      <c r="O186" t="inlineStr"/>
+      <c r="P186" t="inlineStr"/>
       <c r="Q186" t="inlineStr">
         <is>
           <t>x</t>
@@ -14413,28 +14449,28 @@
       <c r="U186" t="inlineStr"/>
       <c r="V186" t="inlineStr">
         <is>
-          <t>OpPdmpDt</t>
+          <t>MedcdExp</t>
         </is>
       </c>
       <c r="W186" t="inlineStr">
         <is>
-          <t>Operational PDMP start date</t>
+          <t>Total Medicaid Spending</t>
         </is>
       </c>
       <c r="X186" t="inlineStr"/>
       <c r="Y186" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/PDMP_Presence.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Medical_Expenditures.md</t>
         </is>
       </c>
       <c r="Z186" t="inlineStr">
         <is>
-          <t>OPTIC 2017-2022</t>
+          <t>KFF 2018, 2019</t>
         </is>
       </c>
       <c r="AA186" t="inlineStr">
         <is>
-          <t>RAND-USC Schaeffer Opioid Policy Tools and Information Center, 2017-2022</t>
+          <t>Kaiser Family Foundation,  2018, 2019</t>
         </is>
       </c>
       <c r="AB186" t="inlineStr"/>
@@ -14449,7 +14485,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Prescription Drug Monitoring Programs (PDMP)</t>
+          <t>State &amp; Local Government Expenditures</t>
         </is>
       </c>
       <c r="C187" t="inlineStr"/>
@@ -14460,16 +14496,8 @@
       <c r="H187" t="inlineStr"/>
       <c r="I187" t="inlineStr"/>
       <c r="J187" t="inlineStr"/>
-      <c r="K187" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="L187" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="K187" t="inlineStr"/>
+      <c r="L187" t="inlineStr"/>
       <c r="M187" t="inlineStr">
         <is>
           <t>x</t>
@@ -14490,39 +14518,35 @@
           <t>x</t>
         </is>
       </c>
-      <c r="Q187" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="Q187" t="inlineStr"/>
       <c r="R187" t="inlineStr"/>
       <c r="S187" t="inlineStr"/>
       <c r="T187" t="inlineStr"/>
       <c r="U187" t="inlineStr"/>
       <c r="V187" t="inlineStr">
         <is>
-          <t>OpPdmpFr</t>
+          <t>PlcFyrExp</t>
         </is>
       </c>
       <c r="W187" t="inlineStr">
         <is>
-          <t>Operational PDMP (fraction of year in 2017)</t>
+          <t>Police &amp; fire expenditures</t>
         </is>
       </c>
       <c r="X187" t="inlineStr"/>
       <c r="Y187" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/PDMP_Presence.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Public_Expenditures.md</t>
         </is>
       </c>
       <c r="Z187" t="inlineStr">
         <is>
-          <t>OPTIC 2017-2022</t>
+          <t>Survey of State and Local Government Finances 2018-2022</t>
         </is>
       </c>
       <c r="AA187" t="inlineStr">
         <is>
-          <t>RAND-USC Schaeffer Opioid Policy Tools and Information Center, 2017-2022</t>
+          <t>U.S. Census Bureau Annual Survey of State and Local Government Finances via Urban Institute &amp; Tax Policy Center's State and Local Finance Data Finder</t>
         </is>
       </c>
       <c r="AB187" t="inlineStr"/>
@@ -14549,56 +14573,48 @@
       <c r="I188" t="inlineStr"/>
       <c r="J188" t="inlineStr"/>
       <c r="K188" t="inlineStr"/>
-      <c r="L188" t="inlineStr"/>
-      <c r="M188" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="N188" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="O188" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="P188" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="Q188" t="inlineStr"/>
+      <c r="L188" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M188" t="inlineStr"/>
+      <c r="N188" t="inlineStr"/>
+      <c r="O188" t="inlineStr"/>
+      <c r="P188" t="inlineStr"/>
+      <c r="Q188" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="R188" t="inlineStr"/>
       <c r="S188" t="inlineStr"/>
       <c r="T188" t="inlineStr"/>
       <c r="U188" t="inlineStr"/>
       <c r="V188" t="inlineStr">
         <is>
-          <t>CrrctExp</t>
+          <t>TradFedExp</t>
         </is>
       </c>
       <c r="W188" t="inlineStr">
         <is>
-          <t>Corrections expenditures</t>
+          <t>Traditional Medicaid Federal Spending</t>
         </is>
       </c>
       <c r="X188" t="inlineStr"/>
       <c r="Y188" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Public_Expenditures.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Medical_Expenditures.md</t>
         </is>
       </c>
       <c r="Z188" t="inlineStr">
         <is>
-          <t>Survey of State and Local Government Finances 2018-2022</t>
+          <t>KFF 2018, 2019</t>
         </is>
       </c>
       <c r="AA188" t="inlineStr">
         <is>
-          <t>U.S. Census Bureau Annual Survey of State and Local Government Finances via Urban Institute &amp; Tax Policy Center's State and Local Finance Data Finder</t>
+          <t>Kaiser Family Foundation,  2018, 2019</t>
         </is>
       </c>
       <c r="AB188" t="inlineStr"/>
@@ -14645,12 +14661,12 @@
       <c r="U189" t="inlineStr"/>
       <c r="V189" t="inlineStr">
         <is>
-          <t>ExpnFedExp</t>
+          <t>TradSttExp</t>
         </is>
       </c>
       <c r="W189" t="inlineStr">
         <is>
-          <t>Expansion Medicaid Federal Spending</t>
+          <t>Traditional Medicaid State Spending</t>
         </is>
       </c>
       <c r="X189" t="inlineStr"/>
@@ -14693,48 +14709,56 @@
       <c r="I190" t="inlineStr"/>
       <c r="J190" t="inlineStr"/>
       <c r="K190" t="inlineStr"/>
-      <c r="L190" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="M190" t="inlineStr"/>
-      <c r="N190" t="inlineStr"/>
-      <c r="O190" t="inlineStr"/>
-      <c r="P190" t="inlineStr"/>
-      <c r="Q190" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L190" t="inlineStr"/>
+      <c r="M190" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N190" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O190" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="P190" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Q190" t="inlineStr"/>
       <c r="R190" t="inlineStr"/>
       <c r="S190" t="inlineStr"/>
       <c r="T190" t="inlineStr"/>
       <c r="U190" t="inlineStr"/>
       <c r="V190" t="inlineStr">
         <is>
-          <t>ExpnSttExp</t>
+          <t>WlfrExp</t>
         </is>
       </c>
       <c r="W190" t="inlineStr">
         <is>
-          <t>Expansion Medicaid State Spending</t>
+          <t>Public welfare expenditures</t>
         </is>
       </c>
       <c r="X190" t="inlineStr"/>
       <c r="Y190" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Medical_Expenditures.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Public_Expenditures.md</t>
         </is>
       </c>
       <c r="Z190" t="inlineStr">
         <is>
-          <t>KFF 2018, 2019</t>
+          <t>Survey of State and Local Government Finances 2018-2022</t>
         </is>
       </c>
       <c r="AA190" t="inlineStr">
         <is>
-          <t>Kaiser Family Foundation,  2018, 2019</t>
+          <t>U.S. Census Bureau Annual Survey of State and Local Government Finances via Urban Institute &amp; Tax Policy Center's State and Local Finance Data Finder</t>
         </is>
       </c>
       <c r="AB190" t="inlineStr"/>
@@ -14744,12 +14768,12 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Policy</t>
+          <t>Outcome</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>State &amp; Local Government Expenditures</t>
+          <t>Hepatitis C Rates</t>
         </is>
       </c>
       <c r="C191" t="inlineStr"/>
@@ -14760,28 +14784,16 @@
       <c r="H191" t="inlineStr"/>
       <c r="I191" t="inlineStr"/>
       <c r="J191" t="inlineStr"/>
-      <c r="K191" t="inlineStr"/>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="L191" t="inlineStr"/>
-      <c r="M191" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="N191" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="O191" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="P191" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="M191" t="inlineStr"/>
+      <c r="N191" t="inlineStr"/>
+      <c r="O191" t="inlineStr"/>
+      <c r="P191" t="inlineStr"/>
       <c r="Q191" t="inlineStr"/>
       <c r="R191" t="inlineStr"/>
       <c r="S191" t="inlineStr"/>
@@ -14789,28 +14801,28 @@
       <c r="U191" t="inlineStr"/>
       <c r="V191" t="inlineStr">
         <is>
-          <t>HlthExp</t>
+          <t>A50_74Hcv</t>
         </is>
       </c>
       <c r="W191" t="inlineStr">
         <is>
-          <t>Public health expenditures</t>
+          <t>Yearly Hepatitis C cases - 50 to 74 years old (2013-2016)</t>
         </is>
       </c>
       <c r="X191" t="inlineStr"/>
       <c r="Y191" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Public_Expenditures.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/HepatitisC_Rates.md</t>
         </is>
       </c>
       <c r="Z191" t="inlineStr">
         <is>
-          <t>Survey of State and Local Government Finances 2018-2022</t>
+          <t>HepVu 2013-2016, 2018-2022</t>
         </is>
       </c>
       <c r="AA191" t="inlineStr">
         <is>
-          <t>U.S. Census Bureau Annual Survey of State and Local Government Finances via Urban Institute &amp; Tax Policy Center's State and Local Finance Data Finder</t>
+          <t>HepVu, Emory University Rollins School of Public Health, 2013-2016 &amp; 2018-2022</t>
         </is>
       </c>
       <c r="AB191" t="inlineStr"/>
@@ -14820,23 +14832,43 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Policy</t>
+          <t>Outcome</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>State &amp; Local Government Expenditures</t>
+          <t>Hepatitis C Rates</t>
         </is>
       </c>
       <c r="C192" t="inlineStr"/>
       <c r="D192" t="inlineStr"/>
       <c r="E192" t="inlineStr"/>
       <c r="F192" t="inlineStr"/>
-      <c r="G192" t="inlineStr"/>
-      <c r="H192" t="inlineStr"/>
-      <c r="I192" t="inlineStr"/>
-      <c r="J192" t="inlineStr"/>
-      <c r="K192" t="inlineStr"/>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J192" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="L192" t="inlineStr">
         <is>
           <t>x</t>
@@ -14847,42 +14879,50 @@
           <t>x</t>
         </is>
       </c>
-      <c r="N192" t="inlineStr"/>
-      <c r="O192" t="inlineStr"/>
-      <c r="P192" t="inlineStr"/>
-      <c r="Q192" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N192" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O192" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="P192" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Q192" t="inlineStr"/>
       <c r="R192" t="inlineStr"/>
       <c r="S192" t="inlineStr"/>
       <c r="T192" t="inlineStr"/>
       <c r="U192" t="inlineStr"/>
       <c r="V192" t="inlineStr">
         <is>
-          <t>MedcdExp</t>
+          <t>A50_74HcvD</t>
         </is>
       </c>
       <c r="W192" t="inlineStr">
         <is>
-          <t>Total Medicaid Spending</t>
+          <t>Hepatitis C Deaths - 50 to 74 years old</t>
         </is>
       </c>
       <c r="X192" t="inlineStr"/>
       <c r="Y192" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Medical_Expenditures.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/HepatitisC_Rates.md</t>
         </is>
       </c>
       <c r="Z192" t="inlineStr">
         <is>
-          <t>KFF 2018, 2019</t>
+          <t>HepVu 2013-2016, 2018-2022</t>
         </is>
       </c>
       <c r="AA192" t="inlineStr">
         <is>
-          <t>Kaiser Family Foundation,  2018, 2019</t>
+          <t>HepVu, Emory University Rollins School of Public Health, 2013-2016 &amp; 2018-2022</t>
         </is>
       </c>
       <c r="AB192" t="inlineStr"/>
@@ -14892,24 +14932,48 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Policy</t>
+          <t>Outcome</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>State &amp; Local Government Expenditures</t>
+          <t>Hepatitis C Rates</t>
         </is>
       </c>
       <c r="C193" t="inlineStr"/>
       <c r="D193" t="inlineStr"/>
       <c r="E193" t="inlineStr"/>
       <c r="F193" t="inlineStr"/>
-      <c r="G193" t="inlineStr"/>
-      <c r="H193" t="inlineStr"/>
-      <c r="I193" t="inlineStr"/>
-      <c r="J193" t="inlineStr"/>
-      <c r="K193" t="inlineStr"/>
-      <c r="L193" t="inlineStr"/>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="L193" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="M193" t="inlineStr">
         <is>
           <t>x</t>
@@ -14937,28 +15001,28 @@
       <c r="U193" t="inlineStr"/>
       <c r="V193" t="inlineStr">
         <is>
-          <t>PlcFyrExp</t>
+          <t>AmInHcvD</t>
         </is>
       </c>
       <c r="W193" t="inlineStr">
         <is>
-          <t>Police &amp; fire expenditures</t>
+          <t>Hepatitis C Deaths - American Indian</t>
         </is>
       </c>
       <c r="X193" t="inlineStr"/>
       <c r="Y193" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Public_Expenditures.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/HepatitisC_Rates.md</t>
         </is>
       </c>
       <c r="Z193" t="inlineStr">
         <is>
-          <t>Survey of State and Local Government Finances 2018-2022</t>
+          <t>HepVu 2013-2016, 2018-2022</t>
         </is>
       </c>
       <c r="AA193" t="inlineStr">
         <is>
-          <t>U.S. Census Bureau Annual Survey of State and Local Government Finances via Urban Institute &amp; Tax Policy Center's State and Local Finance Data Finder</t>
+          <t>HepVu, Emory University Rollins School of Public Health, 2013-2016 &amp; 2018-2022</t>
         </is>
       </c>
       <c r="AB193" t="inlineStr"/>
@@ -14968,12 +15032,12 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Policy</t>
+          <t>Outcome</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>State &amp; Local Government Expenditures</t>
+          <t>Hepatitis C Rates</t>
         </is>
       </c>
       <c r="C194" t="inlineStr"/>
@@ -14990,43 +15054,55 @@
           <t>x</t>
         </is>
       </c>
-      <c r="M194" t="inlineStr"/>
-      <c r="N194" t="inlineStr"/>
-      <c r="O194" t="inlineStr"/>
-      <c r="P194" t="inlineStr"/>
-      <c r="Q194" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="M194" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N194" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O194" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="P194" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Q194" t="inlineStr"/>
       <c r="R194" t="inlineStr"/>
       <c r="S194" t="inlineStr"/>
       <c r="T194" t="inlineStr"/>
       <c r="U194" t="inlineStr"/>
       <c r="V194" t="inlineStr">
         <is>
-          <t>TradFedExp</t>
+          <t>AsHcvD</t>
         </is>
       </c>
       <c r="W194" t="inlineStr">
         <is>
-          <t>Traditional Medicaid Federal Spending</t>
+          <t xml:space="preserve">Hepatitis C deaths among Asian populations </t>
         </is>
       </c>
       <c r="X194" t="inlineStr"/>
       <c r="Y194" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Medical_Expenditures.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/HepatitisC_Rates.md</t>
         </is>
       </c>
       <c r="Z194" t="inlineStr">
         <is>
-          <t>KFF 2018, 2019</t>
+          <t>HepVu 2013-2016, 2018-2022</t>
         </is>
       </c>
       <c r="AA194" t="inlineStr">
         <is>
-          <t>Kaiser Family Foundation,  2018, 2019</t>
+          <t>HepVu, Emory University Rollins School of Public Health, 2013-2016 &amp; 2018-2022</t>
         </is>
       </c>
       <c r="AB194" t="inlineStr"/>
@@ -15036,65 +15112,77 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Policy</t>
+          <t>Outcome</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>State &amp; Local Government Expenditures</t>
+          <t>Hepatitis C Rates</t>
         </is>
       </c>
       <c r="C195" t="inlineStr"/>
       <c r="D195" t="inlineStr"/>
       <c r="E195" t="inlineStr"/>
       <c r="F195" t="inlineStr"/>
-      <c r="G195" t="inlineStr"/>
-      <c r="H195" t="inlineStr"/>
-      <c r="I195" t="inlineStr"/>
-      <c r="J195" t="inlineStr"/>
-      <c r="K195" t="inlineStr"/>
-      <c r="L195" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="L195" t="inlineStr"/>
       <c r="M195" t="inlineStr"/>
       <c r="N195" t="inlineStr"/>
       <c r="O195" t="inlineStr"/>
       <c r="P195" t="inlineStr"/>
-      <c r="Q195" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="Q195" t="inlineStr"/>
       <c r="R195" t="inlineStr"/>
       <c r="S195" t="inlineStr"/>
       <c r="T195" t="inlineStr"/>
       <c r="U195" t="inlineStr"/>
       <c r="V195" t="inlineStr">
         <is>
-          <t>TradSttExp</t>
+          <t>AsPiHcvD</t>
         </is>
       </c>
       <c r="W195" t="inlineStr">
         <is>
-          <t>Traditional Medicaid State Spending</t>
+          <t>Hepatitis C Deaths - Asian &amp; Pacific Islander</t>
         </is>
       </c>
       <c r="X195" t="inlineStr"/>
       <c r="Y195" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Medical_Expenditures.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/HepatitisC_Rates.md</t>
         </is>
       </c>
       <c r="Z195" t="inlineStr">
         <is>
-          <t>KFF 2018, 2019</t>
+          <t>HepVu 2013-2016, 2018-2022</t>
         </is>
       </c>
       <c r="AA195" t="inlineStr">
         <is>
-          <t>Kaiser Family Foundation,  2018, 2019</t>
+          <t>HepVu, Emory University Rollins School of Public Health, 2013-2016 &amp; 2018-2022</t>
         </is>
       </c>
       <c r="AB195" t="inlineStr"/>
@@ -15104,12 +15192,12 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Policy</t>
+          <t>Outcome</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>State &amp; Local Government Expenditures</t>
+          <t>Hepatitis C Rates</t>
         </is>
       </c>
       <c r="C196" t="inlineStr"/>
@@ -15120,23 +15208,15 @@
       <c r="H196" t="inlineStr"/>
       <c r="I196" t="inlineStr"/>
       <c r="J196" t="inlineStr"/>
-      <c r="K196" t="inlineStr"/>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="L196" t="inlineStr"/>
-      <c r="M196" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="N196" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="O196" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="M196" t="inlineStr"/>
+      <c r="N196" t="inlineStr"/>
+      <c r="O196" t="inlineStr"/>
       <c r="P196" t="inlineStr">
         <is>
           <t>x</t>
@@ -15149,28 +15229,28 @@
       <c r="U196" t="inlineStr"/>
       <c r="V196" t="inlineStr">
         <is>
-          <t>WlfrExp</t>
+          <t>AvA50_74HcvD</t>
         </is>
       </c>
       <c r="W196" t="inlineStr">
         <is>
-          <t>Public welfare expenditures</t>
+          <t>Average Ages between 50 to 74 Hepitatis C virus Deaths</t>
         </is>
       </c>
       <c r="X196" t="inlineStr"/>
       <c r="Y196" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Public_Expenditures.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/HepatitisC_Rates.md</t>
         </is>
       </c>
       <c r="Z196" t="inlineStr">
         <is>
-          <t>Survey of State and Local Government Finances 2018-2022</t>
+          <t>HepVu 2013-2016, 2018-2022</t>
         </is>
       </c>
       <c r="AA196" t="inlineStr">
         <is>
-          <t>U.S. Census Bureau Annual Survey of State and Local Government Finances via Urban Institute &amp; Tax Policy Center's State and Local Finance Data Finder</t>
+          <t>HepVu, Emory University Rollins School of Public Health, 2013-2016 &amp; 2018-2022</t>
         </is>
       </c>
       <c r="AB196" t="inlineStr"/>
@@ -15205,7 +15285,11 @@
       <c r="M197" t="inlineStr"/>
       <c r="N197" t="inlineStr"/>
       <c r="O197" t="inlineStr"/>
-      <c r="P197" t="inlineStr"/>
+      <c r="P197" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="Q197" t="inlineStr"/>
       <c r="R197" t="inlineStr"/>
       <c r="S197" t="inlineStr"/>
@@ -15213,12 +15297,12 @@
       <c r="U197" t="inlineStr"/>
       <c r="V197" t="inlineStr">
         <is>
-          <t>A50_74Hcv</t>
+          <t>AvAmInHcvD</t>
         </is>
       </c>
       <c r="W197" t="inlineStr">
         <is>
-          <t>Yearly Hepatitis C cases - 50 to 74 years old (2013-2016)</t>
+          <t>Hepatitis C Deaths - American Indian (5-Year Averages)</t>
         </is>
       </c>
       <c r="X197" t="inlineStr"/>
@@ -15256,51 +15340,15 @@
       <c r="D198" t="inlineStr"/>
       <c r="E198" t="inlineStr"/>
       <c r="F198" t="inlineStr"/>
-      <c r="G198" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="H198" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="I198" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="J198" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="K198" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="L198" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="M198" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="N198" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="O198" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="G198" t="inlineStr"/>
+      <c r="H198" t="inlineStr"/>
+      <c r="I198" t="inlineStr"/>
+      <c r="J198" t="inlineStr"/>
+      <c r="K198" t="inlineStr"/>
+      <c r="L198" t="inlineStr"/>
+      <c r="M198" t="inlineStr"/>
+      <c r="N198" t="inlineStr"/>
+      <c r="O198" t="inlineStr"/>
       <c r="P198" t="inlineStr">
         <is>
           <t>x</t>
@@ -15313,12 +15361,12 @@
       <c r="U198" t="inlineStr"/>
       <c r="V198" t="inlineStr">
         <is>
-          <t>A50_74HcvD</t>
+          <t>AvAsHcvD</t>
         </is>
       </c>
       <c r="W198" t="inlineStr">
         <is>
-          <t>Hepatitis C Deaths - 50 to 74 years old</t>
+          <t>Mean yearly Hepatitis C deaths among Asian population from 2018-2022</t>
         </is>
       </c>
       <c r="X198" t="inlineStr"/>
@@ -15356,56 +15404,20 @@
       <c r="D199" t="inlineStr"/>
       <c r="E199" t="inlineStr"/>
       <c r="F199" t="inlineStr"/>
-      <c r="G199" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="H199" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="I199" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="J199" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="G199" t="inlineStr"/>
+      <c r="H199" t="inlineStr"/>
+      <c r="I199" t="inlineStr"/>
+      <c r="J199" t="inlineStr"/>
       <c r="K199" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="L199" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="M199" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="N199" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="O199" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="P199" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L199" t="inlineStr"/>
+      <c r="M199" t="inlineStr"/>
+      <c r="N199" t="inlineStr"/>
+      <c r="O199" t="inlineStr"/>
+      <c r="P199" t="inlineStr"/>
       <c r="Q199" t="inlineStr"/>
       <c r="R199" t="inlineStr"/>
       <c r="S199" t="inlineStr"/>
@@ -15413,12 +15425,12 @@
       <c r="U199" t="inlineStr"/>
       <c r="V199" t="inlineStr">
         <is>
-          <t>AmInHcvD</t>
+          <t>AvAsPiHcvD</t>
         </is>
       </c>
       <c r="W199" t="inlineStr">
         <is>
-          <t>Hepatitis C Deaths - American Indian</t>
+          <t>Hepatitis C Deaths - Asian &amp; Pacific Islander (2013 - 2017)</t>
         </is>
       </c>
       <c r="X199" t="inlineStr"/>
@@ -15460,27 +15472,15 @@
       <c r="H200" t="inlineStr"/>
       <c r="I200" t="inlineStr"/>
       <c r="J200" t="inlineStr"/>
-      <c r="K200" t="inlineStr"/>
-      <c r="L200" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="M200" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="N200" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="O200" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="L200" t="inlineStr"/>
+      <c r="M200" t="inlineStr"/>
+      <c r="N200" t="inlineStr"/>
+      <c r="O200" t="inlineStr"/>
       <c r="P200" t="inlineStr">
         <is>
           <t>x</t>
@@ -15493,12 +15493,12 @@
       <c r="U200" t="inlineStr"/>
       <c r="V200" t="inlineStr">
         <is>
-          <t>AsHcvD</t>
+          <t>AvBlkHcvD</t>
         </is>
       </c>
       <c r="W200" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hepatitis C deaths among Asian populations </t>
+          <t>Hepatitis C Deaths - Black (5-Year Averages)</t>
         </is>
       </c>
       <c r="X200" t="inlineStr"/>
@@ -15536,26 +15536,10 @@
       <c r="D201" t="inlineStr"/>
       <c r="E201" t="inlineStr"/>
       <c r="F201" t="inlineStr"/>
-      <c r="G201" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="H201" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="I201" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="J201" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="G201" t="inlineStr"/>
+      <c r="H201" t="inlineStr"/>
+      <c r="I201" t="inlineStr"/>
+      <c r="J201" t="inlineStr"/>
       <c r="K201" t="inlineStr">
         <is>
           <t>x</t>
@@ -15565,7 +15549,11 @@
       <c r="M201" t="inlineStr"/>
       <c r="N201" t="inlineStr"/>
       <c r="O201" t="inlineStr"/>
-      <c r="P201" t="inlineStr"/>
+      <c r="P201" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="Q201" t="inlineStr"/>
       <c r="R201" t="inlineStr"/>
       <c r="S201" t="inlineStr"/>
@@ -15573,12 +15561,12 @@
       <c r="U201" t="inlineStr"/>
       <c r="V201" t="inlineStr">
         <is>
-          <t>AsPiHcvD</t>
+          <t>AvFlHcvD</t>
         </is>
       </c>
       <c r="W201" t="inlineStr">
         <is>
-          <t>Hepatitis C Deaths - Asian &amp; Pacific Islander</t>
+          <t>Hepatitis C Deaths - Women (5-Year Averages)</t>
         </is>
       </c>
       <c r="X201" t="inlineStr"/>
@@ -15641,12 +15629,12 @@
       <c r="U202" t="inlineStr"/>
       <c r="V202" t="inlineStr">
         <is>
-          <t>AvA50_74HcvD</t>
+          <t>AvHcvD</t>
         </is>
       </c>
       <c r="W202" t="inlineStr">
         <is>
-          <t>Average Ages between 50 to 74 Hepitatis C virus Deaths</t>
+          <t>Average Hepitatis C virus Deaths (5-Year Averages)</t>
         </is>
       </c>
       <c r="X202" t="inlineStr"/>
@@ -15709,12 +15697,12 @@
       <c r="U203" t="inlineStr"/>
       <c r="V203" t="inlineStr">
         <is>
-          <t>AvAmInHcvD</t>
+          <t>AvHspHcvD</t>
         </is>
       </c>
       <c r="W203" t="inlineStr">
         <is>
-          <t>Hepatitis C Deaths - American Indian (5-Year Averages)</t>
+          <t>Hepatitis C Deaths - Hispanic (5-Year Averages)</t>
         </is>
       </c>
       <c r="X203" t="inlineStr"/>
@@ -15756,7 +15744,11 @@
       <c r="H204" t="inlineStr"/>
       <c r="I204" t="inlineStr"/>
       <c r="J204" t="inlineStr"/>
-      <c r="K204" t="inlineStr"/>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="L204" t="inlineStr"/>
       <c r="M204" t="inlineStr"/>
       <c r="N204" t="inlineStr"/>
@@ -15773,12 +15765,12 @@
       <c r="U204" t="inlineStr"/>
       <c r="V204" t="inlineStr">
         <is>
-          <t>AvAsHcvD</t>
+          <t>AvMlHcvD</t>
         </is>
       </c>
       <c r="W204" t="inlineStr">
         <is>
-          <t>Mean yearly Hepatitis C deaths among Asian population from 2018-2022</t>
+          <t>Hepatitis C Deaths - Men (5-Year Averages)</t>
         </is>
       </c>
       <c r="X204" t="inlineStr"/>
@@ -15820,16 +15812,16 @@
       <c r="H205" t="inlineStr"/>
       <c r="I205" t="inlineStr"/>
       <c r="J205" t="inlineStr"/>
-      <c r="K205" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="K205" t="inlineStr"/>
       <c r="L205" t="inlineStr"/>
       <c r="M205" t="inlineStr"/>
       <c r="N205" t="inlineStr"/>
       <c r="O205" t="inlineStr"/>
-      <c r="P205" t="inlineStr"/>
+      <c r="P205" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="Q205" t="inlineStr"/>
       <c r="R205" t="inlineStr"/>
       <c r="S205" t="inlineStr"/>
@@ -15837,12 +15829,12 @@
       <c r="U205" t="inlineStr"/>
       <c r="V205" t="inlineStr">
         <is>
-          <t>AvAsPiHcvD</t>
+          <t>AvMulHcvD</t>
         </is>
       </c>
       <c r="W205" t="inlineStr">
         <is>
-          <t>Hepatitis C Deaths - Asian &amp; Pacific Islander (2013 - 2017)</t>
+          <t>Mean yearly Hepatitis C deaths among Multiple Race populations from 2018-2022</t>
         </is>
       </c>
       <c r="X205" t="inlineStr"/>
@@ -15884,11 +15876,7 @@
       <c r="H206" t="inlineStr"/>
       <c r="I206" t="inlineStr"/>
       <c r="J206" t="inlineStr"/>
-      <c r="K206" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="K206" t="inlineStr"/>
       <c r="L206" t="inlineStr"/>
       <c r="M206" t="inlineStr"/>
       <c r="N206" t="inlineStr"/>
@@ -15905,12 +15893,12 @@
       <c r="U206" t="inlineStr"/>
       <c r="V206" t="inlineStr">
         <is>
-          <t>AvBlkHcvD</t>
+          <t>AvNhPiHcvD</t>
         </is>
       </c>
       <c r="W206" t="inlineStr">
         <is>
-          <t>Hepatitis C Deaths - Black (5-Year Averages)</t>
+          <t>Mean yearly Hepatitis C deaths among Native Hawaiian and Pacific Islanders population from 2018-2022</t>
         </is>
       </c>
       <c r="X206" t="inlineStr"/>
@@ -15973,12 +15961,12 @@
       <c r="U207" t="inlineStr"/>
       <c r="V207" t="inlineStr">
         <is>
-          <t>AvFlHcvD</t>
+          <t>AvO75HcvD</t>
         </is>
       </c>
       <c r="W207" t="inlineStr">
         <is>
-          <t>Hepatitis C Deaths - Women (5-Year Averages)</t>
+          <t>Hepatitis C Deaths - Age Over 75  (5-Year Averages)</t>
         </is>
       </c>
       <c r="X207" t="inlineStr"/>
@@ -16041,12 +16029,12 @@
       <c r="U208" t="inlineStr"/>
       <c r="V208" t="inlineStr">
         <is>
-          <t>AvHcvD</t>
+          <t>AvU50HcvD</t>
         </is>
       </c>
       <c r="W208" t="inlineStr">
         <is>
-          <t>Average Hepitatis C virus Deaths (5-Year Averages)</t>
+          <t>Hepatitis C Deaths - Age Under 50 (5-Year Averages)</t>
         </is>
       </c>
       <c r="X208" t="inlineStr"/>
@@ -16088,11 +16076,7 @@
       <c r="H209" t="inlineStr"/>
       <c r="I209" t="inlineStr"/>
       <c r="J209" t="inlineStr"/>
-      <c r="K209" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="K209" t="inlineStr"/>
       <c r="L209" t="inlineStr"/>
       <c r="M209" t="inlineStr"/>
       <c r="N209" t="inlineStr"/>
@@ -16109,12 +16093,12 @@
       <c r="U209" t="inlineStr"/>
       <c r="V209" t="inlineStr">
         <is>
-          <t>AvHspHcvD</t>
+          <t>AvWhHcvD</t>
         </is>
       </c>
       <c r="W209" t="inlineStr">
         <is>
-          <t>Hepatitis C Deaths - Hispanic (5-Year Averages)</t>
+          <t>Average White Hepitatis C virus Deaths</t>
         </is>
       </c>
       <c r="X209" t="inlineStr"/>
@@ -16165,11 +16149,7 @@
       <c r="M210" t="inlineStr"/>
       <c r="N210" t="inlineStr"/>
       <c r="O210" t="inlineStr"/>
-      <c r="P210" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="P210" t="inlineStr"/>
       <c r="Q210" t="inlineStr"/>
       <c r="R210" t="inlineStr"/>
       <c r="S210" t="inlineStr"/>
@@ -16177,12 +16157,12 @@
       <c r="U210" t="inlineStr"/>
       <c r="V210" t="inlineStr">
         <is>
-          <t>AvMlHcvD</t>
+          <t>BlkHcv</t>
         </is>
       </c>
       <c r="W210" t="inlineStr">
         <is>
-          <t>Hepatitis C Deaths - Men (5-Year Averages)</t>
+          <t>Yearly Hepatitis C cases - Black (2013-2016)</t>
         </is>
       </c>
       <c r="X210" t="inlineStr"/>
@@ -16220,15 +16200,51 @@
       <c r="D211" t="inlineStr"/>
       <c r="E211" t="inlineStr"/>
       <c r="F211" t="inlineStr"/>
-      <c r="G211" t="inlineStr"/>
-      <c r="H211" t="inlineStr"/>
-      <c r="I211" t="inlineStr"/>
-      <c r="J211" t="inlineStr"/>
-      <c r="K211" t="inlineStr"/>
-      <c r="L211" t="inlineStr"/>
-      <c r="M211" t="inlineStr"/>
-      <c r="N211" t="inlineStr"/>
-      <c r="O211" t="inlineStr"/>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="L211" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M211" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N211" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O211" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="P211" t="inlineStr">
         <is>
           <t>x</t>
@@ -16241,12 +16257,12 @@
       <c r="U211" t="inlineStr"/>
       <c r="V211" t="inlineStr">
         <is>
-          <t>AvMulHcvD</t>
+          <t>BlkHcvD</t>
         </is>
       </c>
       <c r="W211" t="inlineStr">
         <is>
-          <t>Mean yearly Hepatitis C deaths among Multiple Race populations from 2018-2022</t>
+          <t>Hepatitis C Deaths - Black</t>
         </is>
       </c>
       <c r="X211" t="inlineStr"/>
@@ -16284,15 +16300,51 @@
       <c r="D212" t="inlineStr"/>
       <c r="E212" t="inlineStr"/>
       <c r="F212" t="inlineStr"/>
-      <c r="G212" t="inlineStr"/>
-      <c r="H212" t="inlineStr"/>
-      <c r="I212" t="inlineStr"/>
-      <c r="J212" t="inlineStr"/>
-      <c r="K212" t="inlineStr"/>
-      <c r="L212" t="inlineStr"/>
-      <c r="M212" t="inlineStr"/>
-      <c r="N212" t="inlineStr"/>
-      <c r="O212" t="inlineStr"/>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="L212" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M212" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N212" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O212" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="P212" t="inlineStr">
         <is>
           <t>x</t>
@@ -16305,12 +16357,12 @@
       <c r="U212" t="inlineStr"/>
       <c r="V212" t="inlineStr">
         <is>
-          <t>AvNhPiHcvD</t>
+          <t>FlHcvD</t>
         </is>
       </c>
       <c r="W212" t="inlineStr">
         <is>
-          <t>Mean yearly Hepatitis C deaths among Native Hawaiian and Pacific Islanders population from 2018-2022</t>
+          <t>Hepatitis C Deaths - Women</t>
         </is>
       </c>
       <c r="X212" t="inlineStr"/>
@@ -16361,11 +16413,7 @@
       <c r="M213" t="inlineStr"/>
       <c r="N213" t="inlineStr"/>
       <c r="O213" t="inlineStr"/>
-      <c r="P213" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="P213" t="inlineStr"/>
       <c r="Q213" t="inlineStr"/>
       <c r="R213" t="inlineStr"/>
       <c r="S213" t="inlineStr"/>
@@ -16373,12 +16421,12 @@
       <c r="U213" t="inlineStr"/>
       <c r="V213" t="inlineStr">
         <is>
-          <t>AvO75HcvD</t>
+          <t>FmHcv</t>
         </is>
       </c>
       <c r="W213" t="inlineStr">
         <is>
-          <t>Hepatitis C Deaths - Age Over 75  (5-Year Averages)</t>
+          <t>Yearly Hepatitis C cases - Women (2013-2016)</t>
         </is>
       </c>
       <c r="X213" t="inlineStr"/>
@@ -16416,19 +16464,51 @@
       <c r="D214" t="inlineStr"/>
       <c r="E214" t="inlineStr"/>
       <c r="F214" t="inlineStr"/>
-      <c r="G214" t="inlineStr"/>
-      <c r="H214" t="inlineStr"/>
-      <c r="I214" t="inlineStr"/>
-      <c r="J214" t="inlineStr"/>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J214" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="K214" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="L214" t="inlineStr"/>
-      <c r="M214" t="inlineStr"/>
-      <c r="N214" t="inlineStr"/>
-      <c r="O214" t="inlineStr"/>
+      <c r="L214" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M214" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N214" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O214" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="P214" t="inlineStr">
         <is>
           <t>x</t>
@@ -16441,12 +16521,12 @@
       <c r="U214" t="inlineStr"/>
       <c r="V214" t="inlineStr">
         <is>
-          <t>AvU50HcvD</t>
+          <t>HcvD</t>
         </is>
       </c>
       <c r="W214" t="inlineStr">
         <is>
-          <t>Hepatitis C Deaths - Age Under 50 (5-Year Averages)</t>
+          <t>Hepatitis C Deaths</t>
         </is>
       </c>
       <c r="X214" t="inlineStr"/>
@@ -16484,15 +16564,51 @@
       <c r="D215" t="inlineStr"/>
       <c r="E215" t="inlineStr"/>
       <c r="F215" t="inlineStr"/>
-      <c r="G215" t="inlineStr"/>
-      <c r="H215" t="inlineStr"/>
-      <c r="I215" t="inlineStr"/>
-      <c r="J215" t="inlineStr"/>
-      <c r="K215" t="inlineStr"/>
-      <c r="L215" t="inlineStr"/>
-      <c r="M215" t="inlineStr"/>
-      <c r="N215" t="inlineStr"/>
-      <c r="O215" t="inlineStr"/>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J215" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="L215" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M215" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N215" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O215" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="P215" t="inlineStr">
         <is>
           <t>x</t>
@@ -16505,12 +16621,12 @@
       <c r="U215" t="inlineStr"/>
       <c r="V215" t="inlineStr">
         <is>
-          <t>AvWhHcvD</t>
+          <t>HspHcvD</t>
         </is>
       </c>
       <c r="W215" t="inlineStr">
         <is>
-          <t>Average White Hepitatis C virus Deaths</t>
+          <t>Hepatitis C Deaths - Hispanic</t>
         </is>
       </c>
       <c r="X215" t="inlineStr"/>
@@ -16569,12 +16685,12 @@
       <c r="U216" t="inlineStr"/>
       <c r="V216" t="inlineStr">
         <is>
-          <t>BlkHcv</t>
+          <t>MlHcv</t>
         </is>
       </c>
       <c r="W216" t="inlineStr">
         <is>
-          <t>Yearly Hepatitis C cases - Black (2013-2016)</t>
+          <t>Yearly Hepatitis C cases - Men (2013-2016)</t>
         </is>
       </c>
       <c r="X216" t="inlineStr"/>
@@ -16669,12 +16785,12 @@
       <c r="U217" t="inlineStr"/>
       <c r="V217" t="inlineStr">
         <is>
-          <t>BlkHcvD</t>
+          <t>MlHcvD</t>
         </is>
       </c>
       <c r="W217" t="inlineStr">
         <is>
-          <t>Hepatitis C Deaths - Black</t>
+          <t>Hepatitis C Deaths - Men</t>
         </is>
       </c>
       <c r="X217" t="inlineStr"/>
@@ -16712,31 +16828,11 @@
       <c r="D218" t="inlineStr"/>
       <c r="E218" t="inlineStr"/>
       <c r="F218" t="inlineStr"/>
-      <c r="G218" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="H218" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="I218" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="J218" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="K218" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="G218" t="inlineStr"/>
+      <c r="H218" t="inlineStr"/>
+      <c r="I218" t="inlineStr"/>
+      <c r="J218" t="inlineStr"/>
+      <c r="K218" t="inlineStr"/>
       <c r="L218" t="inlineStr">
         <is>
           <t>x</t>
@@ -16769,12 +16865,12 @@
       <c r="U218" t="inlineStr"/>
       <c r="V218" t="inlineStr">
         <is>
-          <t>FlHcvD</t>
+          <t>MulHcvD</t>
         </is>
       </c>
       <c r="W218" t="inlineStr">
         <is>
-          <t>Hepatitis C Deaths - Women</t>
+          <t xml:space="preserve">Hepatitis C deaths among Multiple Race populations </t>
         </is>
       </c>
       <c r="X218" t="inlineStr"/>
@@ -16816,16 +16912,32 @@
       <c r="H219" t="inlineStr"/>
       <c r="I219" t="inlineStr"/>
       <c r="J219" t="inlineStr"/>
-      <c r="K219" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="L219" t="inlineStr"/>
-      <c r="M219" t="inlineStr"/>
-      <c r="N219" t="inlineStr"/>
-      <c r="O219" t="inlineStr"/>
-      <c r="P219" t="inlineStr"/>
+      <c r="K219" t="inlineStr"/>
+      <c r="L219" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M219" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N219" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O219" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="P219" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="Q219" t="inlineStr"/>
       <c r="R219" t="inlineStr"/>
       <c r="S219" t="inlineStr"/>
@@ -16833,12 +16945,12 @@
       <c r="U219" t="inlineStr"/>
       <c r="V219" t="inlineStr">
         <is>
-          <t>FmHcv</t>
+          <t>NhPiHcvD</t>
         </is>
       </c>
       <c r="W219" t="inlineStr">
         <is>
-          <t>Yearly Hepatitis C cases - Women (2013-2016)</t>
+          <t xml:space="preserve">Hepatitis C deaths among Native Hawaiian and Pacific Islander populations </t>
         </is>
       </c>
       <c r="X219" t="inlineStr"/>
@@ -16876,56 +16988,20 @@
       <c r="D220" t="inlineStr"/>
       <c r="E220" t="inlineStr"/>
       <c r="F220" t="inlineStr"/>
-      <c r="G220" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="H220" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="I220" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="J220" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="G220" t="inlineStr"/>
+      <c r="H220" t="inlineStr"/>
+      <c r="I220" t="inlineStr"/>
+      <c r="J220" t="inlineStr"/>
       <c r="K220" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="L220" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="M220" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="N220" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="O220" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="P220" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L220" t="inlineStr"/>
+      <c r="M220" t="inlineStr"/>
+      <c r="N220" t="inlineStr"/>
+      <c r="O220" t="inlineStr"/>
+      <c r="P220" t="inlineStr"/>
       <c r="Q220" t="inlineStr"/>
       <c r="R220" t="inlineStr"/>
       <c r="S220" t="inlineStr"/>
@@ -16933,12 +17009,12 @@
       <c r="U220" t="inlineStr"/>
       <c r="V220" t="inlineStr">
         <is>
-          <t>HcvD</t>
+          <t>NonBlkHcv</t>
         </is>
       </c>
       <c r="W220" t="inlineStr">
         <is>
-          <t>Hepatitis C Deaths</t>
+          <t>Yearly Hepatitis C cases - non-Black (2013-2016)</t>
         </is>
       </c>
       <c r="X220" t="inlineStr"/>
@@ -17033,12 +17109,12 @@
       <c r="U221" t="inlineStr"/>
       <c r="V221" t="inlineStr">
         <is>
-          <t>HspHcvD</t>
+          <t>O75HcvD</t>
         </is>
       </c>
       <c r="W221" t="inlineStr">
         <is>
-          <t>Hepatitis C Deaths - Hispanic</t>
+          <t>Hepatitis C Deaths - Over 75 years old</t>
         </is>
       </c>
       <c r="X221" t="inlineStr"/>
@@ -17097,12 +17173,12 @@
       <c r="U222" t="inlineStr"/>
       <c r="V222" t="inlineStr">
         <is>
-          <t>MlHcv</t>
+          <t>Ov75Hcv</t>
         </is>
       </c>
       <c r="W222" t="inlineStr">
         <is>
-          <t>Yearly Hepatitis C cases - Men (2013-2016)</t>
+          <t>Yearly Hepatitis C cases - Over 75 years old (2013-2016)</t>
         </is>
       </c>
       <c r="X222" t="inlineStr"/>
@@ -17140,56 +17216,20 @@
       <c r="D223" t="inlineStr"/>
       <c r="E223" t="inlineStr"/>
       <c r="F223" t="inlineStr"/>
-      <c r="G223" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="H223" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="I223" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="J223" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="G223" t="inlineStr"/>
+      <c r="H223" t="inlineStr"/>
+      <c r="I223" t="inlineStr"/>
+      <c r="J223" t="inlineStr"/>
       <c r="K223" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="L223" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="M223" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="N223" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="O223" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="P223" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L223" t="inlineStr"/>
+      <c r="M223" t="inlineStr"/>
+      <c r="N223" t="inlineStr"/>
+      <c r="O223" t="inlineStr"/>
+      <c r="P223" t="inlineStr"/>
       <c r="Q223" t="inlineStr"/>
       <c r="R223" t="inlineStr"/>
       <c r="S223" t="inlineStr"/>
@@ -17197,12 +17237,12 @@
       <c r="U223" t="inlineStr"/>
       <c r="V223" t="inlineStr">
         <is>
-          <t>MlHcvD</t>
+          <t>TotHcv</t>
         </is>
       </c>
       <c r="W223" t="inlineStr">
         <is>
-          <t>Hepatitis C Deaths - Men</t>
+          <t>Yearly Hepatitis C cases (2013-2016)</t>
         </is>
       </c>
       <c r="X223" t="inlineStr"/>
@@ -17240,11 +17280,31 @@
       <c r="D224" t="inlineStr"/>
       <c r="E224" t="inlineStr"/>
       <c r="F224" t="inlineStr"/>
-      <c r="G224" t="inlineStr"/>
-      <c r="H224" t="inlineStr"/>
-      <c r="I224" t="inlineStr"/>
-      <c r="J224" t="inlineStr"/>
-      <c r="K224" t="inlineStr"/>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J224" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="L224" t="inlineStr">
         <is>
           <t>x</t>
@@ -17277,12 +17337,12 @@
       <c r="U224" t="inlineStr"/>
       <c r="V224" t="inlineStr">
         <is>
-          <t>MulHcvD</t>
+          <t>U50HcvD</t>
         </is>
       </c>
       <c r="W224" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hepatitis C deaths among Multiple Race populations </t>
+          <t>Hepatitis C Deaths - Under 50 years old</t>
         </is>
       </c>
       <c r="X224" t="inlineStr"/>
@@ -17324,32 +17384,16 @@
       <c r="H225" t="inlineStr"/>
       <c r="I225" t="inlineStr"/>
       <c r="J225" t="inlineStr"/>
-      <c r="K225" t="inlineStr"/>
-      <c r="L225" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="M225" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="N225" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="O225" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="P225" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="L225" t="inlineStr"/>
+      <c r="M225" t="inlineStr"/>
+      <c r="N225" t="inlineStr"/>
+      <c r="O225" t="inlineStr"/>
+      <c r="P225" t="inlineStr"/>
       <c r="Q225" t="inlineStr"/>
       <c r="R225" t="inlineStr"/>
       <c r="S225" t="inlineStr"/>
@@ -17357,12 +17401,12 @@
       <c r="U225" t="inlineStr"/>
       <c r="V225" t="inlineStr">
         <is>
-          <t>NhPiHcvD</t>
+          <t>Un50Hcv</t>
         </is>
       </c>
       <c r="W225" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hepatitis C deaths among Native Hawaiian and Pacific Islander populations </t>
+          <t>Yearly Hepatitis C cases - Under 50 years old (2013-2016)</t>
         </is>
       </c>
       <c r="X225" t="inlineStr"/>
@@ -17404,16 +17448,32 @@
       <c r="H226" t="inlineStr"/>
       <c r="I226" t="inlineStr"/>
       <c r="J226" t="inlineStr"/>
-      <c r="K226" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="L226" t="inlineStr"/>
-      <c r="M226" t="inlineStr"/>
-      <c r="N226" t="inlineStr"/>
-      <c r="O226" t="inlineStr"/>
-      <c r="P226" t="inlineStr"/>
+      <c r="K226" t="inlineStr"/>
+      <c r="L226" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M226" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N226" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O226" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="P226" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="Q226" t="inlineStr"/>
       <c r="R226" t="inlineStr"/>
       <c r="S226" t="inlineStr"/>
@@ -17421,12 +17481,12 @@
       <c r="U226" t="inlineStr"/>
       <c r="V226" t="inlineStr">
         <is>
-          <t>NonBlkHcv</t>
+          <t>WhtHcvD</t>
         </is>
       </c>
       <c r="W226" t="inlineStr">
         <is>
-          <t>Yearly Hepatitis C cases - non-Black (2013-2016)</t>
+          <t>Hepatitis C deaths among White populations</t>
         </is>
       </c>
       <c r="X226" t="inlineStr"/>
@@ -17457,18 +17517,14 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Hepatitis C Rates</t>
+          <t>Opioid Indicators</t>
         </is>
       </c>
       <c r="C227" t="inlineStr"/>
       <c r="D227" t="inlineStr"/>
       <c r="E227" t="inlineStr"/>
       <c r="F227" t="inlineStr"/>
-      <c r="G227" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="G227" t="inlineStr"/>
       <c r="H227" t="inlineStr">
         <is>
           <t>x</t>
@@ -17521,28 +17577,28 @@
       <c r="U227" t="inlineStr"/>
       <c r="V227" t="inlineStr">
         <is>
-          <t>O75HcvD</t>
+          <t>OdMortRt</t>
         </is>
       </c>
       <c r="W227" t="inlineStr">
         <is>
-          <t>Hepatitis C Deaths - Over 75 years old</t>
+          <t>Overdose Mortality Rate</t>
         </is>
       </c>
       <c r="X227" t="inlineStr"/>
       <c r="Y227" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/HepatitisC_Rates.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Opioid_Outcomes.md</t>
         </is>
       </c>
       <c r="Z227" t="inlineStr">
         <is>
-          <t>HepVu 2013-2016, 2018-2022</t>
+          <t>HepVu 2014-2022</t>
         </is>
       </c>
       <c r="AA227" t="inlineStr">
         <is>
-          <t>HepVu, Emory University Rollins School of Public Health, 2013-2016 &amp; 2018-2022</t>
+          <t>HepVu, Emory University Rollins School of Public Health, 2014-2022</t>
         </is>
       </c>
       <c r="AB227" t="inlineStr"/>
@@ -17557,7 +17613,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Hepatitis C Rates</t>
+          <t>Opioid Indicators</t>
         </is>
       </c>
       <c r="C228" t="inlineStr"/>
@@ -17568,14 +17624,14 @@
       <c r="H228" t="inlineStr"/>
       <c r="I228" t="inlineStr"/>
       <c r="J228" t="inlineStr"/>
-      <c r="K228" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="K228" t="inlineStr"/>
       <c r="L228" t="inlineStr"/>
       <c r="M228" t="inlineStr"/>
-      <c r="N228" t="inlineStr"/>
+      <c r="N228" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O228" t="inlineStr"/>
       <c r="P228" t="inlineStr"/>
       <c r="Q228" t="inlineStr"/>
@@ -17585,28 +17641,28 @@
       <c r="U228" t="inlineStr"/>
       <c r="V228" t="inlineStr">
         <is>
-          <t>Ov75Hcv</t>
+          <t>OdMortRtAv</t>
         </is>
       </c>
       <c r="W228" t="inlineStr">
         <is>
-          <t>Yearly Hepatitis C cases - Over 75 years old (2013-2016)</t>
+          <t>Overdose Mortality Rate Average (2016-2020)</t>
         </is>
       </c>
       <c r="X228" t="inlineStr"/>
       <c r="Y228" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/HepatitisC_Rates.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Opioid_Outcomes.md</t>
         </is>
       </c>
       <c r="Z228" t="inlineStr">
         <is>
-          <t>HepVu 2013-2016, 2018-2022</t>
+          <t>HepVu 2014-2022</t>
         </is>
       </c>
       <c r="AA228" t="inlineStr">
         <is>
-          <t>HepVu, Emory University Rollins School of Public Health, 2013-2016 &amp; 2018-2022</t>
+          <t>HepVu, Emory University Rollins School of Public Health, 2014-2022</t>
         </is>
       </c>
       <c r="AB228" t="inlineStr"/>
@@ -17621,7 +17677,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Hepatitis C Rates</t>
+          <t>Opioid Indicators</t>
         </is>
       </c>
       <c r="C229" t="inlineStr"/>
@@ -17632,16 +17688,20 @@
       <c r="H229" t="inlineStr"/>
       <c r="I229" t="inlineStr"/>
       <c r="J229" t="inlineStr"/>
-      <c r="K229" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="K229" t="inlineStr"/>
       <c r="L229" t="inlineStr"/>
       <c r="M229" t="inlineStr"/>
-      <c r="N229" t="inlineStr"/>
+      <c r="N229" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O229" t="inlineStr"/>
-      <c r="P229" t="inlineStr"/>
+      <c r="P229" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="Q229" t="inlineStr"/>
       <c r="R229" t="inlineStr"/>
       <c r="S229" t="inlineStr"/>
@@ -17649,28 +17709,28 @@
       <c r="U229" t="inlineStr"/>
       <c r="V229" t="inlineStr">
         <is>
-          <t>TotHcv</t>
+          <t>OpRxRt</t>
         </is>
       </c>
       <c r="W229" t="inlineStr">
         <is>
-          <t>Yearly Hepatitis C cases (2013-2016)</t>
+          <t>Opioid Prescription Rate</t>
         </is>
       </c>
       <c r="X229" t="inlineStr"/>
       <c r="Y229" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/HepatitisC_Rates.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Opioid_Outcomes.md</t>
         </is>
       </c>
       <c r="Z229" t="inlineStr">
         <is>
-          <t>HepVu 2013-2016, 2018-2022</t>
+          <t>HepVu 2014-2022</t>
         </is>
       </c>
       <c r="AA229" t="inlineStr">
         <is>
-          <t>HepVu, Emory University Rollins School of Public Health, 2013-2016 &amp; 2018-2022</t>
+          <t>HepVu, Emory University Rollins School of Public Health, 2014-2022</t>
         </is>
       </c>
       <c r="AB229" t="inlineStr"/>
@@ -17685,58 +17745,26 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Hepatitis C Rates</t>
+          <t>Opioid Indicators</t>
         </is>
       </c>
       <c r="C230" t="inlineStr"/>
       <c r="D230" t="inlineStr"/>
       <c r="E230" t="inlineStr"/>
       <c r="F230" t="inlineStr"/>
-      <c r="G230" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="H230" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="I230" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="J230" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="K230" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="L230" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="M230" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="G230" t="inlineStr"/>
+      <c r="H230" t="inlineStr"/>
+      <c r="I230" t="inlineStr"/>
+      <c r="J230" t="inlineStr"/>
+      <c r="K230" t="inlineStr"/>
+      <c r="L230" t="inlineStr"/>
+      <c r="M230" t="inlineStr"/>
       <c r="N230" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="O230" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="O230" t="inlineStr"/>
       <c r="P230" t="inlineStr">
         <is>
           <t>x</t>
@@ -17749,473 +17777,33 @@
       <c r="U230" t="inlineStr"/>
       <c r="V230" t="inlineStr">
         <is>
-          <t>U50HcvD</t>
+          <t>PrMsuseP</t>
         </is>
       </c>
       <c r="W230" t="inlineStr">
         <is>
-          <t>Hepatitis C Deaths - Under 50 years old</t>
+          <t>% Self-Report Misuse of Prescription Pain Medication (2020)</t>
         </is>
       </c>
       <c r="X230" t="inlineStr"/>
       <c r="Y230" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/HepatitisC_Rates.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Opioid_Outcomes.md</t>
         </is>
       </c>
       <c r="Z230" t="inlineStr">
         <is>
-          <t>HepVu 2013-2016, 2018-2022</t>
+          <t>HepVu 2014-2022</t>
         </is>
       </c>
       <c r="AA230" t="inlineStr">
         <is>
-          <t>HepVu, Emory University Rollins School of Public Health, 2013-2016 &amp; 2018-2022</t>
+          <t>HepVu, Emory University Rollins School of Public Health, 2014-2022</t>
         </is>
       </c>
       <c r="AB230" t="inlineStr"/>
       <c r="AC230" t="inlineStr"/>
       <c r="AD230" t="inlineStr"/>
-    </row>
-    <row r="231">
-      <c r="A231" t="inlineStr">
-        <is>
-          <t>Outcome</t>
-        </is>
-      </c>
-      <c r="B231" t="inlineStr">
-        <is>
-          <t>Hepatitis C Rates</t>
-        </is>
-      </c>
-      <c r="C231" t="inlineStr"/>
-      <c r="D231" t="inlineStr"/>
-      <c r="E231" t="inlineStr"/>
-      <c r="F231" t="inlineStr"/>
-      <c r="G231" t="inlineStr"/>
-      <c r="H231" t="inlineStr"/>
-      <c r="I231" t="inlineStr"/>
-      <c r="J231" t="inlineStr"/>
-      <c r="K231" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="L231" t="inlineStr"/>
-      <c r="M231" t="inlineStr"/>
-      <c r="N231" t="inlineStr"/>
-      <c r="O231" t="inlineStr"/>
-      <c r="P231" t="inlineStr"/>
-      <c r="Q231" t="inlineStr"/>
-      <c r="R231" t="inlineStr"/>
-      <c r="S231" t="inlineStr"/>
-      <c r="T231" t="inlineStr"/>
-      <c r="U231" t="inlineStr"/>
-      <c r="V231" t="inlineStr">
-        <is>
-          <t>Un50Hcv</t>
-        </is>
-      </c>
-      <c r="W231" t="inlineStr">
-        <is>
-          <t>Yearly Hepatitis C cases - Under 50 years old (2013-2016)</t>
-        </is>
-      </c>
-      <c r="X231" t="inlineStr"/>
-      <c r="Y231" t="inlineStr">
-        <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/HepatitisC_Rates.md</t>
-        </is>
-      </c>
-      <c r="Z231" t="inlineStr">
-        <is>
-          <t>HepVu 2013-2016, 2018-2022</t>
-        </is>
-      </c>
-      <c r="AA231" t="inlineStr">
-        <is>
-          <t>HepVu, Emory University Rollins School of Public Health, 2013-2016 &amp; 2018-2022</t>
-        </is>
-      </c>
-      <c r="AB231" t="inlineStr"/>
-      <c r="AC231" t="inlineStr"/>
-      <c r="AD231" t="inlineStr"/>
-    </row>
-    <row r="232">
-      <c r="A232" t="inlineStr">
-        <is>
-          <t>Outcome</t>
-        </is>
-      </c>
-      <c r="B232" t="inlineStr">
-        <is>
-          <t>Hepatitis C Rates</t>
-        </is>
-      </c>
-      <c r="C232" t="inlineStr"/>
-      <c r="D232" t="inlineStr"/>
-      <c r="E232" t="inlineStr"/>
-      <c r="F232" t="inlineStr"/>
-      <c r="G232" t="inlineStr"/>
-      <c r="H232" t="inlineStr"/>
-      <c r="I232" t="inlineStr"/>
-      <c r="J232" t="inlineStr"/>
-      <c r="K232" t="inlineStr"/>
-      <c r="L232" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="M232" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="N232" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="O232" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="P232" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="Q232" t="inlineStr"/>
-      <c r="R232" t="inlineStr"/>
-      <c r="S232" t="inlineStr"/>
-      <c r="T232" t="inlineStr"/>
-      <c r="U232" t="inlineStr"/>
-      <c r="V232" t="inlineStr">
-        <is>
-          <t>WhtHcvD</t>
-        </is>
-      </c>
-      <c r="W232" t="inlineStr">
-        <is>
-          <t>Hepatitis C deaths among White populations</t>
-        </is>
-      </c>
-      <c r="X232" t="inlineStr"/>
-      <c r="Y232" t="inlineStr">
-        <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/HepatitisC_Rates.md</t>
-        </is>
-      </c>
-      <c r="Z232" t="inlineStr">
-        <is>
-          <t>HepVu 2013-2016, 2018-2022</t>
-        </is>
-      </c>
-      <c r="AA232" t="inlineStr">
-        <is>
-          <t>HepVu, Emory University Rollins School of Public Health, 2013-2016 &amp; 2018-2022</t>
-        </is>
-      </c>
-      <c r="AB232" t="inlineStr"/>
-      <c r="AC232" t="inlineStr"/>
-      <c r="AD232" t="inlineStr"/>
-    </row>
-    <row r="233">
-      <c r="A233" t="inlineStr">
-        <is>
-          <t>Outcome</t>
-        </is>
-      </c>
-      <c r="B233" t="inlineStr">
-        <is>
-          <t>Opioid Indicators</t>
-        </is>
-      </c>
-      <c r="C233" t="inlineStr"/>
-      <c r="D233" t="inlineStr"/>
-      <c r="E233" t="inlineStr"/>
-      <c r="F233" t="inlineStr"/>
-      <c r="G233" t="inlineStr"/>
-      <c r="H233" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="I233" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="J233" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="K233" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="L233" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="M233" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="N233" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="O233" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="P233" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="Q233" t="inlineStr"/>
-      <c r="R233" t="inlineStr"/>
-      <c r="S233" t="inlineStr"/>
-      <c r="T233" t="inlineStr"/>
-      <c r="U233" t="inlineStr"/>
-      <c r="V233" t="inlineStr">
-        <is>
-          <t>OdMortRt</t>
-        </is>
-      </c>
-      <c r="W233" t="inlineStr">
-        <is>
-          <t>Overdose Mortality Rate</t>
-        </is>
-      </c>
-      <c r="X233" t="inlineStr"/>
-      <c r="Y233" t="inlineStr">
-        <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Opioid_Outcomes.md</t>
-        </is>
-      </c>
-      <c r="Z233" t="inlineStr">
-        <is>
-          <t>HepVu 2014-2022</t>
-        </is>
-      </c>
-      <c r="AA233" t="inlineStr">
-        <is>
-          <t>HepVu, Emory University Rollins School of Public Health, 2014-2022</t>
-        </is>
-      </c>
-      <c r="AB233" t="inlineStr"/>
-      <c r="AC233" t="inlineStr"/>
-      <c r="AD233" t="inlineStr"/>
-    </row>
-    <row r="234">
-      <c r="A234" t="inlineStr">
-        <is>
-          <t>Outcome</t>
-        </is>
-      </c>
-      <c r="B234" t="inlineStr">
-        <is>
-          <t>Opioid Indicators</t>
-        </is>
-      </c>
-      <c r="C234" t="inlineStr"/>
-      <c r="D234" t="inlineStr"/>
-      <c r="E234" t="inlineStr"/>
-      <c r="F234" t="inlineStr"/>
-      <c r="G234" t="inlineStr"/>
-      <c r="H234" t="inlineStr"/>
-      <c r="I234" t="inlineStr"/>
-      <c r="J234" t="inlineStr"/>
-      <c r="K234" t="inlineStr"/>
-      <c r="L234" t="inlineStr"/>
-      <c r="M234" t="inlineStr"/>
-      <c r="N234" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="O234" t="inlineStr"/>
-      <c r="P234" t="inlineStr"/>
-      <c r="Q234" t="inlineStr"/>
-      <c r="R234" t="inlineStr"/>
-      <c r="S234" t="inlineStr"/>
-      <c r="T234" t="inlineStr"/>
-      <c r="U234" t="inlineStr"/>
-      <c r="V234" t="inlineStr">
-        <is>
-          <t>OdMortRtAv</t>
-        </is>
-      </c>
-      <c r="W234" t="inlineStr">
-        <is>
-          <t>Overdose Mortality Rate Average (2016-2020)</t>
-        </is>
-      </c>
-      <c r="X234" t="inlineStr"/>
-      <c r="Y234" t="inlineStr">
-        <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Opioid_Outcomes.md</t>
-        </is>
-      </c>
-      <c r="Z234" t="inlineStr">
-        <is>
-          <t>HepVu 2014-2022</t>
-        </is>
-      </c>
-      <c r="AA234" t="inlineStr">
-        <is>
-          <t>HepVu, Emory University Rollins School of Public Health, 2014-2022</t>
-        </is>
-      </c>
-      <c r="AB234" t="inlineStr"/>
-      <c r="AC234" t="inlineStr"/>
-      <c r="AD234" t="inlineStr"/>
-    </row>
-    <row r="235">
-      <c r="A235" t="inlineStr">
-        <is>
-          <t>Outcome</t>
-        </is>
-      </c>
-      <c r="B235" t="inlineStr">
-        <is>
-          <t>Opioid Indicators</t>
-        </is>
-      </c>
-      <c r="C235" t="inlineStr"/>
-      <c r="D235" t="inlineStr"/>
-      <c r="E235" t="inlineStr"/>
-      <c r="F235" t="inlineStr"/>
-      <c r="G235" t="inlineStr"/>
-      <c r="H235" t="inlineStr"/>
-      <c r="I235" t="inlineStr"/>
-      <c r="J235" t="inlineStr"/>
-      <c r="K235" t="inlineStr"/>
-      <c r="L235" t="inlineStr"/>
-      <c r="M235" t="inlineStr"/>
-      <c r="N235" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="O235" t="inlineStr"/>
-      <c r="P235" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="Q235" t="inlineStr"/>
-      <c r="R235" t="inlineStr"/>
-      <c r="S235" t="inlineStr"/>
-      <c r="T235" t="inlineStr"/>
-      <c r="U235" t="inlineStr"/>
-      <c r="V235" t="inlineStr">
-        <is>
-          <t>OpRxRt</t>
-        </is>
-      </c>
-      <c r="W235" t="inlineStr">
-        <is>
-          <t>Opioid Prescription Rate</t>
-        </is>
-      </c>
-      <c r="X235" t="inlineStr"/>
-      <c r="Y235" t="inlineStr">
-        <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Opioid_Outcomes.md</t>
-        </is>
-      </c>
-      <c r="Z235" t="inlineStr">
-        <is>
-          <t>HepVu 2014-2022</t>
-        </is>
-      </c>
-      <c r="AA235" t="inlineStr">
-        <is>
-          <t>HepVu, Emory University Rollins School of Public Health, 2014-2022</t>
-        </is>
-      </c>
-      <c r="AB235" t="inlineStr"/>
-      <c r="AC235" t="inlineStr"/>
-      <c r="AD235" t="inlineStr"/>
-    </row>
-    <row r="236">
-      <c r="A236" t="inlineStr">
-        <is>
-          <t>Outcome</t>
-        </is>
-      </c>
-      <c r="B236" t="inlineStr">
-        <is>
-          <t>Opioid Indicators</t>
-        </is>
-      </c>
-      <c r="C236" t="inlineStr"/>
-      <c r="D236" t="inlineStr"/>
-      <c r="E236" t="inlineStr"/>
-      <c r="F236" t="inlineStr"/>
-      <c r="G236" t="inlineStr"/>
-      <c r="H236" t="inlineStr"/>
-      <c r="I236" t="inlineStr"/>
-      <c r="J236" t="inlineStr"/>
-      <c r="K236" t="inlineStr"/>
-      <c r="L236" t="inlineStr"/>
-      <c r="M236" t="inlineStr"/>
-      <c r="N236" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="O236" t="inlineStr"/>
-      <c r="P236" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="Q236" t="inlineStr"/>
-      <c r="R236" t="inlineStr"/>
-      <c r="S236" t="inlineStr"/>
-      <c r="T236" t="inlineStr"/>
-      <c r="U236" t="inlineStr"/>
-      <c r="V236" t="inlineStr">
-        <is>
-          <t>PrMsuseP</t>
-        </is>
-      </c>
-      <c r="W236" t="inlineStr">
-        <is>
-          <t>% Self-Report Misuse of Prescription Pain Medication (2020)</t>
-        </is>
-      </c>
-      <c r="X236" t="inlineStr"/>
-      <c r="Y236" t="inlineStr">
-        <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Opioid_Outcomes.md</t>
-        </is>
-      </c>
-      <c r="Z236" t="inlineStr">
-        <is>
-          <t>HepVu 2014-2022</t>
-        </is>
-      </c>
-      <c r="AA236" t="inlineStr">
-        <is>
-          <t>HepVu, Emory University Rollins School of Public Health, 2014-2022</t>
-        </is>
-      </c>
-      <c r="AB236" t="inlineStr"/>
-      <c r="AC236" t="inlineStr"/>
-      <c r="AD236" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/src/reference/data-dictionaries/S_Dict.xlsx
+++ b/docs/src/reference/data-dictionaries/S_Dict.xlsx
@@ -10717,12 +10717,12 @@
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>SAMHSA 2020</t>
+          <t>SAMHSA 2020, 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB138" t="inlineStr"/>
@@ -10781,12 +10781,12 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>SAMHSA 2020</t>
+          <t>SAMHSA 2020, 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB139" t="inlineStr"/>
@@ -10845,12 +10845,12 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>SAMHSA 2020</t>
+          <t>SAMHSA 2020, 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB140" t="inlineStr"/>
@@ -10909,12 +10909,12 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>SAMHSA 2020</t>
+          <t>SAMHSA 2020, 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB141" t="inlineStr"/>
@@ -10973,12 +10973,12 @@
       </c>
       <c r="Z142" t="inlineStr">
         <is>
-          <t>SAMHSA 2020</t>
+          <t>SAMHSA 2020, 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB142" t="inlineStr"/>
@@ -11037,12 +11037,12 @@
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>SAMHSA 2020</t>
+          <t>SAMHSA 2020, 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB143" t="inlineStr"/>
@@ -11101,12 +11101,12 @@
       </c>
       <c r="Z144" t="inlineStr">
         <is>
-          <t>SAMHSA 2020</t>
+          <t>SAMHSA 2020, 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB144" t="inlineStr"/>
@@ -11165,12 +11165,12 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>SAMHSA 2020</t>
+          <t>SAMHSA 2020, 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB145" t="inlineStr"/>
@@ -11229,12 +11229,12 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>SAMHSA 2020</t>
+          <t>SAMHSA 2020, 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB146" t="inlineStr"/>

--- a/docs/src/reference/data-dictionaries/S_Dict.xlsx
+++ b/docs/src/reference/data-dictionaries/S_Dict.xlsx
@@ -930,7 +930,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>% Persons aged 25 years and over with a bachelor’s degree as their highest level of education</t>
+          <t>% Bachelor's degree</t>
         </is>
       </c>
       <c r="X4" t="inlineStr"/>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>% Population aged 25 years and over whose highest educational attainment is a high school diploma (or equivalent)</t>
+          <t>% High School Graduate</t>
         </is>
       </c>
       <c r="X5" t="inlineStr"/>
@@ -1106,7 +1106,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>% Population aged 25 years and over with less than a high school diploma</t>
+          <t>% No High School Diploma</t>
         </is>
       </c>
       <c r="X6" t="inlineStr"/>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>Proportion of the population aged 5+ who speak a language other than English at home but are proficient in English</t>
+          <t xml:space="preserve">% English Proficiency </t>
         </is>
       </c>
       <c r="X7" t="inlineStr"/>
@@ -1262,7 +1262,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>% Population aged 25 years and over with a graduate or professional degree</t>
+          <t>% Graduate or Professional Degree</t>
         </is>
       </c>
       <c r="X8" t="inlineStr"/>
@@ -1350,7 +1350,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>% Population 25 years and over with some college, but no degree</t>
+          <t>% Some College, but No Degree</t>
         </is>
       </c>
       <c r="X9" t="inlineStr"/>

--- a/docs/src/reference/data-dictionaries/S_Dict.xlsx
+++ b/docs/src/reference/data-dictionaries/S_Dict.xlsx
@@ -9456,7 +9456,11 @@
       <c r="P119" t="inlineStr"/>
       <c r="Q119" t="inlineStr"/>
       <c r="R119" t="inlineStr"/>
-      <c r="S119" t="inlineStr"/>
+      <c r="S119" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T119" t="inlineStr"/>
       <c r="U119" t="inlineStr"/>
       <c r="V119" t="inlineStr">

--- a/docs/src/reference/data-dictionaries/S_Dict.xlsx
+++ b/docs/src/reference/data-dictionaries/S_Dict.xlsx
@@ -4298,7 +4298,7 @@
       </c>
       <c r="W45" t="inlineStr">
         <is>
-          <t>Count Black/African American Populationw</t>
+          <t>Count Black/African American Population</t>
         </is>
       </c>
       <c r="X45" t="inlineStr"/>
@@ -4390,7 +4390,7 @@
       </c>
       <c r="W46" t="inlineStr">
         <is>
-          <t>% Black/African American Populationw</t>
+          <t>% Black/African American Population</t>
         </is>
       </c>
       <c r="X46" t="inlineStr"/>
@@ -16782,7 +16782,7 @@
       </c>
       <c r="W220" t="inlineStr">
         <is>
-          <t>Average Ages between 50 to 74 Hepitatis C virus Deaths</t>
+          <t>Average Ages between 50 to 74 Hepatitis C virus Deaths</t>
         </is>
       </c>
       <c r="X220" t="inlineStr"/>

--- a/docs/src/reference/data-dictionaries/S_Dict.xlsx
+++ b/docs/src/reference/data-dictionaries/S_Dict.xlsx
@@ -2474,7 +2474,7 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>% Population: Age 15-44</t>
+          <t>Population: Age 15-44 (count)</t>
         </is>
       </c>
       <c r="X24" t="inlineStr"/>
@@ -2558,7 +2558,7 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>% Population: Age 15-44</t>
+          <t>% Population: Age 15-44 (percent)</t>
         </is>
       </c>
       <c r="X25" t="inlineStr"/>
@@ -3406,7 +3406,7 @@
       </c>
       <c r="W35" t="inlineStr">
         <is>
-          <t>% Population: Age 65+</t>
+          <t>Population: Age 65+ (count)</t>
         </is>
       </c>
       <c r="X35" t="inlineStr"/>
@@ -3498,7 +3498,7 @@
       </c>
       <c r="W36" t="inlineStr">
         <is>
-          <t>% Population: Age 65+</t>
+          <t>% Population: Age 65+ (percent)</t>
         </is>
       </c>
       <c r="X36" t="inlineStr"/>
@@ -8234,7 +8234,7 @@
       </c>
       <c r="W100" t="inlineStr">
         <is>
-          <t>Driving Time (min) to Nearest Buprenorphine Provider</t>
+          <t>Driving Time (min) to nearest Buprenorphine Provider (state/county average)</t>
         </is>
       </c>
       <c r="X100" t="inlineStr"/>
@@ -8686,7 +8686,7 @@
       </c>
       <c r="W107" t="inlineStr">
         <is>
-          <t>Driving Time (min) to Nearest Methadone Provider</t>
+          <t>Driving Time (min) to nearest Methadone Provider (state/county average)</t>
         </is>
       </c>
       <c r="X107" t="inlineStr"/>
@@ -8946,7 +8946,7 @@
       </c>
       <c r="W111" t="inlineStr">
         <is>
-          <t>Driving Time (min) to Nearest Naltrexone Provider</t>
+          <t>Driving Time (min) to nearest Naltrexone Provider (state/county average)</t>
         </is>
       </c>
       <c r="X111" t="inlineStr"/>
@@ -9206,7 +9206,7 @@
       </c>
       <c r="W115" t="inlineStr">
         <is>
-          <t>Driving Time (min) to nearest Opioid Treatment Program (OTP)</t>
+          <t>Driving Time (min) to nearest Opioid Treatment Program (OTP) (state/county average)</t>
         </is>
       </c>
       <c r="X115" t="inlineStr"/>
@@ -9922,7 +9922,7 @@
       </c>
       <c r="W126" t="inlineStr">
         <is>
-          <t>Driving Time (min) to nearest Mental Health Provider</t>
+          <t>Driving Time (min) to nearest Mental Health Provider (state/county average)</t>
         </is>
       </c>
       <c r="X126" t="inlineStr"/>
@@ -10710,7 +10710,7 @@
       </c>
       <c r="W138" t="inlineStr">
         <is>
-          <t>Driving Time (min) to nearest Substance Use Treatment program</t>
+          <t>Driving Time (min) to nearest Substance Use Treatment program (2025)</t>
         </is>
       </c>
       <c r="X138" t="inlineStr"/>
@@ -10838,7 +10838,7 @@
       </c>
       <c r="W140" t="inlineStr">
         <is>
-          <t>Tracts with Substance Use Treatment (SUT) program (30-min drive)</t>
+          <t>Tracts with Substance Use Treatment (SUT) program (30-min drive) (2025)</t>
         </is>
       </c>
       <c r="X140" t="inlineStr"/>
@@ -10966,7 +10966,7 @@
       </c>
       <c r="W142" t="inlineStr">
         <is>
-          <t>% tracts with Substance Use Treatment program (30-min drive)</t>
+          <t>% tracts with Substance Use Treatment program (30-min drive) (2025)</t>
         </is>
       </c>
       <c r="X142" t="inlineStr"/>
@@ -11094,7 +11094,7 @@
       </c>
       <c r="W144" t="inlineStr">
         <is>
-          <t>Driving Time (min) to nearest Substance Use Treatment program</t>
+          <t>Driving Time (min) to nearest Substance Use Treatment program (2020)</t>
         </is>
       </c>
       <c r="X144" t="inlineStr"/>
@@ -11158,7 +11158,7 @@
       </c>
       <c r="W145" t="inlineStr">
         <is>
-          <t>Tracts with Substance Use Treatment (SUT) program (30-min drive)</t>
+          <t>Tracts with Substance Use Treatment (SUT) program (30-min drive) (2020)</t>
         </is>
       </c>
       <c r="X145" t="inlineStr"/>
@@ -11222,7 +11222,7 @@
       </c>
       <c r="W146" t="inlineStr">
         <is>
-          <t>% tracts with Substance Use Treatment program (30-min drive)</t>
+          <t>% tracts with Substance Use Treatment program (30-min drive) (2020)</t>
         </is>
       </c>
       <c r="X146" t="inlineStr"/>

--- a/docs/src/reference/data-dictionaries/S_Dict.xlsx
+++ b/docs/src/reference/data-dictionaries/S_Dict.xlsx
@@ -8234,7 +8234,7 @@
       </c>
       <c r="W100" t="inlineStr">
         <is>
-          <t>Driving Time (min) to nearest Buprenorphine Provider (state/county average)</t>
+          <t>Average Driving Time (min) to Nearest Buprenorphine Provider(state/county average)</t>
         </is>
       </c>
       <c r="X100" t="inlineStr"/>
@@ -8426,7 +8426,7 @@
       </c>
       <c r="W103" t="inlineStr">
         <is>
-          <t>% Tracts within 30-min drive of Buprenorphine Provider(BUP), with Impedance factor</t>
+          <t>% Tracts with Buprenorphine Provider (30-min driving range), with Impedance Factor</t>
         </is>
       </c>
       <c r="X103" t="inlineStr"/>
@@ -8686,7 +8686,7 @@
       </c>
       <c r="W107" t="inlineStr">
         <is>
-          <t>Driving Time (min) to nearest Methadone Provider (state/county average)</t>
+          <t>Average Driving Time (min) to Nearest Methadone Provider (state/county average)</t>
         </is>
       </c>
       <c r="X107" t="inlineStr"/>
@@ -8750,7 +8750,7 @@
       </c>
       <c r="W108" t="inlineStr">
         <is>
-          <t>Average driving time to nearest Methadone Provider(MET), with Impedance factor</t>
+          <t>Average Driving Time (min) to Nearest Methadone Provider (state/county average) with Impedance factor</t>
         </is>
       </c>
       <c r="X108" t="inlineStr"/>
@@ -8878,7 +8878,7 @@
       </c>
       <c r="W110" t="inlineStr">
         <is>
-          <t>% Tracts within 30-min drive of Methadone Provider(MET), with Impedance factor</t>
+          <t>% Tracts With Methadone Provider (30-min drive), with Impedance Factor</t>
         </is>
       </c>
       <c r="X110" t="inlineStr"/>
@@ -8946,7 +8946,7 @@
       </c>
       <c r="W111" t="inlineStr">
         <is>
-          <t>Driving Time (min) to nearest Naltrexone Provider (state/county average)</t>
+          <t>Average Driving Time (min) to Nearest Naltrexone Provider (state/county average)</t>
         </is>
       </c>
       <c r="X111" t="inlineStr"/>
@@ -9138,7 +9138,7 @@
       </c>
       <c r="W114" t="inlineStr">
         <is>
-          <t>% Tracts within 30-min drive of Naltrexone Provider (NALT), with Impedance factor</t>
+          <t>% Tracts with Naltrexone Provider (30-min drive), with Impedance factor</t>
         </is>
       </c>
       <c r="X114" t="inlineStr"/>
@@ -9206,7 +9206,7 @@
       </c>
       <c r="W115" t="inlineStr">
         <is>
-          <t>Driving Time (min) to nearest Opioid Treatment Program (OTP) (state/county average)</t>
+          <t>Average Driving Time (min) to Nearest Opioid Treatment Program (OTP) (state/county average)</t>
         </is>
       </c>
       <c r="X115" t="inlineStr"/>
@@ -10710,7 +10710,7 @@
       </c>
       <c r="W138" t="inlineStr">
         <is>
-          <t>Driving Time (min) to nearest Substance Use Treatment program (2025)</t>
+          <t>Average Driving Time (min) to nearest Substance Use Treatment program (2025)</t>
         </is>
       </c>
       <c r="X138" t="inlineStr"/>
@@ -11094,7 +11094,7 @@
       </c>
       <c r="W144" t="inlineStr">
         <is>
-          <t>Driving Time (min) to nearest Substance Use Treatment program (2020)</t>
+          <t>Average Driving Time (min) to nearest Substance Use Treatment program (2020)</t>
         </is>
       </c>
       <c r="X144" t="inlineStr"/>
